--- a/Data/EXCEL/Transfer/salemon/202206/3592-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/3592-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93950898-ABA2-4A59-9893-683F45F9B6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55C54EA7-2C8C-4F8A-BF9B-4DC6096CAEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="3592-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1218,22 +1218,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q181"/>
+  <dimension ref="A1:Q182"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="10.5" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="10.5" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="12.625" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="10.5" customWidth="1"/>
-    <col min="10" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="10.5" customWidth="1"/>
-    <col min="15" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="11.25" customWidth="1"/>
+    <col min="1" max="1" width="14.875" customWidth="1"/>
+    <col min="2" max="2" width="11.875" customWidth="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="4" max="4" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="13.75" customWidth="1"/>
+    <col min="7" max="7" width="14.375" customWidth="1"/>
+    <col min="8" max="8" width="12.5" customWidth="1"/>
+    <col min="9" max="9" width="11.875" customWidth="1"/>
+    <col min="10" max="13" width="12.5" customWidth="1"/>
+    <col min="14" max="14" width="11.875" customWidth="1"/>
+    <col min="15" max="16" width="12.5" customWidth="1"/>
+    <col min="17" max="17" width="13.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1386,325 +1386,325 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="C5" s="7">
-        <v>509</v>
+        <v>347.5</v>
       </c>
       <c r="D5" s="7">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="E5" s="7">
-        <v>470</v>
+        <v>346.5</v>
       </c>
       <c r="F5" s="8">
-        <v>19.5</v>
+        <v>-161.5</v>
       </c>
       <c r="G5" s="8">
-        <v>3.98</v>
+        <v>-31.73</v>
       </c>
       <c r="H5" s="9">
-        <v>24.7</v>
-      </c>
-      <c r="I5" s="10">
-        <v>-8.67</v>
+        <v>18.489999999999998</v>
+      </c>
+      <c r="I5" s="8">
+        <v>-25.2</v>
       </c>
       <c r="J5" s="8">
-        <v>22.3</v>
+        <v>-10.4</v>
       </c>
       <c r="K5" s="9">
-        <v>128.69999999999999</v>
-      </c>
-      <c r="L5" s="8">
-        <v>37.4</v>
+        <v>147.19999999999999</v>
+      </c>
+      <c r="L5" s="10">
+        <v>28.7</v>
       </c>
       <c r="M5" s="9">
-        <v>24.7</v>
-      </c>
-      <c r="N5" s="10">
-        <v>-8.67</v>
+        <v>18.489999999999998</v>
+      </c>
+      <c r="N5" s="8">
+        <v>-25.2</v>
       </c>
       <c r="O5" s="8">
-        <v>22.3</v>
+        <v>-10.4</v>
       </c>
       <c r="P5" s="9">
-        <v>128.69999999999999</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>37.4</v>
+        <v>147.19999999999999</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>28.7</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="C6" s="7">
-        <v>489.5</v>
+        <v>509</v>
       </c>
       <c r="D6" s="7">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="E6" s="7">
-        <v>446.5</v>
+        <v>470</v>
       </c>
       <c r="F6" s="10">
-        <v>-20.5</v>
+        <v>19.5</v>
       </c>
       <c r="G6" s="10">
-        <v>-4.0199999999999996</v>
+        <v>3.98</v>
       </c>
       <c r="H6" s="9">
-        <v>27.05</v>
+        <v>24.7</v>
       </c>
       <c r="I6" s="8">
-        <v>1.81</v>
-      </c>
-      <c r="J6" s="8">
-        <v>26</v>
+        <v>-8.67</v>
+      </c>
+      <c r="J6" s="10">
+        <v>22.3</v>
       </c>
       <c r="K6" s="9">
-        <v>104</v>
-      </c>
-      <c r="L6" s="8">
-        <v>41.5</v>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="L6" s="10">
+        <v>37.4</v>
       </c>
       <c r="M6" s="9">
-        <v>27.05</v>
+        <v>24.7</v>
       </c>
       <c r="N6" s="8">
-        <v>1.81</v>
-      </c>
-      <c r="O6" s="8">
-        <v>26</v>
+        <v>-8.67</v>
+      </c>
+      <c r="O6" s="10">
+        <v>22.3</v>
       </c>
       <c r="P6" s="9">
-        <v>104</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>41.5</v>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>37.4</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>602</v>
+        <v>503</v>
       </c>
       <c r="C7" s="7">
-        <v>510</v>
+        <v>489.5</v>
       </c>
       <c r="D7" s="7">
-        <v>608</v>
+        <v>514</v>
       </c>
       <c r="E7" s="7">
-        <v>494</v>
-      </c>
-      <c r="F7" s="10">
-        <v>-86</v>
-      </c>
-      <c r="G7" s="10">
-        <v>-14.43</v>
+        <v>446.5</v>
+      </c>
+      <c r="F7" s="8">
+        <v>-20.5</v>
+      </c>
+      <c r="G7" s="8">
+        <v>-4.0199999999999996</v>
       </c>
       <c r="H7" s="9">
-        <v>26.57</v>
-      </c>
-      <c r="I7" s="8">
-        <v>10</v>
-      </c>
-      <c r="J7" s="8">
-        <v>39</v>
+        <v>27.05</v>
+      </c>
+      <c r="I7" s="10">
+        <v>1.81</v>
+      </c>
+      <c r="J7" s="10">
+        <v>26</v>
       </c>
       <c r="K7" s="9">
-        <v>76.98</v>
-      </c>
-      <c r="L7" s="8">
-        <v>47.8</v>
+        <v>104</v>
+      </c>
+      <c r="L7" s="10">
+        <v>41.5</v>
       </c>
       <c r="M7" s="9">
-        <v>26.57</v>
-      </c>
-      <c r="N7" s="8">
-        <v>10</v>
-      </c>
-      <c r="O7" s="8">
-        <v>39</v>
+        <v>27.05</v>
+      </c>
+      <c r="N7" s="10">
+        <v>1.81</v>
+      </c>
+      <c r="O7" s="10">
+        <v>26</v>
       </c>
       <c r="P7" s="9">
-        <v>76.98</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>47.8</v>
+        <v>104</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>41.5</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>641</v>
+        <v>602</v>
       </c>
       <c r="C8" s="7">
-        <v>596</v>
+        <v>510</v>
       </c>
       <c r="D8" s="7">
-        <v>699</v>
+        <v>608</v>
       </c>
       <c r="E8" s="7">
-        <v>560</v>
-      </c>
-      <c r="F8" s="10">
-        <v>-30</v>
-      </c>
-      <c r="G8" s="10">
-        <v>-4.79</v>
+        <v>494</v>
+      </c>
+      <c r="F8" s="8">
+        <v>-86</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-14.43</v>
       </c>
       <c r="H8" s="9">
-        <v>24.14</v>
+        <v>26.57</v>
       </c>
       <c r="I8" s="10">
-        <v>-8.08</v>
-      </c>
-      <c r="J8" s="8">
-        <v>58.9</v>
+        <v>10</v>
+      </c>
+      <c r="J8" s="10">
+        <v>39</v>
       </c>
       <c r="K8" s="9">
-        <v>50.41</v>
-      </c>
-      <c r="L8" s="8">
-        <v>53</v>
+        <v>76.98</v>
+      </c>
+      <c r="L8" s="10">
+        <v>47.8</v>
       </c>
       <c r="M8" s="9">
-        <v>24.14</v>
+        <v>26.57</v>
       </c>
       <c r="N8" s="10">
-        <v>-8.08</v>
-      </c>
-      <c r="O8" s="8">
-        <v>58.9</v>
+        <v>10</v>
+      </c>
+      <c r="O8" s="10">
+        <v>39</v>
       </c>
       <c r="P8" s="9">
-        <v>50.41</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>53</v>
+        <v>76.98</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>47.8</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>531</v>
+        <v>641</v>
       </c>
       <c r="C9" s="7">
-        <v>626</v>
+        <v>596</v>
       </c>
       <c r="D9" s="7">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="E9" s="7">
-        <v>503</v>
+        <v>560</v>
       </c>
       <c r="F9" s="8">
-        <v>318</v>
+        <v>-30</v>
       </c>
       <c r="G9" s="8">
-        <v>103.25</v>
+        <v>-4.79</v>
       </c>
       <c r="H9" s="9">
-        <v>26.27</v>
+        <v>24.14</v>
       </c>
       <c r="I9" s="8">
-        <v>11.7</v>
-      </c>
-      <c r="J9" s="8">
-        <v>47.9</v>
+        <v>-8.08</v>
+      </c>
+      <c r="J9" s="10">
+        <v>58.9</v>
       </c>
       <c r="K9" s="9">
-        <v>26.27</v>
-      </c>
-      <c r="L9" s="8">
-        <v>47.9</v>
+        <v>50.41</v>
+      </c>
+      <c r="L9" s="10">
+        <v>53</v>
       </c>
       <c r="M9" s="9">
-        <v>26.27</v>
+        <v>24.14</v>
       </c>
       <c r="N9" s="8">
-        <v>11.7</v>
-      </c>
-      <c r="O9" s="8">
-        <v>47.9</v>
+        <v>-8.08</v>
+      </c>
+      <c r="O9" s="10">
+        <v>58.9</v>
       </c>
       <c r="P9" s="9">
-        <v>26.27</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>47.9</v>
+        <v>50.41</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>17</v>
+        <v>44562</v>
+      </c>
+      <c r="B10" s="7">
+        <v>531</v>
+      </c>
+      <c r="C10" s="7">
+        <v>626</v>
+      </c>
+      <c r="D10" s="7">
+        <v>690</v>
+      </c>
+      <c r="E10" s="7">
+        <v>503</v>
+      </c>
+      <c r="F10" s="10">
+        <v>318</v>
+      </c>
+      <c r="G10" s="10">
+        <v>103.25</v>
       </c>
       <c r="H10" s="9">
-        <v>23.51</v>
-      </c>
-      <c r="I10" s="8">
-        <v>8.6</v>
-      </c>
-      <c r="J10" s="8">
-        <v>52.3</v>
+        <v>26.27</v>
+      </c>
+      <c r="I10" s="10">
+        <v>11.7</v>
+      </c>
+      <c r="J10" s="10">
+        <v>47.9</v>
       </c>
       <c r="K10" s="9">
-        <v>248.3</v>
-      </c>
-      <c r="L10" s="8">
-        <v>72.2</v>
+        <v>26.27</v>
+      </c>
+      <c r="L10" s="10">
+        <v>47.9</v>
       </c>
       <c r="M10" s="9">
-        <v>23.51</v>
-      </c>
-      <c r="N10" s="8">
-        <v>8.6</v>
-      </c>
-      <c r="O10" s="8">
-        <v>52.3</v>
+        <v>26.27</v>
+      </c>
+      <c r="N10" s="10">
+        <v>11.7</v>
+      </c>
+      <c r="O10" s="10">
+        <v>47.9</v>
       </c>
       <c r="P10" s="9">
-        <v>248.3</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>72.2</v>
+        <v>26.27</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>47.9</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>17</v>
@@ -1725,39 +1725,39 @@
         <v>17</v>
       </c>
       <c r="H11" s="9">
-        <v>21.65</v>
-      </c>
-      <c r="I11" s="8">
-        <v>1.01</v>
-      </c>
-      <c r="J11" s="8">
-        <v>61.4</v>
+        <v>23.51</v>
+      </c>
+      <c r="I11" s="10">
+        <v>8.6</v>
+      </c>
+      <c r="J11" s="10">
+        <v>52.3</v>
       </c>
       <c r="K11" s="9">
-        <v>224.8</v>
-      </c>
-      <c r="L11" s="8">
-        <v>74.5</v>
+        <v>248.3</v>
+      </c>
+      <c r="L11" s="10">
+        <v>72.2</v>
       </c>
       <c r="M11" s="9">
-        <v>21.65</v>
-      </c>
-      <c r="N11" s="8">
-        <v>1.01</v>
-      </c>
-      <c r="O11" s="8">
-        <v>61.4</v>
+        <v>23.51</v>
+      </c>
+      <c r="N11" s="10">
+        <v>8.6</v>
+      </c>
+      <c r="O11" s="10">
+        <v>52.3</v>
       </c>
       <c r="P11" s="9">
-        <v>224.8</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>74.5</v>
+        <v>248.3</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>72.2</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>17</v>
@@ -1778,39 +1778,39 @@
         <v>17</v>
       </c>
       <c r="H12" s="9">
-        <v>21.43</v>
+        <v>21.65</v>
       </c>
       <c r="I12" s="10">
-        <v>-2.33</v>
-      </c>
-      <c r="J12" s="8">
-        <v>56.8</v>
+        <v>1.01</v>
+      </c>
+      <c r="J12" s="10">
+        <v>61.4</v>
       </c>
       <c r="K12" s="9">
-        <v>203.2</v>
-      </c>
-      <c r="L12" s="8">
-        <v>76.099999999999994</v>
+        <v>224.8</v>
+      </c>
+      <c r="L12" s="10">
+        <v>74.5</v>
       </c>
       <c r="M12" s="9">
-        <v>21.43</v>
+        <v>21.65</v>
       </c>
       <c r="N12" s="10">
-        <v>-2.33</v>
-      </c>
-      <c r="O12" s="8">
-        <v>56.8</v>
+        <v>1.01</v>
+      </c>
+      <c r="O12" s="10">
+        <v>61.4</v>
       </c>
       <c r="P12" s="9">
-        <v>203.2</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>76.099999999999994</v>
+        <v>224.8</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>74.5</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>17</v>
@@ -1831,39 +1831,39 @@
         <v>17</v>
       </c>
       <c r="H13" s="9">
-        <v>21.95</v>
-      </c>
-      <c r="I13" s="10">
-        <v>-3.63</v>
-      </c>
-      <c r="J13" s="8">
-        <v>58.7</v>
+        <v>21.43</v>
+      </c>
+      <c r="I13" s="8">
+        <v>-2.33</v>
+      </c>
+      <c r="J13" s="10">
+        <v>56.8</v>
       </c>
       <c r="K13" s="9">
-        <v>181.7</v>
-      </c>
-      <c r="L13" s="8">
-        <v>78.599999999999994</v>
+        <v>203.2</v>
+      </c>
+      <c r="L13" s="10">
+        <v>76.099999999999994</v>
       </c>
       <c r="M13" s="9">
-        <v>21.95</v>
-      </c>
-      <c r="N13" s="10">
-        <v>-3.63</v>
-      </c>
-      <c r="O13" s="8">
-        <v>58.7</v>
+        <v>21.43</v>
+      </c>
+      <c r="N13" s="8">
+        <v>-2.33</v>
+      </c>
+      <c r="O13" s="10">
+        <v>56.8</v>
       </c>
       <c r="P13" s="9">
-        <v>181.7</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>78.599999999999994</v>
+        <v>203.2</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>76.099999999999994</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>17</v>
@@ -1884,39 +1884,39 @@
         <v>17</v>
       </c>
       <c r="H14" s="9">
-        <v>22.77</v>
+        <v>21.95</v>
       </c>
       <c r="I14" s="8">
-        <v>0.53</v>
-      </c>
-      <c r="J14" s="8">
-        <v>78.2</v>
+        <v>-3.63</v>
+      </c>
+      <c r="J14" s="10">
+        <v>58.7</v>
       </c>
       <c r="K14" s="9">
-        <v>159.80000000000001</v>
-      </c>
-      <c r="L14" s="8">
-        <v>81.8</v>
+        <v>181.7</v>
+      </c>
+      <c r="L14" s="10">
+        <v>78.599999999999994</v>
       </c>
       <c r="M14" s="9">
-        <v>22.77</v>
+        <v>21.95</v>
       </c>
       <c r="N14" s="8">
-        <v>0.53</v>
-      </c>
-      <c r="O14" s="8">
-        <v>78.2</v>
+        <v>-3.63</v>
+      </c>
+      <c r="O14" s="10">
+        <v>58.7</v>
       </c>
       <c r="P14" s="9">
-        <v>159.80000000000001</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>81.8</v>
+        <v>181.7</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>78.599999999999994</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>17</v>
@@ -1937,39 +1937,39 @@
         <v>17</v>
       </c>
       <c r="H15" s="9">
-        <v>22.65</v>
-      </c>
-      <c r="I15" s="8">
-        <v>9.77</v>
-      </c>
-      <c r="J15" s="8">
-        <v>93.5</v>
+        <v>22.77</v>
+      </c>
+      <c r="I15" s="10">
+        <v>0.53</v>
+      </c>
+      <c r="J15" s="10">
+        <v>78.2</v>
       </c>
       <c r="K15" s="9">
-        <v>137</v>
-      </c>
-      <c r="L15" s="8">
-        <v>82.4</v>
+        <v>159.80000000000001</v>
+      </c>
+      <c r="L15" s="10">
+        <v>81.8</v>
       </c>
       <c r="M15" s="9">
-        <v>22.65</v>
-      </c>
-      <c r="N15" s="8">
-        <v>9.77</v>
-      </c>
-      <c r="O15" s="8">
-        <v>93.5</v>
+        <v>22.77</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0.53</v>
+      </c>
+      <c r="O15" s="10">
+        <v>78.2</v>
       </c>
       <c r="P15" s="9">
-        <v>137</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>82.4</v>
+        <v>159.80000000000001</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>81.8</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>17</v>
@@ -1990,39 +1990,39 @@
         <v>17</v>
       </c>
       <c r="H16" s="9">
-        <v>20.64</v>
-      </c>
-      <c r="I16" s="8">
-        <v>2.16</v>
-      </c>
-      <c r="J16" s="8">
-        <v>105.4</v>
+        <v>22.65</v>
+      </c>
+      <c r="I16" s="10">
+        <v>9.77</v>
+      </c>
+      <c r="J16" s="10">
+        <v>93.5</v>
       </c>
       <c r="K16" s="9">
-        <v>114.4</v>
-      </c>
-      <c r="L16" s="8">
-        <v>80.400000000000006</v>
+        <v>137</v>
+      </c>
+      <c r="L16" s="10">
+        <v>82.4</v>
       </c>
       <c r="M16" s="9">
-        <v>20.64</v>
-      </c>
-      <c r="N16" s="8">
-        <v>2.16</v>
-      </c>
-      <c r="O16" s="8">
-        <v>105.4</v>
+        <v>22.65</v>
+      </c>
+      <c r="N16" s="10">
+        <v>9.77</v>
+      </c>
+      <c r="O16" s="10">
+        <v>93.5</v>
       </c>
       <c r="P16" s="9">
-        <v>114.4</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>80.400000000000006</v>
+        <v>137</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>82.4</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>17</v>
@@ -2043,39 +2043,39 @@
         <v>17</v>
       </c>
       <c r="H17" s="9">
-        <v>20.2</v>
+        <v>20.64</v>
       </c>
       <c r="I17" s="10">
-        <v>-5.9</v>
-      </c>
-      <c r="J17" s="8">
-        <v>109</v>
+        <v>2.16</v>
+      </c>
+      <c r="J17" s="10">
+        <v>105.4</v>
       </c>
       <c r="K17" s="9">
-        <v>93.73</v>
-      </c>
-      <c r="L17" s="8">
-        <v>75.7</v>
+        <v>114.4</v>
+      </c>
+      <c r="L17" s="10">
+        <v>80.400000000000006</v>
       </c>
       <c r="M17" s="9">
-        <v>20.2</v>
+        <v>20.64</v>
       </c>
       <c r="N17" s="10">
-        <v>-5.9</v>
-      </c>
-      <c r="O17" s="8">
-        <v>109</v>
+        <v>2.16</v>
+      </c>
+      <c r="O17" s="10">
+        <v>105.4</v>
       </c>
       <c r="P17" s="9">
-        <v>93.73</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>75.7</v>
+        <v>114.4</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>80.400000000000006</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>17</v>
@@ -2096,39 +2096,39 @@
         <v>17</v>
       </c>
       <c r="H18" s="9">
-        <v>21.47</v>
+        <v>20.2</v>
       </c>
       <c r="I18" s="8">
-        <v>12.3</v>
-      </c>
-      <c r="J18" s="8">
-        <v>101.9</v>
+        <v>-5.9</v>
+      </c>
+      <c r="J18" s="10">
+        <v>109</v>
       </c>
       <c r="K18" s="9">
-        <v>73.53</v>
-      </c>
-      <c r="L18" s="8">
-        <v>68.3</v>
+        <v>93.73</v>
+      </c>
+      <c r="L18" s="10">
+        <v>75.7</v>
       </c>
       <c r="M18" s="9">
-        <v>21.47</v>
+        <v>20.2</v>
       </c>
       <c r="N18" s="8">
-        <v>12.3</v>
-      </c>
-      <c r="O18" s="8">
-        <v>101.9</v>
+        <v>-5.9</v>
+      </c>
+      <c r="O18" s="10">
+        <v>109</v>
       </c>
       <c r="P18" s="9">
-        <v>73.53</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>68.3</v>
+        <v>93.73</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>75.7</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>17</v>
@@ -2149,39 +2149,39 @@
         <v>17</v>
       </c>
       <c r="H19" s="9">
-        <v>19.11</v>
-      </c>
-      <c r="I19" s="8">
-        <v>25.7</v>
-      </c>
-      <c r="J19" s="8">
-        <v>66.599999999999994</v>
+        <v>21.47</v>
+      </c>
+      <c r="I19" s="10">
+        <v>12.3</v>
+      </c>
+      <c r="J19" s="10">
+        <v>101.9</v>
       </c>
       <c r="K19" s="9">
-        <v>52.06</v>
-      </c>
-      <c r="L19" s="8">
-        <v>57.5</v>
+        <v>73.53</v>
+      </c>
+      <c r="L19" s="10">
+        <v>68.3</v>
       </c>
       <c r="M19" s="9">
-        <v>19.11</v>
-      </c>
-      <c r="N19" s="8">
-        <v>25.7</v>
-      </c>
-      <c r="O19" s="8">
-        <v>66.599999999999994</v>
+        <v>21.47</v>
+      </c>
+      <c r="N19" s="10">
+        <v>12.3</v>
+      </c>
+      <c r="O19" s="10">
+        <v>101.9</v>
       </c>
       <c r="P19" s="9">
-        <v>52.06</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>57.5</v>
+        <v>73.53</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>68.3</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>17</v>
@@ -2202,39 +2202,39 @@
         <v>17</v>
       </c>
       <c r="H20" s="9">
-        <v>15.2</v>
+        <v>19.11</v>
       </c>
       <c r="I20" s="10">
-        <v>-14.4</v>
-      </c>
-      <c r="J20" s="8">
-        <v>47.4</v>
+        <v>25.7</v>
+      </c>
+      <c r="J20" s="10">
+        <v>66.599999999999994</v>
       </c>
       <c r="K20" s="9">
-        <v>32.96</v>
-      </c>
-      <c r="L20" s="8">
-        <v>52.6</v>
+        <v>52.06</v>
+      </c>
+      <c r="L20" s="10">
+        <v>57.5</v>
       </c>
       <c r="M20" s="9">
-        <v>15.2</v>
+        <v>19.11</v>
       </c>
       <c r="N20" s="10">
-        <v>-14.4</v>
-      </c>
-      <c r="O20" s="8">
-        <v>47.4</v>
+        <v>25.7</v>
+      </c>
+      <c r="O20" s="10">
+        <v>66.599999999999994</v>
       </c>
       <c r="P20" s="9">
-        <v>32.96</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>52.6</v>
+        <v>52.06</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>57.5</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>17</v>
@@ -2255,39 +2255,39 @@
         <v>17</v>
       </c>
       <c r="H21" s="9">
-        <v>17.760000000000002</v>
+        <v>15.2</v>
       </c>
       <c r="I21" s="8">
-        <v>15</v>
-      </c>
-      <c r="J21" s="8">
-        <v>57.5</v>
+        <v>-14.4</v>
+      </c>
+      <c r="J21" s="10">
+        <v>47.4</v>
       </c>
       <c r="K21" s="9">
-        <v>17.760000000000002</v>
-      </c>
-      <c r="L21" s="8">
-        <v>57.5</v>
+        <v>32.96</v>
+      </c>
+      <c r="L21" s="10">
+        <v>52.6</v>
       </c>
       <c r="M21" s="9">
-        <v>17.760000000000002</v>
+        <v>15.2</v>
       </c>
       <c r="N21" s="8">
-        <v>15</v>
-      </c>
-      <c r="O21" s="8">
-        <v>57.5</v>
+        <v>-14.4</v>
+      </c>
+      <c r="O21" s="10">
+        <v>47.4</v>
       </c>
       <c r="P21" s="9">
-        <v>17.760000000000002</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>57.5</v>
+        <v>32.96</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>52.6</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>17</v>
@@ -2308,39 +2308,39 @@
         <v>17</v>
       </c>
       <c r="H22" s="9">
-        <v>15.44</v>
-      </c>
-      <c r="I22" s="8">
-        <v>15.1</v>
-      </c>
-      <c r="J22" s="8">
-        <v>32.200000000000003</v>
+        <v>17.760000000000002</v>
+      </c>
+      <c r="I22" s="10">
+        <v>15</v>
+      </c>
+      <c r="J22" s="10">
+        <v>57.5</v>
       </c>
       <c r="K22" s="9">
-        <v>144.30000000000001</v>
-      </c>
-      <c r="L22" s="8">
-        <v>3.54</v>
+        <v>17.760000000000002</v>
+      </c>
+      <c r="L22" s="10">
+        <v>57.5</v>
       </c>
       <c r="M22" s="9">
-        <v>15.44</v>
-      </c>
-      <c r="N22" s="8">
-        <v>15.1</v>
-      </c>
-      <c r="O22" s="8">
-        <v>32.200000000000003</v>
+        <v>17.760000000000002</v>
+      </c>
+      <c r="N22" s="10">
+        <v>15</v>
+      </c>
+      <c r="O22" s="10">
+        <v>57.5</v>
       </c>
       <c r="P22" s="9">
-        <v>144.30000000000001</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>3.54</v>
+        <v>17.760000000000002</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>57.5</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>17</v>
@@ -2361,39 +2361,39 @@
         <v>17</v>
       </c>
       <c r="H23" s="9">
-        <v>13.42</v>
+        <v>15.44</v>
       </c>
       <c r="I23" s="10">
-        <v>-1.88</v>
-      </c>
-      <c r="J23" s="8">
-        <v>10.199999999999999</v>
+        <v>15.1</v>
+      </c>
+      <c r="J23" s="10">
+        <v>32.200000000000003</v>
       </c>
       <c r="K23" s="9">
-        <v>128.80000000000001</v>
-      </c>
-      <c r="L23" s="8">
-        <v>0.91</v>
+        <v>144.30000000000001</v>
+      </c>
+      <c r="L23" s="10">
+        <v>3.54</v>
       </c>
       <c r="M23" s="9">
-        <v>13.42</v>
+        <v>15.44</v>
       </c>
       <c r="N23" s="10">
-        <v>-1.88</v>
-      </c>
-      <c r="O23" s="8">
-        <v>10.199999999999999</v>
+        <v>15.1</v>
+      </c>
+      <c r="O23" s="10">
+        <v>32.200000000000003</v>
       </c>
       <c r="P23" s="9">
-        <v>128.80000000000001</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>0.91</v>
+        <v>144.30000000000001</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>3.54</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>17</v>
@@ -2414,39 +2414,39 @@
         <v>17</v>
       </c>
       <c r="H24" s="9">
-        <v>13.67</v>
-      </c>
-      <c r="I24" s="10">
-        <v>-1.1299999999999999</v>
-      </c>
-      <c r="J24" s="8">
-        <v>14.2</v>
+        <v>13.42</v>
+      </c>
+      <c r="I24" s="8">
+        <v>-1.88</v>
+      </c>
+      <c r="J24" s="10">
+        <v>10.199999999999999</v>
       </c>
       <c r="K24" s="9">
-        <v>115.4</v>
+        <v>128.80000000000001</v>
       </c>
       <c r="L24" s="10">
-        <v>-0.06</v>
+        <v>0.91</v>
       </c>
       <c r="M24" s="9">
-        <v>13.67</v>
-      </c>
-      <c r="N24" s="10">
-        <v>-1.1299999999999999</v>
-      </c>
-      <c r="O24" s="8">
-        <v>14.2</v>
+        <v>13.42</v>
+      </c>
+      <c r="N24" s="8">
+        <v>-1.88</v>
+      </c>
+      <c r="O24" s="10">
+        <v>10.199999999999999</v>
       </c>
       <c r="P24" s="9">
-        <v>115.4</v>
+        <v>128.80000000000001</v>
       </c>
       <c r="Q24" s="10">
-        <v>-0.06</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>17</v>
@@ -2467,39 +2467,39 @@
         <v>17</v>
       </c>
       <c r="H25" s="9">
-        <v>13.83</v>
+        <v>13.67</v>
       </c>
       <c r="I25" s="8">
-        <v>8.19</v>
-      </c>
-      <c r="J25" s="8">
-        <v>18.2</v>
+        <v>-1.1299999999999999</v>
+      </c>
+      <c r="J25" s="10">
+        <v>14.2</v>
       </c>
       <c r="K25" s="9">
-        <v>101.7</v>
-      </c>
-      <c r="L25" s="10">
-        <v>-1.71</v>
+        <v>115.4</v>
+      </c>
+      <c r="L25" s="8">
+        <v>-0.06</v>
       </c>
       <c r="M25" s="9">
-        <v>13.83</v>
+        <v>13.67</v>
       </c>
       <c r="N25" s="8">
-        <v>8.19</v>
-      </c>
-      <c r="O25" s="8">
-        <v>18.2</v>
+        <v>-1.1299999999999999</v>
+      </c>
+      <c r="O25" s="10">
+        <v>14.2</v>
       </c>
       <c r="P25" s="9">
-        <v>101.7</v>
-      </c>
-      <c r="Q25" s="10">
-        <v>-1.71</v>
+        <v>115.4</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>17</v>
@@ -2520,39 +2520,39 @@
         <v>17</v>
       </c>
       <c r="H26" s="9">
-        <v>12.78</v>
-      </c>
-      <c r="I26" s="8">
-        <v>9.19</v>
-      </c>
-      <c r="J26" s="8">
-        <v>3.1</v>
+        <v>13.83</v>
+      </c>
+      <c r="I26" s="10">
+        <v>8.19</v>
+      </c>
+      <c r="J26" s="10">
+        <v>18.2</v>
       </c>
       <c r="K26" s="9">
-        <v>87.89</v>
-      </c>
-      <c r="L26" s="10">
-        <v>-4.24</v>
+        <v>101.7</v>
+      </c>
+      <c r="L26" s="8">
+        <v>-1.71</v>
       </c>
       <c r="M26" s="9">
-        <v>12.78</v>
-      </c>
-      <c r="N26" s="8">
-        <v>9.19</v>
-      </c>
-      <c r="O26" s="8">
-        <v>3.1</v>
+        <v>13.83</v>
+      </c>
+      <c r="N26" s="10">
+        <v>8.19</v>
+      </c>
+      <c r="O26" s="10">
+        <v>18.2</v>
       </c>
       <c r="P26" s="9">
-        <v>87.89</v>
-      </c>
-      <c r="Q26" s="10">
-        <v>-4.24</v>
+        <v>101.7</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>17</v>
@@ -2573,39 +2573,39 @@
         <v>17</v>
       </c>
       <c r="H27" s="9">
-        <v>11.71</v>
-      </c>
-      <c r="I27" s="8">
-        <v>16.5</v>
+        <v>12.78</v>
+      </c>
+      <c r="I27" s="10">
+        <v>9.19</v>
       </c>
       <c r="J27" s="10">
-        <v>-0.88</v>
+        <v>3.1</v>
       </c>
       <c r="K27" s="9">
-        <v>75.11</v>
-      </c>
-      <c r="L27" s="10">
-        <v>-5.39</v>
+        <v>87.89</v>
+      </c>
+      <c r="L27" s="8">
+        <v>-4.24</v>
       </c>
       <c r="M27" s="9">
-        <v>11.71</v>
-      </c>
-      <c r="N27" s="8">
-        <v>16.5</v>
+        <v>12.78</v>
+      </c>
+      <c r="N27" s="10">
+        <v>9.19</v>
       </c>
       <c r="O27" s="10">
-        <v>-0.88</v>
+        <v>3.1</v>
       </c>
       <c r="P27" s="9">
-        <v>75.11</v>
-      </c>
-      <c r="Q27" s="10">
-        <v>-5.39</v>
+        <v>87.89</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>-4.24</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>17</v>
@@ -2626,39 +2626,39 @@
         <v>17</v>
       </c>
       <c r="H28" s="9">
-        <v>10.050000000000001</v>
-      </c>
-      <c r="I28" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="J28" s="10">
-        <v>-13.2</v>
+        <v>11.71</v>
+      </c>
+      <c r="I28" s="10">
+        <v>16.5</v>
+      </c>
+      <c r="J28" s="8">
+        <v>-0.88</v>
       </c>
       <c r="K28" s="9">
-        <v>63.4</v>
-      </c>
-      <c r="L28" s="10">
-        <v>-6.18</v>
+        <v>75.11</v>
+      </c>
+      <c r="L28" s="8">
+        <v>-5.39</v>
       </c>
       <c r="M28" s="9">
-        <v>10.050000000000001</v>
-      </c>
-      <c r="N28" s="8">
-        <v>3.94</v>
-      </c>
-      <c r="O28" s="10">
-        <v>-13.2</v>
+        <v>11.71</v>
+      </c>
+      <c r="N28" s="10">
+        <v>16.5</v>
+      </c>
+      <c r="O28" s="8">
+        <v>-0.88</v>
       </c>
       <c r="P28" s="9">
-        <v>63.4</v>
-      </c>
-      <c r="Q28" s="10">
-        <v>-6.18</v>
+        <v>75.11</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>-5.39</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>17</v>
@@ -2679,39 +2679,39 @@
         <v>17</v>
       </c>
       <c r="H29" s="9">
-        <v>9.67</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="I29" s="10">
-        <v>-9.09</v>
-      </c>
-      <c r="J29" s="10">
-        <v>-15.4</v>
+        <v>3.94</v>
+      </c>
+      <c r="J29" s="8">
+        <v>-13.2</v>
       </c>
       <c r="K29" s="9">
-        <v>53.36</v>
-      </c>
-      <c r="L29" s="10">
-        <v>-4.74</v>
+        <v>63.4</v>
+      </c>
+      <c r="L29" s="8">
+        <v>-6.18</v>
       </c>
       <c r="M29" s="9">
-        <v>9.67</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="N29" s="10">
-        <v>-9.09</v>
-      </c>
-      <c r="O29" s="10">
-        <v>-15.4</v>
+        <v>3.94</v>
+      </c>
+      <c r="O29" s="8">
+        <v>-13.2</v>
       </c>
       <c r="P29" s="9">
-        <v>53.36</v>
-      </c>
-      <c r="Q29" s="10">
-        <v>-4.74</v>
+        <v>63.4</v>
+      </c>
+      <c r="Q29" s="8">
+        <v>-6.18</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>17</v>
@@ -2732,39 +2732,39 @@
         <v>17</v>
       </c>
       <c r="H30" s="9">
-        <v>10.63</v>
-      </c>
-      <c r="I30" s="10">
-        <v>-7.25</v>
-      </c>
-      <c r="J30" s="10">
-        <v>-11.5</v>
+        <v>9.67</v>
+      </c>
+      <c r="I30" s="8">
+        <v>-9.09</v>
+      </c>
+      <c r="J30" s="8">
+        <v>-15.4</v>
       </c>
       <c r="K30" s="9">
-        <v>43.69</v>
-      </c>
-      <c r="L30" s="10">
-        <v>-2</v>
+        <v>53.36</v>
+      </c>
+      <c r="L30" s="8">
+        <v>-4.74</v>
       </c>
       <c r="M30" s="9">
-        <v>10.63</v>
-      </c>
-      <c r="N30" s="10">
-        <v>-7.25</v>
-      </c>
-      <c r="O30" s="10">
-        <v>-11.5</v>
+        <v>9.67</v>
+      </c>
+      <c r="N30" s="8">
+        <v>-9.09</v>
+      </c>
+      <c r="O30" s="8">
+        <v>-15.4</v>
       </c>
       <c r="P30" s="9">
-        <v>43.69</v>
-      </c>
-      <c r="Q30" s="10">
-        <v>-2</v>
+        <v>53.36</v>
+      </c>
+      <c r="Q30" s="8">
+        <v>-4.74</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>17</v>
@@ -2785,39 +2785,39 @@
         <v>17</v>
       </c>
       <c r="H31" s="9">
-        <v>11.47</v>
+        <v>10.63</v>
       </c>
       <c r="I31" s="8">
-        <v>11.2</v>
-      </c>
-      <c r="J31" s="10">
-        <v>-1.32</v>
+        <v>-7.25</v>
+      </c>
+      <c r="J31" s="8">
+        <v>-11.5</v>
       </c>
       <c r="K31" s="9">
-        <v>33.06</v>
+        <v>43.69</v>
       </c>
       <c r="L31" s="8">
-        <v>1.51</v>
+        <v>-2</v>
       </c>
       <c r="M31" s="9">
-        <v>11.47</v>
+        <v>10.63</v>
       </c>
       <c r="N31" s="8">
-        <v>11.2</v>
-      </c>
-      <c r="O31" s="10">
-        <v>-1.32</v>
+        <v>-7.25</v>
+      </c>
+      <c r="O31" s="8">
+        <v>-11.5</v>
       </c>
       <c r="P31" s="9">
-        <v>33.06</v>
+        <v>43.69</v>
       </c>
       <c r="Q31" s="8">
-        <v>1.51</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>17</v>
@@ -2838,39 +2838,39 @@
         <v>17</v>
       </c>
       <c r="H32" s="9">
-        <v>10.31</v>
+        <v>11.47</v>
       </c>
       <c r="I32" s="10">
-        <v>-8.58</v>
+        <v>11.2</v>
       </c>
       <c r="J32" s="8">
-        <v>5.71</v>
+        <v>-1.32</v>
       </c>
       <c r="K32" s="9">
-        <v>21.59</v>
-      </c>
-      <c r="L32" s="8">
-        <v>3.08</v>
+        <v>33.06</v>
+      </c>
+      <c r="L32" s="10">
+        <v>1.51</v>
       </c>
       <c r="M32" s="9">
-        <v>10.31</v>
+        <v>11.47</v>
       </c>
       <c r="N32" s="10">
-        <v>-8.58</v>
+        <v>11.2</v>
       </c>
       <c r="O32" s="8">
-        <v>5.71</v>
+        <v>-1.32</v>
       </c>
       <c r="P32" s="9">
-        <v>21.59</v>
-      </c>
-      <c r="Q32" s="8">
-        <v>3.08</v>
+        <v>33.06</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>1.51</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>17</v>
@@ -2891,39 +2891,39 @@
         <v>17</v>
       </c>
       <c r="H33" s="9">
-        <v>11.28</v>
-      </c>
-      <c r="I33" s="10">
-        <v>-3.38</v>
-      </c>
-      <c r="J33" s="8">
-        <v>0.8</v>
+        <v>10.31</v>
+      </c>
+      <c r="I33" s="8">
+        <v>-8.58</v>
+      </c>
+      <c r="J33" s="10">
+        <v>5.71</v>
       </c>
       <c r="K33" s="9">
-        <v>11.28</v>
-      </c>
-      <c r="L33" s="8">
-        <v>0.8</v>
+        <v>21.59</v>
+      </c>
+      <c r="L33" s="10">
+        <v>3.08</v>
       </c>
       <c r="M33" s="9">
-        <v>11.28</v>
-      </c>
-      <c r="N33" s="10">
-        <v>-3.38</v>
-      </c>
-      <c r="O33" s="8">
-        <v>0.8</v>
+        <v>10.31</v>
+      </c>
+      <c r="N33" s="8">
+        <v>-8.58</v>
+      </c>
+      <c r="O33" s="10">
+        <v>5.71</v>
       </c>
       <c r="P33" s="9">
-        <v>11.28</v>
-      </c>
-      <c r="Q33" s="8">
-        <v>0.8</v>
+        <v>21.59</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>3.08</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>17</v>
@@ -2944,39 +2944,39 @@
         <v>17</v>
       </c>
       <c r="H34" s="9">
-        <v>11.67</v>
-      </c>
-      <c r="I34" s="10">
-        <v>-4.05</v>
+        <v>11.28</v>
+      </c>
+      <c r="I34" s="8">
+        <v>-3.38</v>
       </c>
       <c r="J34" s="10">
-        <v>-5.65</v>
+        <v>0.8</v>
       </c>
       <c r="K34" s="9">
-        <v>139.30000000000001</v>
-      </c>
-      <c r="L34" s="8">
-        <v>27.1</v>
+        <v>11.28</v>
+      </c>
+      <c r="L34" s="10">
+        <v>0.8</v>
       </c>
       <c r="M34" s="9">
-        <v>11.67</v>
-      </c>
-      <c r="N34" s="10">
-        <v>-4.05</v>
+        <v>11.28</v>
+      </c>
+      <c r="N34" s="8">
+        <v>-3.38</v>
       </c>
       <c r="O34" s="10">
-        <v>-5.65</v>
+        <v>0.8</v>
       </c>
       <c r="P34" s="9">
-        <v>139.30000000000001</v>
-      </c>
-      <c r="Q34" s="8">
-        <v>27.1</v>
+        <v>11.28</v>
+      </c>
+      <c r="Q34" s="10">
+        <v>0.8</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>17</v>
@@ -2997,39 +2997,39 @@
         <v>17</v>
       </c>
       <c r="H35" s="9">
-        <v>12.17</v>
+        <v>11.67</v>
       </c>
       <c r="I35" s="8">
-        <v>1.6</v>
+        <v>-4.05</v>
       </c>
       <c r="J35" s="8">
-        <v>10</v>
+        <v>-5.65</v>
       </c>
       <c r="K35" s="9">
-        <v>127.6</v>
-      </c>
-      <c r="L35" s="8">
-        <v>31.2</v>
+        <v>139.30000000000001</v>
+      </c>
+      <c r="L35" s="10">
+        <v>27.1</v>
       </c>
       <c r="M35" s="9">
-        <v>12.17</v>
+        <v>11.67</v>
       </c>
       <c r="N35" s="8">
-        <v>1.6</v>
+        <v>-4.05</v>
       </c>
       <c r="O35" s="8">
-        <v>10</v>
+        <v>-5.65</v>
       </c>
       <c r="P35" s="9">
-        <v>127.6</v>
-      </c>
-      <c r="Q35" s="8">
-        <v>31.2</v>
+        <v>139.30000000000001</v>
+      </c>
+      <c r="Q35" s="10">
+        <v>27.1</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>17</v>
@@ -3050,39 +3050,39 @@
         <v>17</v>
       </c>
       <c r="H36" s="9">
-        <v>11.98</v>
-      </c>
-      <c r="I36" s="8">
-        <v>2.33</v>
-      </c>
-      <c r="J36" s="8">
-        <v>14.7</v>
+        <v>12.17</v>
+      </c>
+      <c r="I36" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="J36" s="10">
+        <v>10</v>
       </c>
       <c r="K36" s="9">
-        <v>115.5</v>
-      </c>
-      <c r="L36" s="8">
-        <v>34</v>
+        <v>127.6</v>
+      </c>
+      <c r="L36" s="10">
+        <v>31.2</v>
       </c>
       <c r="M36" s="9">
-        <v>11.98</v>
-      </c>
-      <c r="N36" s="8">
-        <v>2.33</v>
-      </c>
-      <c r="O36" s="8">
-        <v>14.7</v>
+        <v>12.17</v>
+      </c>
+      <c r="N36" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="O36" s="10">
+        <v>10</v>
       </c>
       <c r="P36" s="9">
-        <v>115.5</v>
-      </c>
-      <c r="Q36" s="8">
-        <v>34</v>
+        <v>127.6</v>
+      </c>
+      <c r="Q36" s="10">
+        <v>31.2</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>17</v>
@@ -3103,39 +3103,39 @@
         <v>17</v>
       </c>
       <c r="H37" s="9">
-        <v>11.7</v>
+        <v>11.98</v>
       </c>
       <c r="I37" s="10">
-        <v>-5.61</v>
-      </c>
-      <c r="J37" s="8">
-        <v>11.3</v>
+        <v>2.33</v>
+      </c>
+      <c r="J37" s="10">
+        <v>14.7</v>
       </c>
       <c r="K37" s="9">
-        <v>103.5</v>
-      </c>
-      <c r="L37" s="8">
-        <v>36.6</v>
+        <v>115.5</v>
+      </c>
+      <c r="L37" s="10">
+        <v>34</v>
       </c>
       <c r="M37" s="9">
-        <v>11.7</v>
+        <v>11.98</v>
       </c>
       <c r="N37" s="10">
-        <v>-5.61</v>
-      </c>
-      <c r="O37" s="8">
-        <v>11.3</v>
+        <v>2.33</v>
+      </c>
+      <c r="O37" s="10">
+        <v>14.7</v>
       </c>
       <c r="P37" s="9">
-        <v>103.5</v>
-      </c>
-      <c r="Q37" s="8">
-        <v>36.6</v>
+        <v>115.5</v>
+      </c>
+      <c r="Q37" s="10">
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>17</v>
@@ -3156,39 +3156,39 @@
         <v>17</v>
       </c>
       <c r="H38" s="9">
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="I38" s="8">
-        <v>4.97</v>
-      </c>
-      <c r="J38" s="8">
-        <v>7.94</v>
+        <v>-5.61</v>
+      </c>
+      <c r="J38" s="10">
+        <v>11.3</v>
       </c>
       <c r="K38" s="9">
-        <v>91.79</v>
-      </c>
-      <c r="L38" s="8">
-        <v>40.700000000000003</v>
+        <v>103.5</v>
+      </c>
+      <c r="L38" s="10">
+        <v>36.6</v>
       </c>
       <c r="M38" s="9">
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="N38" s="8">
-        <v>4.97</v>
-      </c>
-      <c r="O38" s="8">
-        <v>7.94</v>
+        <v>-5.61</v>
+      </c>
+      <c r="O38" s="10">
+        <v>11.3</v>
       </c>
       <c r="P38" s="9">
-        <v>91.79</v>
-      </c>
-      <c r="Q38" s="8">
-        <v>40.700000000000003</v>
+        <v>103.5</v>
+      </c>
+      <c r="Q38" s="10">
+        <v>36.6</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>17</v>
@@ -3209,39 +3209,39 @@
         <v>17</v>
       </c>
       <c r="H39" s="9">
-        <v>11.81</v>
-      </c>
-      <c r="I39" s="8">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="J39" s="8">
-        <v>24.7</v>
+        <v>12.4</v>
+      </c>
+      <c r="I39" s="10">
+        <v>4.97</v>
+      </c>
+      <c r="J39" s="10">
+        <v>7.94</v>
       </c>
       <c r="K39" s="9">
-        <v>79.400000000000006</v>
-      </c>
-      <c r="L39" s="8">
-        <v>47.7</v>
+        <v>91.79</v>
+      </c>
+      <c r="L39" s="10">
+        <v>40.700000000000003</v>
       </c>
       <c r="M39" s="9">
-        <v>11.81</v>
-      </c>
-      <c r="N39" s="8">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="O39" s="8">
-        <v>24.7</v>
+        <v>12.4</v>
+      </c>
+      <c r="N39" s="10">
+        <v>4.97</v>
+      </c>
+      <c r="O39" s="10">
+        <v>7.94</v>
       </c>
       <c r="P39" s="9">
-        <v>79.400000000000006</v>
-      </c>
-      <c r="Q39" s="8">
-        <v>47.7</v>
+        <v>91.79</v>
+      </c>
+      <c r="Q39" s="10">
+        <v>40.700000000000003</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>17</v>
@@ -3262,39 +3262,39 @@
         <v>17</v>
       </c>
       <c r="H40" s="9">
-        <v>11.57</v>
-      </c>
-      <c r="I40" s="8">
-        <v>1.21</v>
-      </c>
-      <c r="J40" s="8">
-        <v>29.4</v>
+        <v>11.81</v>
+      </c>
+      <c r="I40" s="10">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="J40" s="10">
+        <v>24.7</v>
       </c>
       <c r="K40" s="9">
-        <v>67.59</v>
-      </c>
-      <c r="L40" s="8">
-        <v>52.6</v>
+        <v>79.400000000000006</v>
+      </c>
+      <c r="L40" s="10">
+        <v>47.7</v>
       </c>
       <c r="M40" s="9">
-        <v>11.57</v>
-      </c>
-      <c r="N40" s="8">
-        <v>1.21</v>
-      </c>
-      <c r="O40" s="8">
-        <v>29.4</v>
+        <v>11.81</v>
+      </c>
+      <c r="N40" s="10">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="O40" s="10">
+        <v>24.7</v>
       </c>
       <c r="P40" s="9">
-        <v>67.59</v>
-      </c>
-      <c r="Q40" s="8">
-        <v>52.6</v>
+        <v>79.400000000000006</v>
+      </c>
+      <c r="Q40" s="10">
+        <v>47.7</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>17</v>
@@ -3315,39 +3315,39 @@
         <v>17</v>
       </c>
       <c r="H41" s="9">
-        <v>11.43</v>
+        <v>11.57</v>
       </c>
       <c r="I41" s="10">
-        <v>-4.88</v>
-      </c>
-      <c r="J41" s="8">
-        <v>44.9</v>
+        <v>1.21</v>
+      </c>
+      <c r="J41" s="10">
+        <v>29.4</v>
       </c>
       <c r="K41" s="9">
-        <v>56.01</v>
-      </c>
-      <c r="L41" s="8">
-        <v>58.5</v>
+        <v>67.59</v>
+      </c>
+      <c r="L41" s="10">
+        <v>52.6</v>
       </c>
       <c r="M41" s="9">
-        <v>11.43</v>
+        <v>11.57</v>
       </c>
       <c r="N41" s="10">
-        <v>-4.88</v>
-      </c>
-      <c r="O41" s="8">
-        <v>44.9</v>
+        <v>1.21</v>
+      </c>
+      <c r="O41" s="10">
+        <v>29.4</v>
       </c>
       <c r="P41" s="9">
-        <v>56.01</v>
-      </c>
-      <c r="Q41" s="8">
-        <v>58.5</v>
+        <v>67.59</v>
+      </c>
+      <c r="Q41" s="10">
+        <v>52.6</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>17</v>
@@ -3368,39 +3368,39 @@
         <v>17</v>
       </c>
       <c r="H42" s="9">
-        <v>12.02</v>
+        <v>11.43</v>
       </c>
       <c r="I42" s="8">
-        <v>3.43</v>
-      </c>
-      <c r="J42" s="8">
-        <v>63.9</v>
+        <v>-4.88</v>
+      </c>
+      <c r="J42" s="10">
+        <v>44.9</v>
       </c>
       <c r="K42" s="9">
-        <v>44.58</v>
-      </c>
-      <c r="L42" s="8">
-        <v>62.4</v>
+        <v>56.01</v>
+      </c>
+      <c r="L42" s="10">
+        <v>58.5</v>
       </c>
       <c r="M42" s="9">
-        <v>12.02</v>
+        <v>11.43</v>
       </c>
       <c r="N42" s="8">
-        <v>3.43</v>
-      </c>
-      <c r="O42" s="8">
-        <v>63.9</v>
+        <v>-4.88</v>
+      </c>
+      <c r="O42" s="10">
+        <v>44.9</v>
       </c>
       <c r="P42" s="9">
-        <v>44.58</v>
-      </c>
-      <c r="Q42" s="8">
-        <v>62.4</v>
+        <v>56.01</v>
+      </c>
+      <c r="Q42" s="10">
+        <v>58.5</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>17</v>
@@ -3421,39 +3421,39 @@
         <v>17</v>
       </c>
       <c r="H43" s="9">
-        <v>11.62</v>
-      </c>
-      <c r="I43" s="8">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="J43" s="8">
-        <v>62</v>
+        <v>12.02</v>
+      </c>
+      <c r="I43" s="10">
+        <v>3.43</v>
+      </c>
+      <c r="J43" s="10">
+        <v>63.9</v>
       </c>
       <c r="K43" s="9">
-        <v>32.57</v>
-      </c>
-      <c r="L43" s="8">
-        <v>61.8</v>
+        <v>44.58</v>
+      </c>
+      <c r="L43" s="10">
+        <v>62.4</v>
       </c>
       <c r="M43" s="9">
-        <v>11.62</v>
-      </c>
-      <c r="N43" s="8">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="O43" s="8">
-        <v>62</v>
+        <v>12.02</v>
+      </c>
+      <c r="N43" s="10">
+        <v>3.43</v>
+      </c>
+      <c r="O43" s="10">
+        <v>63.9</v>
       </c>
       <c r="P43" s="9">
-        <v>32.57</v>
-      </c>
-      <c r="Q43" s="8">
-        <v>61.8</v>
+        <v>44.58</v>
+      </c>
+      <c r="Q43" s="10">
+        <v>62.4</v>
       </c>
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>17</v>
@@ -3474,39 +3474,39 @@
         <v>17</v>
       </c>
       <c r="H44" s="9">
-        <v>9.76</v>
+        <v>11.62</v>
       </c>
       <c r="I44" s="10">
-        <v>-12.8</v>
-      </c>
-      <c r="J44" s="8">
-        <v>67.400000000000006</v>
+        <v>19.100000000000001</v>
+      </c>
+      <c r="J44" s="10">
+        <v>62</v>
       </c>
       <c r="K44" s="9">
-        <v>20.95</v>
-      </c>
-      <c r="L44" s="8">
-        <v>61.7</v>
+        <v>32.57</v>
+      </c>
+      <c r="L44" s="10">
+        <v>61.8</v>
       </c>
       <c r="M44" s="9">
-        <v>9.76</v>
+        <v>11.62</v>
       </c>
       <c r="N44" s="10">
-        <v>-12.8</v>
-      </c>
-      <c r="O44" s="8">
-        <v>67.400000000000006</v>
+        <v>19.100000000000001</v>
+      </c>
+      <c r="O44" s="10">
+        <v>62</v>
       </c>
       <c r="P44" s="9">
-        <v>20.95</v>
-      </c>
-      <c r="Q44" s="8">
-        <v>61.7</v>
+        <v>32.57</v>
+      </c>
+      <c r="Q44" s="10">
+        <v>61.8</v>
       </c>
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>17</v>
@@ -3527,39 +3527,39 @@
         <v>17</v>
       </c>
       <c r="H45" s="9">
-        <v>11.19</v>
-      </c>
-      <c r="I45" s="10">
-        <v>-9.57</v>
-      </c>
-      <c r="J45" s="8">
-        <v>57</v>
+        <v>9.76</v>
+      </c>
+      <c r="I45" s="8">
+        <v>-12.8</v>
+      </c>
+      <c r="J45" s="10">
+        <v>67.400000000000006</v>
       </c>
       <c r="K45" s="9">
-        <v>11.19</v>
-      </c>
-      <c r="L45" s="8">
-        <v>57</v>
+        <v>20.95</v>
+      </c>
+      <c r="L45" s="10">
+        <v>61.7</v>
       </c>
       <c r="M45" s="9">
-        <v>11.19</v>
-      </c>
-      <c r="N45" s="10">
-        <v>-9.57</v>
-      </c>
-      <c r="O45" s="8">
-        <v>57</v>
+        <v>9.76</v>
+      </c>
+      <c r="N45" s="8">
+        <v>-12.8</v>
+      </c>
+      <c r="O45" s="10">
+        <v>67.400000000000006</v>
       </c>
       <c r="P45" s="9">
-        <v>11.19</v>
-      </c>
-      <c r="Q45" s="8">
-        <v>57</v>
+        <v>20.95</v>
+      </c>
+      <c r="Q45" s="10">
+        <v>61.7</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>17</v>
@@ -3580,39 +3580,39 @@
         <v>17</v>
       </c>
       <c r="H46" s="9">
-        <v>12.37</v>
+        <v>11.19</v>
       </c>
       <c r="I46" s="8">
-        <v>11.9</v>
-      </c>
-      <c r="J46" s="8">
-        <v>68.7</v>
+        <v>-9.57</v>
+      </c>
+      <c r="J46" s="10">
+        <v>57</v>
       </c>
       <c r="K46" s="9">
-        <v>109.6</v>
-      </c>
-      <c r="L46" s="8">
-        <v>17.399999999999999</v>
+        <v>11.19</v>
+      </c>
+      <c r="L46" s="10">
+        <v>57</v>
       </c>
       <c r="M46" s="9">
-        <v>12.37</v>
+        <v>11.19</v>
       </c>
       <c r="N46" s="8">
-        <v>11.9</v>
-      </c>
-      <c r="O46" s="8">
-        <v>68.7</v>
+        <v>-9.57</v>
+      </c>
+      <c r="O46" s="10">
+        <v>57</v>
       </c>
       <c r="P46" s="9">
-        <v>109.6</v>
-      </c>
-      <c r="Q46" s="8">
-        <v>17.399999999999999</v>
+        <v>11.19</v>
+      </c>
+      <c r="Q46" s="10">
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>17</v>
@@ -3633,39 +3633,39 @@
         <v>17</v>
       </c>
       <c r="H47" s="9">
-        <v>11.06</v>
-      </c>
-      <c r="I47" s="8">
-        <v>5.91</v>
-      </c>
-      <c r="J47" s="8">
-        <v>50.2</v>
+        <v>12.37</v>
+      </c>
+      <c r="I47" s="10">
+        <v>11.9</v>
+      </c>
+      <c r="J47" s="10">
+        <v>68.7</v>
       </c>
       <c r="K47" s="9">
-        <v>97.25</v>
-      </c>
-      <c r="L47" s="8">
-        <v>13.1</v>
+        <v>109.6</v>
+      </c>
+      <c r="L47" s="10">
+        <v>17.399999999999999</v>
       </c>
       <c r="M47" s="9">
-        <v>11.06</v>
-      </c>
-      <c r="N47" s="8">
-        <v>5.91</v>
-      </c>
-      <c r="O47" s="8">
-        <v>50.2</v>
+        <v>12.37</v>
+      </c>
+      <c r="N47" s="10">
+        <v>11.9</v>
+      </c>
+      <c r="O47" s="10">
+        <v>68.7</v>
       </c>
       <c r="P47" s="9">
-        <v>97.25</v>
-      </c>
-      <c r="Q47" s="8">
-        <v>13.1</v>
+        <v>109.6</v>
+      </c>
+      <c r="Q47" s="10">
+        <v>17.399999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>17</v>
@@ -3686,39 +3686,39 @@
         <v>17</v>
       </c>
       <c r="H48" s="9">
-        <v>10.44</v>
+        <v>11.06</v>
       </c>
       <c r="I48" s="10">
-        <v>-0.68</v>
-      </c>
-      <c r="J48" s="8">
-        <v>30.6</v>
+        <v>5.91</v>
+      </c>
+      <c r="J48" s="10">
+        <v>50.2</v>
       </c>
       <c r="K48" s="9">
-        <v>86.2</v>
-      </c>
-      <c r="L48" s="8">
-        <v>9.58</v>
+        <v>97.25</v>
+      </c>
+      <c r="L48" s="10">
+        <v>13.1</v>
       </c>
       <c r="M48" s="9">
-        <v>10.44</v>
+        <v>11.06</v>
       </c>
       <c r="N48" s="10">
-        <v>-0.68</v>
-      </c>
-      <c r="O48" s="8">
-        <v>30.6</v>
+        <v>5.91</v>
+      </c>
+      <c r="O48" s="10">
+        <v>50.2</v>
       </c>
       <c r="P48" s="9">
-        <v>86.2</v>
-      </c>
-      <c r="Q48" s="8">
-        <v>9.58</v>
+        <v>97.25</v>
+      </c>
+      <c r="Q48" s="10">
+        <v>13.1</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>17</v>
@@ -3739,39 +3739,39 @@
         <v>17</v>
       </c>
       <c r="H49" s="9">
-        <v>10.51</v>
-      </c>
-      <c r="I49" s="10">
-        <v>-8.48</v>
-      </c>
-      <c r="J49" s="8">
-        <v>24.3</v>
+        <v>10.44</v>
+      </c>
+      <c r="I49" s="8">
+        <v>-0.68</v>
+      </c>
+      <c r="J49" s="10">
+        <v>30.6</v>
       </c>
       <c r="K49" s="9">
-        <v>75.760000000000005</v>
-      </c>
-      <c r="L49" s="8">
-        <v>7.21</v>
+        <v>86.2</v>
+      </c>
+      <c r="L49" s="10">
+        <v>9.58</v>
       </c>
       <c r="M49" s="9">
-        <v>10.51</v>
-      </c>
-      <c r="N49" s="10">
-        <v>-8.48</v>
-      </c>
-      <c r="O49" s="8">
-        <v>24.3</v>
+        <v>10.44</v>
+      </c>
+      <c r="N49" s="8">
+        <v>-0.68</v>
+      </c>
+      <c r="O49" s="10">
+        <v>30.6</v>
       </c>
       <c r="P49" s="9">
-        <v>75.760000000000005</v>
-      </c>
-      <c r="Q49" s="8">
-        <v>7.21</v>
+        <v>86.2</v>
+      </c>
+      <c r="Q49" s="10">
+        <v>9.58</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>17</v>
@@ -3792,39 +3792,39 @@
         <v>17</v>
       </c>
       <c r="H50" s="9">
-        <v>11.49</v>
+        <v>10.51</v>
       </c>
       <c r="I50" s="8">
-        <v>21.3</v>
-      </c>
-      <c r="J50" s="8">
-        <v>39.700000000000003</v>
+        <v>-8.48</v>
+      </c>
+      <c r="J50" s="10">
+        <v>24.3</v>
       </c>
       <c r="K50" s="9">
-        <v>65.25</v>
-      </c>
-      <c r="L50" s="8">
-        <v>4.88</v>
+        <v>75.760000000000005</v>
+      </c>
+      <c r="L50" s="10">
+        <v>7.21</v>
       </c>
       <c r="M50" s="9">
-        <v>11.49</v>
+        <v>10.51</v>
       </c>
       <c r="N50" s="8">
-        <v>21.3</v>
-      </c>
-      <c r="O50" s="8">
-        <v>39.700000000000003</v>
+        <v>-8.48</v>
+      </c>
+      <c r="O50" s="10">
+        <v>24.3</v>
       </c>
       <c r="P50" s="9">
-        <v>65.25</v>
-      </c>
-      <c r="Q50" s="8">
-        <v>4.88</v>
+        <v>75.760000000000005</v>
+      </c>
+      <c r="Q50" s="10">
+        <v>7.21</v>
       </c>
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>17</v>
@@ -3845,39 +3845,39 @@
         <v>17</v>
       </c>
       <c r="H51" s="9">
-        <v>9.4700000000000006</v>
-      </c>
-      <c r="I51" s="8">
-        <v>5.85</v>
-      </c>
-      <c r="J51" s="8">
-        <v>15.6</v>
+        <v>11.49</v>
+      </c>
+      <c r="I51" s="10">
+        <v>21.3</v>
+      </c>
+      <c r="J51" s="10">
+        <v>39.700000000000003</v>
       </c>
       <c r="K51" s="9">
-        <v>53.76</v>
+        <v>65.25</v>
       </c>
       <c r="L51" s="10">
-        <v>-0.41</v>
+        <v>4.88</v>
       </c>
       <c r="M51" s="9">
-        <v>9.4700000000000006</v>
-      </c>
-      <c r="N51" s="8">
-        <v>5.85</v>
-      </c>
-      <c r="O51" s="8">
-        <v>15.6</v>
+        <v>11.49</v>
+      </c>
+      <c r="N51" s="10">
+        <v>21.3</v>
+      </c>
+      <c r="O51" s="10">
+        <v>39.700000000000003</v>
       </c>
       <c r="P51" s="9">
-        <v>53.76</v>
+        <v>65.25</v>
       </c>
       <c r="Q51" s="10">
-        <v>-0.41</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>17</v>
@@ -3898,39 +3898,39 @@
         <v>17</v>
       </c>
       <c r="H52" s="9">
-        <v>8.94</v>
-      </c>
-      <c r="I52" s="8">
-        <v>13.4</v>
-      </c>
-      <c r="J52" s="8">
-        <v>9.42</v>
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="I52" s="10">
+        <v>5.85</v>
+      </c>
+      <c r="J52" s="10">
+        <v>15.6</v>
       </c>
       <c r="K52" s="9">
-        <v>44.29</v>
-      </c>
-      <c r="L52" s="10">
-        <v>-3.28</v>
+        <v>53.76</v>
+      </c>
+      <c r="L52" s="8">
+        <v>-0.41</v>
       </c>
       <c r="M52" s="9">
-        <v>8.94</v>
-      </c>
-      <c r="N52" s="8">
-        <v>13.4</v>
-      </c>
-      <c r="O52" s="8">
-        <v>9.42</v>
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="N52" s="10">
+        <v>5.85</v>
+      </c>
+      <c r="O52" s="10">
+        <v>15.6</v>
       </c>
       <c r="P52" s="9">
-        <v>44.29</v>
-      </c>
-      <c r="Q52" s="10">
-        <v>-3.28</v>
+        <v>53.76</v>
+      </c>
+      <c r="Q52" s="8">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>17</v>
@@ -3951,39 +3951,39 @@
         <v>17</v>
       </c>
       <c r="H53" s="9">
-        <v>7.89</v>
-      </c>
-      <c r="I53" s="8">
-        <v>7.56</v>
-      </c>
-      <c r="J53" s="8">
-        <v>6.83</v>
+        <v>8.94</v>
+      </c>
+      <c r="I53" s="10">
+        <v>13.4</v>
+      </c>
+      <c r="J53" s="10">
+        <v>9.42</v>
       </c>
       <c r="K53" s="9">
-        <v>35.35</v>
-      </c>
-      <c r="L53" s="10">
-        <v>-6.04</v>
+        <v>44.29</v>
+      </c>
+      <c r="L53" s="8">
+        <v>-3.28</v>
       </c>
       <c r="M53" s="9">
-        <v>7.89</v>
-      </c>
-      <c r="N53" s="8">
-        <v>7.56</v>
-      </c>
-      <c r="O53" s="8">
-        <v>6.83</v>
+        <v>8.94</v>
+      </c>
+      <c r="N53" s="10">
+        <v>13.4</v>
+      </c>
+      <c r="O53" s="10">
+        <v>9.42</v>
       </c>
       <c r="P53" s="9">
-        <v>35.35</v>
-      </c>
-      <c r="Q53" s="10">
-        <v>-6.04</v>
+        <v>44.29</v>
+      </c>
+      <c r="Q53" s="8">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>17</v>
@@ -4004,39 +4004,39 @@
         <v>17</v>
       </c>
       <c r="H54" s="9">
-        <v>7.33</v>
-      </c>
-      <c r="I54" s="8">
-        <v>2.29</v>
+        <v>7.89</v>
+      </c>
+      <c r="I54" s="10">
+        <v>7.56</v>
       </c>
       <c r="J54" s="10">
-        <v>-4.96</v>
+        <v>6.83</v>
       </c>
       <c r="K54" s="9">
-        <v>27.46</v>
-      </c>
-      <c r="L54" s="10">
-        <v>-9.18</v>
+        <v>35.35</v>
+      </c>
+      <c r="L54" s="8">
+        <v>-6.04</v>
       </c>
       <c r="M54" s="9">
-        <v>7.33</v>
-      </c>
-      <c r="N54" s="8">
-        <v>2.29</v>
+        <v>7.89</v>
+      </c>
+      <c r="N54" s="10">
+        <v>7.56</v>
       </c>
       <c r="O54" s="10">
-        <v>-4.96</v>
+        <v>6.83</v>
       </c>
       <c r="P54" s="9">
-        <v>27.46</v>
-      </c>
-      <c r="Q54" s="10">
-        <v>-9.18</v>
+        <v>35.35</v>
+      </c>
+      <c r="Q54" s="8">
+        <v>-6.04</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>17</v>
@@ -4057,39 +4057,39 @@
         <v>17</v>
       </c>
       <c r="H55" s="9">
-        <v>7.17</v>
-      </c>
-      <c r="I55" s="8">
-        <v>23.1</v>
-      </c>
-      <c r="J55" s="10">
-        <v>-9.1199999999999992</v>
+        <v>7.33</v>
+      </c>
+      <c r="I55" s="10">
+        <v>2.29</v>
+      </c>
+      <c r="J55" s="8">
+        <v>-4.96</v>
       </c>
       <c r="K55" s="9">
-        <v>20.12</v>
-      </c>
-      <c r="L55" s="10">
-        <v>-10.6</v>
+        <v>27.46</v>
+      </c>
+      <c r="L55" s="8">
+        <v>-9.18</v>
       </c>
       <c r="M55" s="9">
-        <v>7.17</v>
-      </c>
-      <c r="N55" s="8">
-        <v>23.1</v>
-      </c>
-      <c r="O55" s="10">
-        <v>-9.1199999999999992</v>
+        <v>7.33</v>
+      </c>
+      <c r="N55" s="10">
+        <v>2.29</v>
+      </c>
+      <c r="O55" s="8">
+        <v>-4.96</v>
       </c>
       <c r="P55" s="9">
-        <v>20.12</v>
-      </c>
-      <c r="Q55" s="10">
-        <v>-10.6</v>
+        <v>27.46</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>-9.18</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>17</v>
@@ -4110,39 +4110,39 @@
         <v>17</v>
       </c>
       <c r="H56" s="9">
-        <v>5.83</v>
+        <v>7.17</v>
       </c>
       <c r="I56" s="10">
-        <v>-18.3</v>
-      </c>
-      <c r="J56" s="10">
-        <v>-7.35</v>
+        <v>23.1</v>
+      </c>
+      <c r="J56" s="8">
+        <v>-9.1199999999999992</v>
       </c>
       <c r="K56" s="9">
-        <v>12.95</v>
-      </c>
-      <c r="L56" s="10">
-        <v>-11.4</v>
+        <v>20.12</v>
+      </c>
+      <c r="L56" s="8">
+        <v>-10.6</v>
       </c>
       <c r="M56" s="9">
-        <v>5.83</v>
+        <v>7.17</v>
       </c>
       <c r="N56" s="10">
-        <v>-18.3</v>
-      </c>
-      <c r="O56" s="10">
-        <v>-7.35</v>
+        <v>23.1</v>
+      </c>
+      <c r="O56" s="8">
+        <v>-9.1199999999999992</v>
       </c>
       <c r="P56" s="9">
-        <v>12.95</v>
-      </c>
-      <c r="Q56" s="10">
-        <v>-11.4</v>
+        <v>20.12</v>
+      </c>
+      <c r="Q56" s="8">
+        <v>-10.6</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>17</v>
@@ -4163,39 +4163,39 @@
         <v>17</v>
       </c>
       <c r="H57" s="9">
-        <v>7.13</v>
-      </c>
-      <c r="I57" s="10">
-        <v>-2.81</v>
-      </c>
-      <c r="J57" s="10">
-        <v>-14.5</v>
+        <v>5.83</v>
+      </c>
+      <c r="I57" s="8">
+        <v>-18.3</v>
+      </c>
+      <c r="J57" s="8">
+        <v>-7.35</v>
       </c>
       <c r="K57" s="9">
-        <v>7.13</v>
-      </c>
-      <c r="L57" s="10">
-        <v>-14.5</v>
+        <v>12.95</v>
+      </c>
+      <c r="L57" s="8">
+        <v>-11.4</v>
       </c>
       <c r="M57" s="9">
-        <v>7.13</v>
-      </c>
-      <c r="N57" s="10">
-        <v>-2.81</v>
-      </c>
-      <c r="O57" s="10">
-        <v>-14.5</v>
+        <v>5.83</v>
+      </c>
+      <c r="N57" s="8">
+        <v>-18.3</v>
+      </c>
+      <c r="O57" s="8">
+        <v>-7.35</v>
       </c>
       <c r="P57" s="9">
-        <v>7.13</v>
-      </c>
-      <c r="Q57" s="10">
-        <v>-14.5</v>
+        <v>12.95</v>
+      </c>
+      <c r="Q57" s="8">
+        <v>-11.4</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>17</v>
@@ -4216,39 +4216,39 @@
         <v>17</v>
       </c>
       <c r="H58" s="9">
-        <v>7.34</v>
-      </c>
-      <c r="I58" s="10">
-        <v>-0.34</v>
-      </c>
-      <c r="J58" s="10">
-        <v>-0.7</v>
+        <v>7.13</v>
+      </c>
+      <c r="I58" s="8">
+        <v>-2.81</v>
+      </c>
+      <c r="J58" s="8">
+        <v>-14.5</v>
       </c>
       <c r="K58" s="9">
-        <v>93.35</v>
+        <v>7.13</v>
       </c>
       <c r="L58" s="8">
-        <v>8.2100000000000009</v>
+        <v>-14.5</v>
       </c>
       <c r="M58" s="9">
-        <v>7.34</v>
-      </c>
-      <c r="N58" s="10">
-        <v>-0.34</v>
-      </c>
-      <c r="O58" s="10">
-        <v>-0.7</v>
+        <v>7.13</v>
+      </c>
+      <c r="N58" s="8">
+        <v>-2.81</v>
+      </c>
+      <c r="O58" s="8">
+        <v>-14.5</v>
       </c>
       <c r="P58" s="9">
-        <v>93.35</v>
+        <v>7.13</v>
       </c>
       <c r="Q58" s="8">
-        <v>8.2100000000000009</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>17</v>
@@ -4269,39 +4269,39 @@
         <v>17</v>
       </c>
       <c r="H59" s="9">
-        <v>7.36</v>
-      </c>
-      <c r="I59" s="10">
-        <v>-7.9</v>
-      </c>
-      <c r="J59" s="10">
-        <v>-2.16</v>
+        <v>7.34</v>
+      </c>
+      <c r="I59" s="8">
+        <v>-0.34</v>
+      </c>
+      <c r="J59" s="8">
+        <v>-0.7</v>
       </c>
       <c r="K59" s="9">
-        <v>86.02</v>
-      </c>
-      <c r="L59" s="8">
-        <v>9.0399999999999991</v>
+        <v>93.35</v>
+      </c>
+      <c r="L59" s="10">
+        <v>8.2100000000000009</v>
       </c>
       <c r="M59" s="9">
-        <v>7.36</v>
-      </c>
-      <c r="N59" s="10">
-        <v>-7.9</v>
-      </c>
-      <c r="O59" s="10">
-        <v>-2.16</v>
+        <v>7.34</v>
+      </c>
+      <c r="N59" s="8">
+        <v>-0.34</v>
+      </c>
+      <c r="O59" s="8">
+        <v>-0.7</v>
       </c>
       <c r="P59" s="9">
-        <v>86.02</v>
-      </c>
-      <c r="Q59" s="8">
-        <v>9.0399999999999991</v>
+        <v>93.35</v>
+      </c>
+      <c r="Q59" s="10">
+        <v>8.2100000000000009</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>17</v>
@@ -4322,39 +4322,39 @@
         <v>17</v>
       </c>
       <c r="H60" s="9">
-        <v>7.99</v>
-      </c>
-      <c r="I60" s="10">
-        <v>-5.44</v>
+        <v>7.36</v>
+      </c>
+      <c r="I60" s="8">
+        <v>-7.9</v>
       </c>
       <c r="J60" s="8">
-        <v>9.4600000000000009</v>
+        <v>-2.16</v>
       </c>
       <c r="K60" s="9">
-        <v>78.650000000000006</v>
-      </c>
-      <c r="L60" s="8">
-        <v>10.199999999999999</v>
+        <v>86.02</v>
+      </c>
+      <c r="L60" s="10">
+        <v>9.0399999999999991</v>
       </c>
       <c r="M60" s="9">
-        <v>7.99</v>
-      </c>
-      <c r="N60" s="10">
-        <v>-5.44</v>
+        <v>7.36</v>
+      </c>
+      <c r="N60" s="8">
+        <v>-7.9</v>
       </c>
       <c r="O60" s="8">
-        <v>9.4600000000000009</v>
+        <v>-2.16</v>
       </c>
       <c r="P60" s="9">
-        <v>78.650000000000006</v>
-      </c>
-      <c r="Q60" s="8">
-        <v>10.199999999999999</v>
+        <v>86.02</v>
+      </c>
+      <c r="Q60" s="10">
+        <v>9.0399999999999991</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>17</v>
@@ -4375,39 +4375,39 @@
         <v>17</v>
       </c>
       <c r="H61" s="9">
-        <v>8.4499999999999993</v>
+        <v>7.99</v>
       </c>
       <c r="I61" s="8">
-        <v>2.85</v>
-      </c>
-      <c r="J61" s="8">
-        <v>9.32</v>
+        <v>-5.44</v>
+      </c>
+      <c r="J61" s="10">
+        <v>9.4600000000000009</v>
       </c>
       <c r="K61" s="9">
-        <v>70.66</v>
-      </c>
-      <c r="L61" s="8">
-        <v>10.3</v>
+        <v>78.650000000000006</v>
+      </c>
+      <c r="L61" s="10">
+        <v>10.199999999999999</v>
       </c>
       <c r="M61" s="9">
-        <v>8.4499999999999993</v>
+        <v>7.99</v>
       </c>
       <c r="N61" s="8">
-        <v>2.85</v>
-      </c>
-      <c r="O61" s="8">
-        <v>9.32</v>
+        <v>-5.44</v>
+      </c>
+      <c r="O61" s="10">
+        <v>9.4600000000000009</v>
       </c>
       <c r="P61" s="9">
-        <v>70.66</v>
-      </c>
-      <c r="Q61" s="8">
-        <v>10.3</v>
+        <v>78.650000000000006</v>
+      </c>
+      <c r="Q61" s="10">
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>17</v>
@@ -4428,39 +4428,39 @@
         <v>17</v>
       </c>
       <c r="H62" s="9">
-        <v>8.2200000000000006</v>
-      </c>
-      <c r="I62" s="8">
-        <v>0.32</v>
-      </c>
-      <c r="J62" s="8">
-        <v>6.44</v>
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="I62" s="10">
+        <v>2.85</v>
+      </c>
+      <c r="J62" s="10">
+        <v>9.32</v>
       </c>
       <c r="K62" s="9">
-        <v>62.21</v>
-      </c>
-      <c r="L62" s="8">
-        <v>10.4</v>
+        <v>70.66</v>
+      </c>
+      <c r="L62" s="10">
+        <v>10.3</v>
       </c>
       <c r="M62" s="9">
-        <v>8.2200000000000006</v>
-      </c>
-      <c r="N62" s="8">
-        <v>0.32</v>
-      </c>
-      <c r="O62" s="8">
-        <v>6.44</v>
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="N62" s="10">
+        <v>2.85</v>
+      </c>
+      <c r="O62" s="10">
+        <v>9.32</v>
       </c>
       <c r="P62" s="9">
-        <v>62.21</v>
-      </c>
-      <c r="Q62" s="8">
-        <v>10.4</v>
+        <v>70.66</v>
+      </c>
+      <c r="Q62" s="10">
+        <v>10.3</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>17</v>
@@ -4481,39 +4481,39 @@
         <v>17</v>
       </c>
       <c r="H63" s="9">
-        <v>8.19</v>
-      </c>
-      <c r="I63" s="8">
-        <v>0.22</v>
-      </c>
-      <c r="J63" s="8">
-        <v>9.42</v>
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="I63" s="10">
+        <v>0.32</v>
+      </c>
+      <c r="J63" s="10">
+        <v>6.44</v>
       </c>
       <c r="K63" s="9">
-        <v>53.99</v>
-      </c>
-      <c r="L63" s="8">
-        <v>11.1</v>
+        <v>62.21</v>
+      </c>
+      <c r="L63" s="10">
+        <v>10.4</v>
       </c>
       <c r="M63" s="9">
-        <v>8.19</v>
-      </c>
-      <c r="N63" s="8">
-        <v>0.22</v>
-      </c>
-      <c r="O63" s="8">
-        <v>9.42</v>
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="N63" s="10">
+        <v>0.32</v>
+      </c>
+      <c r="O63" s="10">
+        <v>6.44</v>
       </c>
       <c r="P63" s="9">
-        <v>53.99</v>
-      </c>
-      <c r="Q63" s="8">
-        <v>11.1</v>
+        <v>62.21</v>
+      </c>
+      <c r="Q63" s="10">
+        <v>10.4</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>17</v>
@@ -4534,39 +4534,39 @@
         <v>17</v>
       </c>
       <c r="H64" s="9">
-        <v>8.17</v>
-      </c>
-      <c r="I64" s="8">
-        <v>10.7</v>
-      </c>
-      <c r="J64" s="8">
-        <v>10.7</v>
+        <v>8.19</v>
+      </c>
+      <c r="I64" s="10">
+        <v>0.22</v>
+      </c>
+      <c r="J64" s="10">
+        <v>9.42</v>
       </c>
       <c r="K64" s="9">
-        <v>45.8</v>
-      </c>
-      <c r="L64" s="8">
-        <v>11.4</v>
+        <v>53.99</v>
+      </c>
+      <c r="L64" s="10">
+        <v>11.1</v>
       </c>
       <c r="M64" s="9">
-        <v>8.17</v>
-      </c>
-      <c r="N64" s="8">
-        <v>10.7</v>
-      </c>
-      <c r="O64" s="8">
-        <v>10.7</v>
+        <v>8.19</v>
+      </c>
+      <c r="N64" s="10">
+        <v>0.22</v>
+      </c>
+      <c r="O64" s="10">
+        <v>9.42</v>
       </c>
       <c r="P64" s="9">
-        <v>45.8</v>
-      </c>
-      <c r="Q64" s="8">
-        <v>11.4</v>
+        <v>53.99</v>
+      </c>
+      <c r="Q64" s="10">
+        <v>11.1</v>
       </c>
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>17</v>
@@ -4587,39 +4587,39 @@
         <v>17</v>
       </c>
       <c r="H65" s="9">
-        <v>7.38</v>
+        <v>8.17</v>
       </c>
       <c r="I65" s="10">
-        <v>-4.3099999999999996</v>
-      </c>
-      <c r="J65" s="8">
-        <v>0.11</v>
+        <v>10.7</v>
+      </c>
+      <c r="J65" s="10">
+        <v>10.7</v>
       </c>
       <c r="K65" s="9">
-        <v>37.619999999999997</v>
-      </c>
-      <c r="L65" s="8">
-        <v>11.6</v>
+        <v>45.8</v>
+      </c>
+      <c r="L65" s="10">
+        <v>11.4</v>
       </c>
       <c r="M65" s="9">
-        <v>7.38</v>
+        <v>8.17</v>
       </c>
       <c r="N65" s="10">
-        <v>-4.3099999999999996</v>
-      </c>
-      <c r="O65" s="8">
-        <v>0.11</v>
+        <v>10.7</v>
+      </c>
+      <c r="O65" s="10">
+        <v>10.7</v>
       </c>
       <c r="P65" s="9">
-        <v>37.619999999999997</v>
-      </c>
-      <c r="Q65" s="8">
-        <v>11.6</v>
+        <v>45.8</v>
+      </c>
+      <c r="Q65" s="10">
+        <v>11.4</v>
       </c>
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>17</v>
@@ -4640,39 +4640,39 @@
         <v>17</v>
       </c>
       <c r="H66" s="9">
-        <v>7.72</v>
-      </c>
-      <c r="I66" s="10">
-        <v>-2.17</v>
-      </c>
-      <c r="J66" s="8">
-        <v>5.99</v>
+        <v>7.38</v>
+      </c>
+      <c r="I66" s="8">
+        <v>-4.3099999999999996</v>
+      </c>
+      <c r="J66" s="10">
+        <v>0.11</v>
       </c>
       <c r="K66" s="9">
-        <v>30.24</v>
-      </c>
-      <c r="L66" s="8">
-        <v>14.8</v>
+        <v>37.619999999999997</v>
+      </c>
+      <c r="L66" s="10">
+        <v>11.6</v>
       </c>
       <c r="M66" s="9">
-        <v>7.72</v>
-      </c>
-      <c r="N66" s="10">
-        <v>-2.17</v>
-      </c>
-      <c r="O66" s="8">
-        <v>5.99</v>
+        <v>7.38</v>
+      </c>
+      <c r="N66" s="8">
+        <v>-4.3099999999999996</v>
+      </c>
+      <c r="O66" s="10">
+        <v>0.11</v>
       </c>
       <c r="P66" s="9">
-        <v>30.24</v>
-      </c>
-      <c r="Q66" s="8">
-        <v>14.8</v>
+        <v>37.619999999999997</v>
+      </c>
+      <c r="Q66" s="10">
+        <v>11.6</v>
       </c>
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>17</v>
@@ -4693,39 +4693,39 @@
         <v>17</v>
       </c>
       <c r="H67" s="9">
-        <v>7.89</v>
+        <v>7.72</v>
       </c>
       <c r="I67" s="8">
-        <v>25.5</v>
-      </c>
-      <c r="J67" s="8">
-        <v>23.6</v>
+        <v>-2.17</v>
+      </c>
+      <c r="J67" s="10">
+        <v>5.99</v>
       </c>
       <c r="K67" s="9">
-        <v>22.52</v>
-      </c>
-      <c r="L67" s="8">
-        <v>18.100000000000001</v>
+        <v>30.24</v>
+      </c>
+      <c r="L67" s="10">
+        <v>14.8</v>
       </c>
       <c r="M67" s="9">
-        <v>7.89</v>
+        <v>7.72</v>
       </c>
       <c r="N67" s="8">
-        <v>25.5</v>
-      </c>
-      <c r="O67" s="8">
-        <v>23.6</v>
+        <v>-2.17</v>
+      </c>
+      <c r="O67" s="10">
+        <v>5.99</v>
       </c>
       <c r="P67" s="9">
-        <v>22.52</v>
-      </c>
-      <c r="Q67" s="8">
-        <v>18.100000000000001</v>
+        <v>30.24</v>
+      </c>
+      <c r="Q67" s="10">
+        <v>14.8</v>
       </c>
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>17</v>
@@ -4746,39 +4746,39 @@
         <v>17</v>
       </c>
       <c r="H68" s="9">
-        <v>6.29</v>
+        <v>7.89</v>
       </c>
       <c r="I68" s="10">
-        <v>-24.6</v>
-      </c>
-      <c r="J68" s="8">
-        <v>18.399999999999999</v>
+        <v>25.5</v>
+      </c>
+      <c r="J68" s="10">
+        <v>23.6</v>
       </c>
       <c r="K68" s="9">
-        <v>14.63</v>
-      </c>
-      <c r="L68" s="8">
-        <v>15.3</v>
+        <v>22.52</v>
+      </c>
+      <c r="L68" s="10">
+        <v>18.100000000000001</v>
       </c>
       <c r="M68" s="9">
-        <v>6.29</v>
+        <v>7.89</v>
       </c>
       <c r="N68" s="10">
-        <v>-24.6</v>
-      </c>
-      <c r="O68" s="8">
-        <v>18.399999999999999</v>
+        <v>25.5</v>
+      </c>
+      <c r="O68" s="10">
+        <v>23.6</v>
       </c>
       <c r="P68" s="9">
-        <v>14.63</v>
-      </c>
-      <c r="Q68" s="8">
-        <v>15.3</v>
+        <v>22.52</v>
+      </c>
+      <c r="Q68" s="10">
+        <v>18.100000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42736</v>
+        <v>42767</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>17</v>
@@ -4799,39 +4799,39 @@
         <v>17</v>
       </c>
       <c r="H69" s="9">
-        <v>8.34</v>
+        <v>6.29</v>
       </c>
       <c r="I69" s="8">
-        <v>13.3</v>
-      </c>
-      <c r="J69" s="8">
-        <v>13.1</v>
+        <v>-24.6</v>
+      </c>
+      <c r="J69" s="10">
+        <v>18.399999999999999</v>
       </c>
       <c r="K69" s="9">
-        <v>8.34</v>
-      </c>
-      <c r="L69" s="8">
-        <v>13.1</v>
+        <v>14.63</v>
+      </c>
+      <c r="L69" s="10">
+        <v>15.3</v>
       </c>
       <c r="M69" s="9">
-        <v>8.34</v>
+        <v>6.29</v>
       </c>
       <c r="N69" s="8">
-        <v>13.3</v>
-      </c>
-      <c r="O69" s="8">
-        <v>13.1</v>
+        <v>-24.6</v>
+      </c>
+      <c r="O69" s="10">
+        <v>18.399999999999999</v>
       </c>
       <c r="P69" s="9">
-        <v>8.34</v>
-      </c>
-      <c r="Q69" s="8">
-        <v>13.1</v>
+        <v>14.63</v>
+      </c>
+      <c r="Q69" s="10">
+        <v>15.3</v>
       </c>
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42705</v>
+        <v>42736</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>17</v>
@@ -4852,39 +4852,39 @@
         <v>17</v>
       </c>
       <c r="H70" s="9">
-        <v>7.39</v>
+        <v>8.34</v>
       </c>
       <c r="I70" s="10">
-        <v>-1.81</v>
-      </c>
-      <c r="J70" s="8">
-        <v>8.91</v>
+        <v>13.3</v>
+      </c>
+      <c r="J70" s="10">
+        <v>13.1</v>
       </c>
       <c r="K70" s="9">
-        <v>86.27</v>
-      </c>
-      <c r="L70" s="8">
-        <v>18.2</v>
+        <v>8.34</v>
+      </c>
+      <c r="L70" s="10">
+        <v>13.1</v>
       </c>
       <c r="M70" s="9">
-        <v>7.39</v>
+        <v>8.34</v>
       </c>
       <c r="N70" s="10">
-        <v>-1.81</v>
-      </c>
-      <c r="O70" s="8">
-        <v>8.91</v>
+        <v>13.3</v>
+      </c>
+      <c r="O70" s="10">
+        <v>13.1</v>
       </c>
       <c r="P70" s="9">
-        <v>86.27</v>
-      </c>
-      <c r="Q70" s="8">
-        <v>18.2</v>
+        <v>8.34</v>
+      </c>
+      <c r="Q70" s="10">
+        <v>13.1</v>
       </c>
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42675</v>
+        <v>42705</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>17</v>
@@ -4905,39 +4905,39 @@
         <v>17</v>
       </c>
       <c r="H71" s="9">
-        <v>7.52</v>
+        <v>7.39</v>
       </c>
       <c r="I71" s="8">
-        <v>3.04</v>
-      </c>
-      <c r="J71" s="8">
-        <v>15.6</v>
+        <v>-1.81</v>
+      </c>
+      <c r="J71" s="10">
+        <v>8.91</v>
       </c>
       <c r="K71" s="9">
-        <v>78.88</v>
-      </c>
-      <c r="L71" s="8">
-        <v>19.2</v>
+        <v>86.27</v>
+      </c>
+      <c r="L71" s="10">
+        <v>18.2</v>
       </c>
       <c r="M71" s="9">
-        <v>7.52</v>
+        <v>7.39</v>
       </c>
       <c r="N71" s="8">
-        <v>3.04</v>
-      </c>
-      <c r="O71" s="8">
-        <v>15.6</v>
+        <v>-1.81</v>
+      </c>
+      <c r="O71" s="10">
+        <v>8.91</v>
       </c>
       <c r="P71" s="9">
-        <v>78.88</v>
-      </c>
-      <c r="Q71" s="8">
-        <v>19.2</v>
+        <v>86.27</v>
+      </c>
+      <c r="Q71" s="10">
+        <v>18.2</v>
       </c>
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>17</v>
@@ -4958,39 +4958,39 @@
         <v>17</v>
       </c>
       <c r="H72" s="9">
-        <v>7.3</v>
+        <v>7.52</v>
       </c>
       <c r="I72" s="10">
-        <v>-5.57</v>
-      </c>
-      <c r="J72" s="8">
-        <v>16</v>
+        <v>3.04</v>
+      </c>
+      <c r="J72" s="10">
+        <v>15.6</v>
       </c>
       <c r="K72" s="9">
-        <v>71.349999999999994</v>
-      </c>
-      <c r="L72" s="8">
-        <v>19.600000000000001</v>
+        <v>78.88</v>
+      </c>
+      <c r="L72" s="10">
+        <v>19.2</v>
       </c>
       <c r="M72" s="9">
-        <v>7.3</v>
+        <v>7.52</v>
       </c>
       <c r="N72" s="10">
-        <v>-5.57</v>
-      </c>
-      <c r="O72" s="8">
-        <v>16</v>
+        <v>3.04</v>
+      </c>
+      <c r="O72" s="10">
+        <v>15.6</v>
       </c>
       <c r="P72" s="9">
-        <v>71.349999999999994</v>
-      </c>
-      <c r="Q72" s="8">
-        <v>19.600000000000001</v>
+        <v>78.88</v>
+      </c>
+      <c r="Q72" s="10">
+        <v>19.2</v>
       </c>
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>17</v>
@@ -5011,39 +5011,39 @@
         <v>17</v>
       </c>
       <c r="H73" s="9">
-        <v>7.73</v>
+        <v>7.3</v>
       </c>
       <c r="I73" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="J73" s="8">
-        <v>29.1</v>
+        <v>-5.57</v>
+      </c>
+      <c r="J73" s="10">
+        <v>16</v>
       </c>
       <c r="K73" s="9">
-        <v>64.05</v>
-      </c>
-      <c r="L73" s="8">
-        <v>20</v>
+        <v>71.349999999999994</v>
+      </c>
+      <c r="L73" s="10">
+        <v>19.600000000000001</v>
       </c>
       <c r="M73" s="9">
-        <v>7.73</v>
+        <v>7.3</v>
       </c>
       <c r="N73" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="O73" s="8">
-        <v>29.1</v>
+        <v>-5.57</v>
+      </c>
+      <c r="O73" s="10">
+        <v>16</v>
       </c>
       <c r="P73" s="9">
-        <v>64.05</v>
-      </c>
-      <c r="Q73" s="8">
-        <v>20</v>
+        <v>71.349999999999994</v>
+      </c>
+      <c r="Q73" s="10">
+        <v>19.600000000000001</v>
       </c>
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>42583</v>
+        <v>42614</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>17</v>
@@ -5064,39 +5064,39 @@
         <v>17</v>
       </c>
       <c r="H74" s="9">
-        <v>7.72</v>
-      </c>
-      <c r="I74" s="8">
-        <v>3.12</v>
-      </c>
-      <c r="J74" s="8">
-        <v>29.4</v>
+        <v>7.73</v>
+      </c>
+      <c r="I74" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J74" s="10">
+        <v>29.1</v>
       </c>
       <c r="K74" s="9">
-        <v>56.32</v>
-      </c>
-      <c r="L74" s="8">
-        <v>18.8</v>
+        <v>64.05</v>
+      </c>
+      <c r="L74" s="10">
+        <v>20</v>
       </c>
       <c r="M74" s="9">
-        <v>7.72</v>
-      </c>
-      <c r="N74" s="8">
-        <v>3.12</v>
-      </c>
-      <c r="O74" s="8">
-        <v>29.4</v>
+        <v>7.73</v>
+      </c>
+      <c r="N74" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="O74" s="10">
+        <v>29.1</v>
       </c>
       <c r="P74" s="9">
-        <v>56.32</v>
-      </c>
-      <c r="Q74" s="8">
-        <v>18.8</v>
+        <v>64.05</v>
+      </c>
+      <c r="Q74" s="10">
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>42552</v>
+        <v>42583</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>17</v>
@@ -5117,39 +5117,39 @@
         <v>17</v>
       </c>
       <c r="H75" s="9">
-        <v>7.49</v>
-      </c>
-      <c r="I75" s="8">
-        <v>1.36</v>
-      </c>
-      <c r="J75" s="8">
-        <v>26.7</v>
+        <v>7.72</v>
+      </c>
+      <c r="I75" s="10">
+        <v>3.12</v>
+      </c>
+      <c r="J75" s="10">
+        <v>29.4</v>
       </c>
       <c r="K75" s="9">
-        <v>48.6</v>
-      </c>
-      <c r="L75" s="8">
-        <v>17.3</v>
+        <v>56.32</v>
+      </c>
+      <c r="L75" s="10">
+        <v>18.8</v>
       </c>
       <c r="M75" s="9">
-        <v>7.49</v>
-      </c>
-      <c r="N75" s="8">
-        <v>1.36</v>
-      </c>
-      <c r="O75" s="8">
-        <v>26.7</v>
+        <v>7.72</v>
+      </c>
+      <c r="N75" s="10">
+        <v>3.12</v>
+      </c>
+      <c r="O75" s="10">
+        <v>29.4</v>
       </c>
       <c r="P75" s="9">
-        <v>48.6</v>
-      </c>
-      <c r="Q75" s="8">
-        <v>17.3</v>
+        <v>56.32</v>
+      </c>
+      <c r="Q75" s="10">
+        <v>18.8</v>
       </c>
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>17</v>
@@ -5170,39 +5170,39 @@
         <v>17</v>
       </c>
       <c r="H76" s="9">
-        <v>7.39</v>
-      </c>
-      <c r="I76" s="8">
-        <v>0.13</v>
-      </c>
-      <c r="J76" s="8">
-        <v>28.9</v>
+        <v>7.49</v>
+      </c>
+      <c r="I76" s="10">
+        <v>1.36</v>
+      </c>
+      <c r="J76" s="10">
+        <v>26.7</v>
       </c>
       <c r="K76" s="9">
-        <v>41.11</v>
-      </c>
-      <c r="L76" s="8">
-        <v>15.7</v>
+        <v>48.6</v>
+      </c>
+      <c r="L76" s="10">
+        <v>17.3</v>
       </c>
       <c r="M76" s="9">
-        <v>7.39</v>
-      </c>
-      <c r="N76" s="8">
-        <v>0.13</v>
-      </c>
-      <c r="O76" s="8">
-        <v>28.9</v>
+        <v>7.49</v>
+      </c>
+      <c r="N76" s="10">
+        <v>1.36</v>
+      </c>
+      <c r="O76" s="10">
+        <v>26.7</v>
       </c>
       <c r="P76" s="9">
-        <v>41.11</v>
-      </c>
-      <c r="Q76" s="8">
-        <v>15.7</v>
+        <v>48.6</v>
+      </c>
+      <c r="Q76" s="10">
+        <v>17.3</v>
       </c>
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>42491</v>
+        <v>42522</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>17</v>
@@ -5223,39 +5223,39 @@
         <v>17</v>
       </c>
       <c r="H77" s="9">
-        <v>7.38</v>
-      </c>
-      <c r="I77" s="8">
-        <v>1.31</v>
-      </c>
-      <c r="J77" s="8">
-        <v>23.3</v>
+        <v>7.39</v>
+      </c>
+      <c r="I77" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="J77" s="10">
+        <v>28.9</v>
       </c>
       <c r="K77" s="9">
-        <v>33.72</v>
-      </c>
-      <c r="L77" s="8">
-        <v>13.2</v>
+        <v>41.11</v>
+      </c>
+      <c r="L77" s="10">
+        <v>15.7</v>
       </c>
       <c r="M77" s="9">
-        <v>7.38</v>
-      </c>
-      <c r="N77" s="8">
-        <v>1.31</v>
-      </c>
-      <c r="O77" s="8">
-        <v>23.3</v>
+        <v>7.39</v>
+      </c>
+      <c r="N77" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="O77" s="10">
+        <v>28.9</v>
       </c>
       <c r="P77" s="9">
-        <v>33.72</v>
-      </c>
-      <c r="Q77" s="8">
-        <v>13.2</v>
+        <v>41.11</v>
+      </c>
+      <c r="Q77" s="10">
+        <v>15.7</v>
       </c>
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>42461</v>
+        <v>42491</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>17</v>
@@ -5276,39 +5276,39 @@
         <v>17</v>
       </c>
       <c r="H78" s="9">
-        <v>7.28</v>
-      </c>
-      <c r="I78" s="8">
-        <v>14.1</v>
-      </c>
-      <c r="J78" s="8">
-        <v>28.6</v>
+        <v>7.38</v>
+      </c>
+      <c r="I78" s="10">
+        <v>1.31</v>
+      </c>
+      <c r="J78" s="10">
+        <v>23.3</v>
       </c>
       <c r="K78" s="9">
-        <v>26.35</v>
-      </c>
-      <c r="L78" s="8">
-        <v>10.6</v>
+        <v>33.72</v>
+      </c>
+      <c r="L78" s="10">
+        <v>13.2</v>
       </c>
       <c r="M78" s="9">
-        <v>7.28</v>
-      </c>
-      <c r="N78" s="8">
-        <v>14.1</v>
-      </c>
-      <c r="O78" s="8">
-        <v>28.6</v>
+        <v>7.38</v>
+      </c>
+      <c r="N78" s="10">
+        <v>1.31</v>
+      </c>
+      <c r="O78" s="10">
+        <v>23.3</v>
       </c>
       <c r="P78" s="9">
-        <v>26.35</v>
-      </c>
-      <c r="Q78" s="8">
-        <v>10.6</v>
+        <v>33.72</v>
+      </c>
+      <c r="Q78" s="10">
+        <v>13.2</v>
       </c>
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>42430</v>
+        <v>42461</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>17</v>
@@ -5329,39 +5329,39 @@
         <v>17</v>
       </c>
       <c r="H79" s="9">
-        <v>6.38</v>
-      </c>
-      <c r="I79" s="8">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="J79" s="8">
-        <v>5.82</v>
+        <v>7.28</v>
+      </c>
+      <c r="I79" s="10">
+        <v>14.1</v>
+      </c>
+      <c r="J79" s="10">
+        <v>28.6</v>
       </c>
       <c r="K79" s="9">
-        <v>19.07</v>
-      </c>
-      <c r="L79" s="8">
-        <v>5.03</v>
+        <v>26.35</v>
+      </c>
+      <c r="L79" s="10">
+        <v>10.6</v>
       </c>
       <c r="M79" s="9">
-        <v>6.38</v>
-      </c>
-      <c r="N79" s="8">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="O79" s="8">
-        <v>5.82</v>
+        <v>7.28</v>
+      </c>
+      <c r="N79" s="10">
+        <v>14.1</v>
+      </c>
+      <c r="O79" s="10">
+        <v>28.6</v>
       </c>
       <c r="P79" s="9">
-        <v>19.07</v>
-      </c>
-      <c r="Q79" s="8">
-        <v>5.03</v>
+        <v>26.35</v>
+      </c>
+      <c r="Q79" s="10">
+        <v>10.6</v>
       </c>
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>42401</v>
+        <v>42430</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>17</v>
@@ -5382,39 +5382,39 @@
         <v>17</v>
       </c>
       <c r="H80" s="9">
-        <v>5.31</v>
+        <v>6.38</v>
       </c>
       <c r="I80" s="10">
-        <v>-28</v>
-      </c>
-      <c r="J80" s="8">
-        <v>2.86</v>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="J80" s="10">
+        <v>5.82</v>
       </c>
       <c r="K80" s="9">
-        <v>12.69</v>
-      </c>
-      <c r="L80" s="8">
-        <v>4.6399999999999997</v>
+        <v>19.07</v>
+      </c>
+      <c r="L80" s="10">
+        <v>5.03</v>
       </c>
       <c r="M80" s="9">
-        <v>5.31</v>
+        <v>6.38</v>
       </c>
       <c r="N80" s="10">
-        <v>-28</v>
-      </c>
-      <c r="O80" s="8">
-        <v>2.86</v>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="O80" s="10">
+        <v>5.82</v>
       </c>
       <c r="P80" s="9">
-        <v>12.69</v>
-      </c>
-      <c r="Q80" s="8">
-        <v>4.6399999999999997</v>
+        <v>19.07</v>
+      </c>
+      <c r="Q80" s="10">
+        <v>5.03</v>
       </c>
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>42370</v>
+        <v>42401</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>17</v>
@@ -5435,39 +5435,39 @@
         <v>17</v>
       </c>
       <c r="H81" s="9">
-        <v>7.38</v>
+        <v>5.31</v>
       </c>
       <c r="I81" s="8">
-        <v>8.7100000000000009</v>
-      </c>
-      <c r="J81" s="8">
-        <v>5.97</v>
+        <v>-28</v>
+      </c>
+      <c r="J81" s="10">
+        <v>2.86</v>
       </c>
       <c r="K81" s="9">
-        <v>7.38</v>
-      </c>
-      <c r="L81" s="8">
-        <v>5.97</v>
+        <v>12.69</v>
+      </c>
+      <c r="L81" s="10">
+        <v>4.6399999999999997</v>
       </c>
       <c r="M81" s="9">
-        <v>7.38</v>
+        <v>5.31</v>
       </c>
       <c r="N81" s="8">
-        <v>8.7100000000000009</v>
-      </c>
-      <c r="O81" s="8">
-        <v>5.97</v>
+        <v>-28</v>
+      </c>
+      <c r="O81" s="10">
+        <v>2.86</v>
       </c>
       <c r="P81" s="9">
-        <v>7.38</v>
-      </c>
-      <c r="Q81" s="8">
-        <v>5.97</v>
+        <v>12.69</v>
+      </c>
+      <c r="Q81" s="10">
+        <v>4.6399999999999997</v>
       </c>
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>42339</v>
+        <v>42370</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>17</v>
@@ -5488,39 +5488,39 @@
         <v>17</v>
       </c>
       <c r="H82" s="9">
-        <v>6.78</v>
-      </c>
-      <c r="I82" s="8">
-        <v>4.1900000000000004</v>
+        <v>7.38</v>
+      </c>
+      <c r="I82" s="10">
+        <v>8.7100000000000009</v>
       </c>
       <c r="J82" s="10">
-        <v>-0.84</v>
+        <v>5.97</v>
       </c>
       <c r="K82" s="9">
-        <v>72.98</v>
+        <v>7.38</v>
       </c>
       <c r="L82" s="10">
-        <v>-9.82</v>
+        <v>5.97</v>
       </c>
       <c r="M82" s="9">
-        <v>6.78</v>
-      </c>
-      <c r="N82" s="8">
-        <v>4.1900000000000004</v>
+        <v>7.38</v>
+      </c>
+      <c r="N82" s="10">
+        <v>8.7100000000000009</v>
       </c>
       <c r="O82" s="10">
-        <v>-0.84</v>
+        <v>5.97</v>
       </c>
       <c r="P82" s="9">
-        <v>72.98</v>
+        <v>7.38</v>
       </c>
       <c r="Q82" s="10">
-        <v>-9.82</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>42309</v>
+        <v>42339</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>17</v>
@@ -5541,39 +5541,39 @@
         <v>17</v>
       </c>
       <c r="H83" s="9">
-        <v>6.51</v>
-      </c>
-      <c r="I83" s="8">
-        <v>3.47</v>
-      </c>
-      <c r="J83" s="10">
-        <v>-8.01</v>
+        <v>6.78</v>
+      </c>
+      <c r="I83" s="10">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="J83" s="8">
+        <v>-0.84</v>
       </c>
       <c r="K83" s="9">
-        <v>66.19</v>
-      </c>
-      <c r="L83" s="10">
-        <v>-10.6</v>
+        <v>72.98</v>
+      </c>
+      <c r="L83" s="8">
+        <v>-9.82</v>
       </c>
       <c r="M83" s="9">
-        <v>6.51</v>
-      </c>
-      <c r="N83" s="8">
-        <v>3.47</v>
-      </c>
-      <c r="O83" s="10">
-        <v>-8.01</v>
+        <v>6.78</v>
+      </c>
+      <c r="N83" s="10">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="O83" s="8">
+        <v>-0.84</v>
       </c>
       <c r="P83" s="9">
-        <v>66.19</v>
-      </c>
-      <c r="Q83" s="10">
-        <v>-10.6</v>
+        <v>72.98</v>
+      </c>
+      <c r="Q83" s="8">
+        <v>-9.82</v>
       </c>
     </row>
     <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>42278</v>
+        <v>42309</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>17</v>
@@ -5594,39 +5594,39 @@
         <v>17</v>
       </c>
       <c r="H84" s="9">
-        <v>6.29</v>
-      </c>
-      <c r="I84" s="8">
-        <v>5.0599999999999996</v>
-      </c>
-      <c r="J84" s="10">
-        <v>-7.17</v>
+        <v>6.51</v>
+      </c>
+      <c r="I84" s="10">
+        <v>3.47</v>
+      </c>
+      <c r="J84" s="8">
+        <v>-8.01</v>
       </c>
       <c r="K84" s="9">
-        <v>59.68</v>
-      </c>
-      <c r="L84" s="10">
-        <v>-10.9</v>
+        <v>66.19</v>
+      </c>
+      <c r="L84" s="8">
+        <v>-10.6</v>
       </c>
       <c r="M84" s="9">
-        <v>6.29</v>
-      </c>
-      <c r="N84" s="8">
-        <v>5.0599999999999996</v>
-      </c>
-      <c r="O84" s="10">
-        <v>-7.17</v>
+        <v>6.51</v>
+      </c>
+      <c r="N84" s="10">
+        <v>3.47</v>
+      </c>
+      <c r="O84" s="8">
+        <v>-8.01</v>
       </c>
       <c r="P84" s="9">
-        <v>59.68</v>
-      </c>
-      <c r="Q84" s="10">
-        <v>-10.9</v>
+        <v>66.19</v>
+      </c>
+      <c r="Q84" s="8">
+        <v>-10.6</v>
       </c>
     </row>
     <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>42248</v>
+        <v>42278</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>17</v>
@@ -5647,39 +5647,39 @@
         <v>17</v>
       </c>
       <c r="H85" s="9">
-        <v>5.99</v>
-      </c>
-      <c r="I85" s="8">
-        <v>0.35</v>
-      </c>
-      <c r="J85" s="10">
-        <v>-11.6</v>
+        <v>6.29</v>
+      </c>
+      <c r="I85" s="10">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="J85" s="8">
+        <v>-7.17</v>
       </c>
       <c r="K85" s="9">
-        <v>53.39</v>
-      </c>
-      <c r="L85" s="10">
-        <v>-11.4</v>
+        <v>59.68</v>
+      </c>
+      <c r="L85" s="8">
+        <v>-10.9</v>
       </c>
       <c r="M85" s="9">
-        <v>5.99</v>
-      </c>
-      <c r="N85" s="8">
-        <v>0.35</v>
-      </c>
-      <c r="O85" s="10">
-        <v>-11.6</v>
+        <v>6.29</v>
+      </c>
+      <c r="N85" s="10">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="O85" s="8">
+        <v>-7.17</v>
       </c>
       <c r="P85" s="9">
-        <v>53.39</v>
-      </c>
-      <c r="Q85" s="10">
-        <v>-11.4</v>
+        <v>59.68</v>
+      </c>
+      <c r="Q85" s="8">
+        <v>-10.9</v>
       </c>
     </row>
     <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>42217</v>
+        <v>42248</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>17</v>
@@ -5700,39 +5700,39 @@
         <v>17</v>
       </c>
       <c r="H86" s="9">
-        <v>5.97</v>
-      </c>
-      <c r="I86" s="8">
-        <v>0.95</v>
-      </c>
-      <c r="J86" s="10">
-        <v>-8.73</v>
+        <v>5.99</v>
+      </c>
+      <c r="I86" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="J86" s="8">
+        <v>-11.6</v>
       </c>
       <c r="K86" s="9">
-        <v>47.4</v>
-      </c>
-      <c r="L86" s="10">
-        <v>-11.3</v>
+        <v>53.39</v>
+      </c>
+      <c r="L86" s="8">
+        <v>-11.4</v>
       </c>
       <c r="M86" s="9">
-        <v>5.97</v>
-      </c>
-      <c r="N86" s="8">
-        <v>0.95</v>
-      </c>
-      <c r="O86" s="10">
-        <v>-8.73</v>
+        <v>5.99</v>
+      </c>
+      <c r="N86" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="O86" s="8">
+        <v>-11.6</v>
       </c>
       <c r="P86" s="9">
-        <v>47.4</v>
-      </c>
-      <c r="Q86" s="10">
-        <v>-11.3</v>
+        <v>53.39</v>
+      </c>
+      <c r="Q86" s="8">
+        <v>-11.4</v>
       </c>
     </row>
     <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>42186</v>
+        <v>42217</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>17</v>
@@ -5753,39 +5753,39 @@
         <v>17</v>
       </c>
       <c r="H87" s="9">
-        <v>5.91</v>
-      </c>
-      <c r="I87" s="8">
-        <v>3.14</v>
-      </c>
-      <c r="J87" s="10">
-        <v>-5.6</v>
+        <v>5.97</v>
+      </c>
+      <c r="I87" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="J87" s="8">
+        <v>-8.73</v>
       </c>
       <c r="K87" s="9">
-        <v>41.44</v>
-      </c>
-      <c r="L87" s="10">
-        <v>-11.7</v>
+        <v>47.4</v>
+      </c>
+      <c r="L87" s="8">
+        <v>-11.3</v>
       </c>
       <c r="M87" s="9">
-        <v>5.91</v>
-      </c>
-      <c r="N87" s="8">
-        <v>3.14</v>
-      </c>
-      <c r="O87" s="10">
-        <v>-5.6</v>
+        <v>5.97</v>
+      </c>
+      <c r="N87" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="O87" s="8">
+        <v>-8.73</v>
       </c>
       <c r="P87" s="9">
-        <v>41.44</v>
-      </c>
-      <c r="Q87" s="10">
-        <v>-11.7</v>
+        <v>47.4</v>
+      </c>
+      <c r="Q87" s="8">
+        <v>-11.3</v>
       </c>
     </row>
     <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>42156</v>
+        <v>42186</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>17</v>
@@ -5806,39 +5806,39 @@
         <v>17</v>
       </c>
       <c r="H88" s="9">
-        <v>5.73</v>
+        <v>5.91</v>
       </c>
       <c r="I88" s="10">
-        <v>-4.18</v>
-      </c>
-      <c r="J88" s="10">
-        <v>-1.42</v>
+        <v>3.14</v>
+      </c>
+      <c r="J88" s="8">
+        <v>-5.6</v>
       </c>
       <c r="K88" s="9">
-        <v>35.53</v>
-      </c>
-      <c r="L88" s="10">
-        <v>-12.6</v>
+        <v>41.44</v>
+      </c>
+      <c r="L88" s="8">
+        <v>-11.7</v>
       </c>
       <c r="M88" s="9">
-        <v>5.73</v>
+        <v>5.91</v>
       </c>
       <c r="N88" s="10">
-        <v>-4.18</v>
-      </c>
-      <c r="O88" s="10">
-        <v>-1.42</v>
+        <v>3.14</v>
+      </c>
+      <c r="O88" s="8">
+        <v>-5.6</v>
       </c>
       <c r="P88" s="9">
-        <v>35.53</v>
-      </c>
-      <c r="Q88" s="10">
-        <v>-12.6</v>
+        <v>41.44</v>
+      </c>
+      <c r="Q88" s="8">
+        <v>-11.7</v>
       </c>
     </row>
     <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
-        <v>42125</v>
+        <v>42156</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>17</v>
@@ -5859,39 +5859,39 @@
         <v>17</v>
       </c>
       <c r="H89" s="9">
-        <v>5.98</v>
+        <v>5.73</v>
       </c>
       <c r="I89" s="8">
-        <v>5.62</v>
-      </c>
-      <c r="J89" s="10">
-        <v>-10</v>
+        <v>-4.18</v>
+      </c>
+      <c r="J89" s="8">
+        <v>-1.42</v>
       </c>
       <c r="K89" s="9">
-        <v>29.8</v>
-      </c>
-      <c r="L89" s="10">
-        <v>-14.5</v>
+        <v>35.53</v>
+      </c>
+      <c r="L89" s="8">
+        <v>-12.6</v>
       </c>
       <c r="M89" s="9">
-        <v>5.98</v>
+        <v>5.73</v>
       </c>
       <c r="N89" s="8">
-        <v>5.62</v>
-      </c>
-      <c r="O89" s="10">
-        <v>-10</v>
+        <v>-4.18</v>
+      </c>
+      <c r="O89" s="8">
+        <v>-1.42</v>
       </c>
       <c r="P89" s="9">
-        <v>29.8</v>
-      </c>
-      <c r="Q89" s="10">
-        <v>-14.5</v>
+        <v>35.53</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>-12.6</v>
       </c>
     </row>
     <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
-        <v>42095</v>
+        <v>42125</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>17</v>
@@ -5912,39 +5912,39 @@
         <v>17</v>
       </c>
       <c r="H90" s="9">
-        <v>5.66</v>
+        <v>5.98</v>
       </c>
       <c r="I90" s="10">
-        <v>-6.09</v>
-      </c>
-      <c r="J90" s="10">
-        <v>-21.8</v>
+        <v>5.62</v>
+      </c>
+      <c r="J90" s="8">
+        <v>-10</v>
       </c>
       <c r="K90" s="9">
-        <v>23.81</v>
-      </c>
-      <c r="L90" s="10">
-        <v>-15.6</v>
+        <v>29.8</v>
+      </c>
+      <c r="L90" s="8">
+        <v>-14.5</v>
       </c>
       <c r="M90" s="9">
-        <v>5.66</v>
+        <v>5.98</v>
       </c>
       <c r="N90" s="10">
-        <v>-6.09</v>
-      </c>
-      <c r="O90" s="10">
-        <v>-21.8</v>
+        <v>5.62</v>
+      </c>
+      <c r="O90" s="8">
+        <v>-10</v>
       </c>
       <c r="P90" s="9">
-        <v>23.81</v>
-      </c>
-      <c r="Q90" s="10">
-        <v>-15.6</v>
+        <v>29.8</v>
+      </c>
+      <c r="Q90" s="8">
+        <v>-14.5</v>
       </c>
     </row>
     <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
-        <v>42064</v>
+        <v>42095</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>17</v>
@@ -5965,39 +5965,39 @@
         <v>17</v>
       </c>
       <c r="H91" s="9">
-        <v>6.03</v>
+        <v>5.66</v>
       </c>
       <c r="I91" s="8">
-        <v>16.8</v>
-      </c>
-      <c r="J91" s="10">
-        <v>-16.7</v>
+        <v>-6.09</v>
+      </c>
+      <c r="J91" s="8">
+        <v>-21.8</v>
       </c>
       <c r="K91" s="9">
-        <v>18.149999999999999</v>
-      </c>
-      <c r="L91" s="10">
-        <v>-13.5</v>
+        <v>23.81</v>
+      </c>
+      <c r="L91" s="8">
+        <v>-15.6</v>
       </c>
       <c r="M91" s="9">
-        <v>6.03</v>
+        <v>5.66</v>
       </c>
       <c r="N91" s="8">
-        <v>16.8</v>
-      </c>
-      <c r="O91" s="10">
-        <v>-16.7</v>
+        <v>-6.09</v>
+      </c>
+      <c r="O91" s="8">
+        <v>-21.8</v>
       </c>
       <c r="P91" s="9">
-        <v>18.149999999999999</v>
-      </c>
-      <c r="Q91" s="10">
-        <v>-13.5</v>
+        <v>23.81</v>
+      </c>
+      <c r="Q91" s="8">
+        <v>-15.6</v>
       </c>
     </row>
     <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
-        <v>42036</v>
+        <v>42064</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>17</v>
@@ -6018,39 +6018,39 @@
         <v>17</v>
       </c>
       <c r="H92" s="9">
-        <v>5.16</v>
+        <v>6.03</v>
       </c>
       <c r="I92" s="10">
-        <v>-25.8</v>
-      </c>
-      <c r="J92" s="10">
-        <v>-14.7</v>
+        <v>16.8</v>
+      </c>
+      <c r="J92" s="8">
+        <v>-16.7</v>
       </c>
       <c r="K92" s="9">
-        <v>12.12</v>
-      </c>
-      <c r="L92" s="10">
-        <v>-11.8</v>
+        <v>18.149999999999999</v>
+      </c>
+      <c r="L92" s="8">
+        <v>-13.5</v>
       </c>
       <c r="M92" s="9">
-        <v>5.16</v>
+        <v>6.03</v>
       </c>
       <c r="N92" s="10">
-        <v>-25.8</v>
-      </c>
-      <c r="O92" s="10">
-        <v>-14.7</v>
+        <v>16.8</v>
+      </c>
+      <c r="O92" s="8">
+        <v>-16.7</v>
       </c>
       <c r="P92" s="9">
-        <v>12.12</v>
-      </c>
-      <c r="Q92" s="10">
-        <v>-11.8</v>
+        <v>18.149999999999999</v>
+      </c>
+      <c r="Q92" s="8">
+        <v>-13.5</v>
       </c>
     </row>
     <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
-        <v>42005</v>
+        <v>42036</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>17</v>
@@ -6071,39 +6071,39 @@
         <v>17</v>
       </c>
       <c r="H93" s="9">
-        <v>6.96</v>
+        <v>5.16</v>
       </c>
       <c r="I93" s="8">
-        <v>1.72</v>
-      </c>
-      <c r="J93" s="10">
-        <v>-9.56</v>
+        <v>-25.8</v>
+      </c>
+      <c r="J93" s="8">
+        <v>-14.7</v>
       </c>
       <c r="K93" s="9">
-        <v>6.96</v>
-      </c>
-      <c r="L93" s="10">
-        <v>-9.56</v>
+        <v>12.12</v>
+      </c>
+      <c r="L93" s="8">
+        <v>-11.8</v>
       </c>
       <c r="M93" s="9">
-        <v>6.96</v>
+        <v>5.16</v>
       </c>
       <c r="N93" s="8">
-        <v>1.72</v>
-      </c>
-      <c r="O93" s="10">
-        <v>-9.56</v>
+        <v>-25.8</v>
+      </c>
+      <c r="O93" s="8">
+        <v>-14.7</v>
       </c>
       <c r="P93" s="9">
-        <v>6.96</v>
-      </c>
-      <c r="Q93" s="10">
-        <v>-9.56</v>
+        <v>12.12</v>
+      </c>
+      <c r="Q93" s="8">
+        <v>-11.8</v>
       </c>
     </row>
     <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
-        <v>41974</v>
+        <v>42005</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>17</v>
@@ -6124,39 +6124,39 @@
         <v>17</v>
       </c>
       <c r="H94" s="9">
-        <v>6.84</v>
+        <v>6.96</v>
       </c>
       <c r="I94" s="10">
-        <v>-3.34</v>
-      </c>
-      <c r="J94" s="10">
-        <v>-0.77</v>
+        <v>1.72</v>
+      </c>
+      <c r="J94" s="8">
+        <v>-9.56</v>
       </c>
       <c r="K94" s="9">
-        <v>80.930000000000007</v>
-      </c>
-      <c r="L94" s="10">
-        <v>-25.8</v>
+        <v>6.96</v>
+      </c>
+      <c r="L94" s="8">
+        <v>-9.56</v>
       </c>
       <c r="M94" s="9">
-        <v>6.84</v>
+        <v>6.96</v>
       </c>
       <c r="N94" s="10">
-        <v>-3.34</v>
-      </c>
-      <c r="O94" s="10">
-        <v>-0.77</v>
+        <v>1.72</v>
+      </c>
+      <c r="O94" s="8">
+        <v>-9.56</v>
       </c>
       <c r="P94" s="9">
-        <v>80.930000000000007</v>
-      </c>
-      <c r="Q94" s="10">
-        <v>-25.8</v>
+        <v>6.96</v>
+      </c>
+      <c r="Q94" s="8">
+        <v>-9.56</v>
       </c>
     </row>
     <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
-        <v>41944</v>
+        <v>41974</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>17</v>
@@ -6177,39 +6177,39 @@
         <v>17</v>
       </c>
       <c r="H95" s="9">
-        <v>7.08</v>
+        <v>6.84</v>
       </c>
       <c r="I95" s="8">
-        <v>4.42</v>
-      </c>
-      <c r="J95" s="10">
-        <v>-12</v>
+        <v>-3.34</v>
+      </c>
+      <c r="J95" s="8">
+        <v>-0.77</v>
       </c>
       <c r="K95" s="9">
-        <v>74.09</v>
-      </c>
-      <c r="L95" s="10">
-        <v>-27.4</v>
+        <v>80.930000000000007</v>
+      </c>
+      <c r="L95" s="8">
+        <v>-25.8</v>
       </c>
       <c r="M95" s="9">
-        <v>7.08</v>
+        <v>6.84</v>
       </c>
       <c r="N95" s="8">
-        <v>4.42</v>
-      </c>
-      <c r="O95" s="10">
-        <v>-12</v>
+        <v>-3.34</v>
+      </c>
+      <c r="O95" s="8">
+        <v>-0.77</v>
       </c>
       <c r="P95" s="9">
-        <v>74.09</v>
-      </c>
-      <c r="Q95" s="10">
-        <v>-27.4</v>
+        <v>80.930000000000007</v>
+      </c>
+      <c r="Q95" s="8">
+        <v>-25.8</v>
       </c>
     </row>
     <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
-        <v>41913</v>
+        <v>41944</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>17</v>
@@ -6230,39 +6230,39 @@
         <v>17</v>
       </c>
       <c r="H96" s="9">
-        <v>6.78</v>
-      </c>
-      <c r="I96" s="8">
-        <v>0.09</v>
-      </c>
-      <c r="J96" s="10">
-        <v>-13.9</v>
+        <v>7.08</v>
+      </c>
+      <c r="I96" s="10">
+        <v>4.42</v>
+      </c>
+      <c r="J96" s="8">
+        <v>-12</v>
       </c>
       <c r="K96" s="9">
-        <v>67.010000000000005</v>
-      </c>
-      <c r="L96" s="10">
-        <v>-28.8</v>
+        <v>74.09</v>
+      </c>
+      <c r="L96" s="8">
+        <v>-27.4</v>
       </c>
       <c r="M96" s="9">
-        <v>6.78</v>
-      </c>
-      <c r="N96" s="8">
-        <v>0.09</v>
-      </c>
-      <c r="O96" s="10">
-        <v>-13.9</v>
+        <v>7.08</v>
+      </c>
+      <c r="N96" s="10">
+        <v>4.42</v>
+      </c>
+      <c r="O96" s="8">
+        <v>-12</v>
       </c>
       <c r="P96" s="9">
-        <v>67.010000000000005</v>
-      </c>
-      <c r="Q96" s="10">
-        <v>-28.8</v>
+        <v>74.09</v>
+      </c>
+      <c r="Q96" s="8">
+        <v>-27.4</v>
       </c>
     </row>
     <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
-        <v>41883</v>
+        <v>41913</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>17</v>
@@ -6283,39 +6283,39 @@
         <v>17</v>
       </c>
       <c r="H97" s="9">
-        <v>6.77</v>
-      </c>
-      <c r="I97" s="8">
-        <v>3.57</v>
-      </c>
-      <c r="J97" s="10">
-        <v>-23.7</v>
+        <v>6.78</v>
+      </c>
+      <c r="I97" s="10">
+        <v>0.09</v>
+      </c>
+      <c r="J97" s="8">
+        <v>-13.9</v>
       </c>
       <c r="K97" s="9">
-        <v>60.23</v>
-      </c>
-      <c r="L97" s="10">
-        <v>-30.1</v>
+        <v>67.010000000000005</v>
+      </c>
+      <c r="L97" s="8">
+        <v>-28.8</v>
       </c>
       <c r="M97" s="9">
-        <v>6.77</v>
-      </c>
-      <c r="N97" s="8">
-        <v>3.57</v>
-      </c>
-      <c r="O97" s="10">
-        <v>-23.7</v>
+        <v>6.78</v>
+      </c>
+      <c r="N97" s="10">
+        <v>0.09</v>
+      </c>
+      <c r="O97" s="8">
+        <v>-13.9</v>
       </c>
       <c r="P97" s="9">
-        <v>60.23</v>
-      </c>
-      <c r="Q97" s="10">
-        <v>-30.1</v>
+        <v>67.010000000000005</v>
+      </c>
+      <c r="Q97" s="8">
+        <v>-28.8</v>
       </c>
     </row>
     <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
-        <v>41852</v>
+        <v>41883</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>17</v>
@@ -6336,39 +6336,39 @@
         <v>17</v>
       </c>
       <c r="H98" s="9">
-        <v>6.54</v>
-      </c>
-      <c r="I98" s="8">
-        <v>4.41</v>
-      </c>
-      <c r="J98" s="10">
-        <v>-35.9</v>
+        <v>6.77</v>
+      </c>
+      <c r="I98" s="10">
+        <v>3.57</v>
+      </c>
+      <c r="J98" s="8">
+        <v>-23.7</v>
       </c>
       <c r="K98" s="9">
-        <v>53.46</v>
-      </c>
-      <c r="L98" s="10">
-        <v>-30.8</v>
+        <v>60.23</v>
+      </c>
+      <c r="L98" s="8">
+        <v>-30.1</v>
       </c>
       <c r="M98" s="9">
-        <v>6.54</v>
-      </c>
-      <c r="N98" s="8">
-        <v>4.41</v>
-      </c>
-      <c r="O98" s="10">
-        <v>-35.9</v>
+        <v>6.77</v>
+      </c>
+      <c r="N98" s="10">
+        <v>3.57</v>
+      </c>
+      <c r="O98" s="8">
+        <v>-23.7</v>
       </c>
       <c r="P98" s="9">
-        <v>53.46</v>
-      </c>
-      <c r="Q98" s="10">
-        <v>-30.8</v>
+        <v>60.23</v>
+      </c>
+      <c r="Q98" s="8">
+        <v>-30.1</v>
       </c>
     </row>
     <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
-        <v>41821</v>
+        <v>41852</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>17</v>
@@ -6389,39 +6389,39 @@
         <v>17</v>
       </c>
       <c r="H99" s="9">
-        <v>6.26</v>
-      </c>
-      <c r="I99" s="8">
-        <v>7.7</v>
-      </c>
-      <c r="J99" s="10">
-        <v>-35.5</v>
+        <v>6.54</v>
+      </c>
+      <c r="I99" s="10">
+        <v>4.41</v>
+      </c>
+      <c r="J99" s="8">
+        <v>-35.9</v>
       </c>
       <c r="K99" s="9">
-        <v>46.92</v>
-      </c>
-      <c r="L99" s="10">
-        <v>-30.1</v>
+        <v>53.46</v>
+      </c>
+      <c r="L99" s="8">
+        <v>-30.8</v>
       </c>
       <c r="M99" s="9">
-        <v>6.26</v>
-      </c>
-      <c r="N99" s="8">
-        <v>7.7</v>
-      </c>
-      <c r="O99" s="10">
-        <v>-35.5</v>
+        <v>6.54</v>
+      </c>
+      <c r="N99" s="10">
+        <v>4.41</v>
+      </c>
+      <c r="O99" s="8">
+        <v>-35.9</v>
       </c>
       <c r="P99" s="9">
-        <v>46.92</v>
-      </c>
-      <c r="Q99" s="10">
-        <v>-30.1</v>
+        <v>53.46</v>
+      </c>
+      <c r="Q99" s="8">
+        <v>-30.8</v>
       </c>
     </row>
     <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
-        <v>41791</v>
+        <v>41821</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>17</v>
@@ -6442,39 +6442,39 @@
         <v>17</v>
       </c>
       <c r="H100" s="9">
-        <v>5.81</v>
+        <v>6.26</v>
       </c>
       <c r="I100" s="10">
-        <v>-12.1</v>
-      </c>
-      <c r="J100" s="10">
-        <v>-39.1</v>
+        <v>7.7</v>
+      </c>
+      <c r="J100" s="8">
+        <v>-35.5</v>
       </c>
       <c r="K100" s="9">
-        <v>40.659999999999997</v>
-      </c>
-      <c r="L100" s="10">
-        <v>-29.2</v>
+        <v>46.92</v>
+      </c>
+      <c r="L100" s="8">
+        <v>-30.1</v>
       </c>
       <c r="M100" s="9">
-        <v>5.81</v>
+        <v>6.26</v>
       </c>
       <c r="N100" s="10">
-        <v>-12.1</v>
-      </c>
-      <c r="O100" s="10">
-        <v>-39.1</v>
+        <v>7.7</v>
+      </c>
+      <c r="O100" s="8">
+        <v>-35.5</v>
       </c>
       <c r="P100" s="9">
-        <v>40.659999999999997</v>
-      </c>
-      <c r="Q100" s="10">
-        <v>-29.2</v>
+        <v>46.92</v>
+      </c>
+      <c r="Q100" s="8">
+        <v>-30.1</v>
       </c>
     </row>
     <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
-        <v>41760</v>
+        <v>41791</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>17</v>
@@ -6495,39 +6495,39 @@
         <v>17</v>
       </c>
       <c r="H101" s="9">
-        <v>6.65</v>
-      </c>
-      <c r="I101" s="10">
-        <v>-8.1999999999999993</v>
-      </c>
-      <c r="J101" s="10">
-        <v>-30.5</v>
+        <v>5.81</v>
+      </c>
+      <c r="I101" s="8">
+        <v>-12.1</v>
+      </c>
+      <c r="J101" s="8">
+        <v>-39.1</v>
       </c>
       <c r="K101" s="9">
-        <v>34.85</v>
-      </c>
-      <c r="L101" s="10">
-        <v>-27.2</v>
+        <v>40.659999999999997</v>
+      </c>
+      <c r="L101" s="8">
+        <v>-29.2</v>
       </c>
       <c r="M101" s="9">
-        <v>6.65</v>
-      </c>
-      <c r="N101" s="10">
-        <v>-8.1999999999999993</v>
-      </c>
-      <c r="O101" s="10">
-        <v>-30.5</v>
+        <v>5.81</v>
+      </c>
+      <c r="N101" s="8">
+        <v>-12.1</v>
+      </c>
+      <c r="O101" s="8">
+        <v>-39.1</v>
       </c>
       <c r="P101" s="9">
-        <v>34.85</v>
-      </c>
-      <c r="Q101" s="10">
-        <v>-27.2</v>
+        <v>40.659999999999997</v>
+      </c>
+      <c r="Q101" s="8">
+        <v>-29.2</v>
       </c>
     </row>
     <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
-        <v>41730</v>
+        <v>41760</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>17</v>
@@ -6548,39 +6548,39 @@
         <v>17</v>
       </c>
       <c r="H102" s="9">
-        <v>7.24</v>
-      </c>
-      <c r="I102" s="9">
-        <v>0</v>
-      </c>
-      <c r="J102" s="10">
-        <v>-29.3</v>
+        <v>6.65</v>
+      </c>
+      <c r="I102" s="8">
+        <v>-8.1999999999999993</v>
+      </c>
+      <c r="J102" s="8">
+        <v>-30.5</v>
       </c>
       <c r="K102" s="9">
-        <v>28.23</v>
-      </c>
-      <c r="L102" s="10">
-        <v>-26.3</v>
+        <v>34.85</v>
+      </c>
+      <c r="L102" s="8">
+        <v>-27.2</v>
       </c>
       <c r="M102" s="9">
-        <v>7.24</v>
-      </c>
-      <c r="N102" s="9">
-        <v>0</v>
-      </c>
-      <c r="O102" s="10">
-        <v>-29.3</v>
+        <v>6.65</v>
+      </c>
+      <c r="N102" s="8">
+        <v>-8.1999999999999993</v>
+      </c>
+      <c r="O102" s="8">
+        <v>-30.5</v>
       </c>
       <c r="P102" s="9">
-        <v>28.23</v>
-      </c>
-      <c r="Q102" s="10">
-        <v>-26.3</v>
+        <v>34.85</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>-27.2</v>
       </c>
     </row>
     <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
-        <v>41699</v>
+        <v>41730</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>17</v>
@@ -6603,37 +6603,37 @@
       <c r="H103" s="9">
         <v>7.24</v>
       </c>
-      <c r="I103" s="8">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="J103" s="10">
-        <v>-27.7</v>
+      <c r="I103" s="9">
+        <v>0</v>
+      </c>
+      <c r="J103" s="8">
+        <v>-29.3</v>
       </c>
       <c r="K103" s="9">
-        <v>20.99</v>
-      </c>
-      <c r="L103" s="10">
-        <v>-25.2</v>
+        <v>28.23</v>
+      </c>
+      <c r="L103" s="8">
+        <v>-26.3</v>
       </c>
       <c r="M103" s="9">
         <v>7.24</v>
       </c>
-      <c r="N103" s="8">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="O103" s="10">
-        <v>-27.7</v>
+      <c r="N103" s="9">
+        <v>0</v>
+      </c>
+      <c r="O103" s="8">
+        <v>-29.3</v>
       </c>
       <c r="P103" s="9">
-        <v>20.99</v>
-      </c>
-      <c r="Q103" s="10">
-        <v>-25.2</v>
+        <v>28.23</v>
+      </c>
+      <c r="Q103" s="8">
+        <v>-26.3</v>
       </c>
     </row>
     <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
-        <v>41671</v>
+        <v>41699</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>17</v>
@@ -6654,39 +6654,39 @@
         <v>17</v>
       </c>
       <c r="H104" s="9">
-        <v>6.06</v>
+        <v>7.24</v>
       </c>
       <c r="I104" s="10">
-        <v>-21.3</v>
-      </c>
-      <c r="J104" s="10">
-        <v>-27.5</v>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="J104" s="8">
+        <v>-27.7</v>
       </c>
       <c r="K104" s="9">
-        <v>13.75</v>
-      </c>
-      <c r="L104" s="10">
-        <v>-23.8</v>
+        <v>20.99</v>
+      </c>
+      <c r="L104" s="8">
+        <v>-25.2</v>
       </c>
       <c r="M104" s="9">
-        <v>6.06</v>
+        <v>7.24</v>
       </c>
       <c r="N104" s="10">
-        <v>-21.3</v>
-      </c>
-      <c r="O104" s="10">
-        <v>-27.5</v>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="O104" s="8">
+        <v>-27.7</v>
       </c>
       <c r="P104" s="9">
-        <v>13.75</v>
-      </c>
-      <c r="Q104" s="10">
-        <v>-23.8</v>
+        <v>20.99</v>
+      </c>
+      <c r="Q104" s="8">
+        <v>-25.2</v>
       </c>
     </row>
     <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
-        <v>41640</v>
+        <v>41671</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>17</v>
@@ -6707,39 +6707,39 @@
         <v>17</v>
       </c>
       <c r="H105" s="9">
-        <v>7.7</v>
+        <v>6.06</v>
       </c>
       <c r="I105" s="8">
-        <v>11.6</v>
-      </c>
-      <c r="J105" s="10">
-        <v>-20.6</v>
+        <v>-21.3</v>
+      </c>
+      <c r="J105" s="8">
+        <v>-27.5</v>
       </c>
       <c r="K105" s="9">
-        <v>7.7</v>
-      </c>
-      <c r="L105" s="10">
-        <v>-20.6</v>
+        <v>13.75</v>
+      </c>
+      <c r="L105" s="8">
+        <v>-23.8</v>
       </c>
       <c r="M105" s="9">
-        <v>7.7</v>
+        <v>6.06</v>
       </c>
       <c r="N105" s="8">
-        <v>11.6</v>
-      </c>
-      <c r="O105" s="10">
-        <v>-20.6</v>
+        <v>-21.3</v>
+      </c>
+      <c r="O105" s="8">
+        <v>-27.5</v>
       </c>
       <c r="P105" s="9">
-        <v>7.7</v>
-      </c>
-      <c r="Q105" s="10">
-        <v>-20.6</v>
+        <v>13.75</v>
+      </c>
+      <c r="Q105" s="8">
+        <v>-23.8</v>
       </c>
     </row>
     <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
-        <v>41609</v>
+        <v>41640</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>17</v>
@@ -6760,39 +6760,39 @@
         <v>17</v>
       </c>
       <c r="H106" s="9">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="I106" s="10">
-        <v>-14.2</v>
-      </c>
-      <c r="J106" s="10">
-        <v>-21.8</v>
+        <v>11.6</v>
+      </c>
+      <c r="J106" s="8">
+        <v>-20.6</v>
       </c>
       <c r="K106" s="9">
-        <v>109</v>
+        <v>7.7</v>
       </c>
       <c r="L106" s="8">
-        <v>3.24</v>
+        <v>-20.6</v>
       </c>
       <c r="M106" s="9">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="N106" s="10">
-        <v>-14.2</v>
-      </c>
-      <c r="O106" s="10">
-        <v>-21.8</v>
+        <v>11.6</v>
+      </c>
+      <c r="O106" s="8">
+        <v>-20.6</v>
       </c>
       <c r="P106" s="9">
-        <v>109</v>
+        <v>7.7</v>
       </c>
       <c r="Q106" s="8">
-        <v>3.24</v>
+        <v>-20.6</v>
       </c>
     </row>
     <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
-        <v>41579</v>
+        <v>41609</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>17</v>
@@ -6813,39 +6813,39 @@
         <v>17</v>
       </c>
       <c r="H107" s="9">
-        <v>8.0399999999999991</v>
+        <v>6.9</v>
       </c>
       <c r="I107" s="8">
-        <v>2.11</v>
-      </c>
-      <c r="J107" s="10">
-        <v>-10.7</v>
+        <v>-14.2</v>
+      </c>
+      <c r="J107" s="8">
+        <v>-21.8</v>
       </c>
       <c r="K107" s="9">
-        <v>102.1</v>
-      </c>
-      <c r="L107" s="8">
-        <v>5.52</v>
+        <v>109</v>
+      </c>
+      <c r="L107" s="10">
+        <v>3.24</v>
       </c>
       <c r="M107" s="9">
-        <v>8.0399999999999991</v>
+        <v>6.9</v>
       </c>
       <c r="N107" s="8">
-        <v>2.11</v>
-      </c>
-      <c r="O107" s="10">
-        <v>-10.7</v>
+        <v>-14.2</v>
+      </c>
+      <c r="O107" s="8">
+        <v>-21.8</v>
       </c>
       <c r="P107" s="9">
-        <v>102.1</v>
-      </c>
-      <c r="Q107" s="8">
-        <v>5.52</v>
+        <v>109</v>
+      </c>
+      <c r="Q107" s="10">
+        <v>3.24</v>
       </c>
     </row>
     <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
-        <v>41548</v>
+        <v>41579</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>17</v>
@@ -6866,39 +6866,39 @@
         <v>17</v>
       </c>
       <c r="H108" s="9">
-        <v>7.88</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="I108" s="10">
-        <v>-11.3</v>
-      </c>
-      <c r="J108" s="10">
-        <v>-18.2</v>
+        <v>2.11</v>
+      </c>
+      <c r="J108" s="8">
+        <v>-10.7</v>
       </c>
       <c r="K108" s="9">
-        <v>94.07</v>
-      </c>
-      <c r="L108" s="8">
-        <v>7.19</v>
+        <v>102.1</v>
+      </c>
+      <c r="L108" s="10">
+        <v>5.52</v>
       </c>
       <c r="M108" s="9">
-        <v>7.88</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="N108" s="10">
-        <v>-11.3</v>
-      </c>
-      <c r="O108" s="10">
-        <v>-18.2</v>
+        <v>2.11</v>
+      </c>
+      <c r="O108" s="8">
+        <v>-10.7</v>
       </c>
       <c r="P108" s="9">
-        <v>94.07</v>
-      </c>
-      <c r="Q108" s="8">
-        <v>7.19</v>
+        <v>102.1</v>
+      </c>
+      <c r="Q108" s="10">
+        <v>5.52</v>
       </c>
     </row>
     <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
-        <v>41518</v>
+        <v>41548</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>17</v>
@@ -6919,39 +6919,39 @@
         <v>17</v>
       </c>
       <c r="H109" s="9">
-        <v>8.8800000000000008</v>
-      </c>
-      <c r="I109" s="10">
-        <v>-13</v>
-      </c>
-      <c r="J109" s="10">
-        <v>-7.92</v>
+        <v>7.88</v>
+      </c>
+      <c r="I109" s="8">
+        <v>-11.3</v>
+      </c>
+      <c r="J109" s="8">
+        <v>-18.2</v>
       </c>
       <c r="K109" s="9">
-        <v>86.19</v>
-      </c>
-      <c r="L109" s="8">
-        <v>10.3</v>
+        <v>94.07</v>
+      </c>
+      <c r="L109" s="10">
+        <v>7.19</v>
       </c>
       <c r="M109" s="9">
-        <v>8.8800000000000008</v>
-      </c>
-      <c r="N109" s="10">
-        <v>-13</v>
-      </c>
-      <c r="O109" s="10">
-        <v>-7.92</v>
+        <v>7.88</v>
+      </c>
+      <c r="N109" s="8">
+        <v>-11.3</v>
+      </c>
+      <c r="O109" s="8">
+        <v>-18.2</v>
       </c>
       <c r="P109" s="9">
-        <v>86.19</v>
-      </c>
-      <c r="Q109" s="8">
-        <v>10.3</v>
+        <v>94.07</v>
+      </c>
+      <c r="Q109" s="10">
+        <v>7.19</v>
       </c>
     </row>
     <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
-        <v>41487</v>
+        <v>41518</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>17</v>
@@ -6972,39 +6972,39 @@
         <v>17</v>
       </c>
       <c r="H110" s="9">
-        <v>10.199999999999999</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="I110" s="8">
-        <v>5.05</v>
+        <v>-13</v>
       </c>
       <c r="J110" s="8">
-        <v>7.22</v>
+        <v>-7.92</v>
       </c>
       <c r="K110" s="9">
-        <v>77.31</v>
-      </c>
-      <c r="L110" s="8">
-        <v>12.9</v>
+        <v>86.19</v>
+      </c>
+      <c r="L110" s="10">
+        <v>10.3</v>
       </c>
       <c r="M110" s="9">
-        <v>10.199999999999999</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="N110" s="8">
-        <v>5.05</v>
+        <v>-13</v>
       </c>
       <c r="O110" s="8">
-        <v>7.22</v>
+        <v>-7.92</v>
       </c>
       <c r="P110" s="9">
-        <v>77.31</v>
-      </c>
-      <c r="Q110" s="8">
-        <v>12.9</v>
+        <v>86.19</v>
+      </c>
+      <c r="Q110" s="10">
+        <v>10.3</v>
       </c>
     </row>
     <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
-        <v>41456</v>
+        <v>41487</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>17</v>
@@ -7025,39 +7025,39 @@
         <v>17</v>
       </c>
       <c r="H111" s="9">
-        <v>9.7100000000000009</v>
-      </c>
-      <c r="I111" s="8">
-        <v>1.67</v>
-      </c>
-      <c r="J111" s="8">
-        <v>14.5</v>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="I111" s="10">
+        <v>5.05</v>
+      </c>
+      <c r="J111" s="10">
+        <v>7.22</v>
       </c>
       <c r="K111" s="9">
-        <v>67.11</v>
-      </c>
-      <c r="L111" s="8">
-        <v>13.8</v>
+        <v>77.31</v>
+      </c>
+      <c r="L111" s="10">
+        <v>12.9</v>
       </c>
       <c r="M111" s="9">
-        <v>9.7100000000000009</v>
-      </c>
-      <c r="N111" s="8">
-        <v>1.67</v>
-      </c>
-      <c r="O111" s="8">
-        <v>14.5</v>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="N111" s="10">
+        <v>5.05</v>
+      </c>
+      <c r="O111" s="10">
+        <v>7.22</v>
       </c>
       <c r="P111" s="9">
-        <v>67.11</v>
-      </c>
-      <c r="Q111" s="8">
-        <v>13.8</v>
+        <v>77.31</v>
+      </c>
+      <c r="Q111" s="10">
+        <v>12.9</v>
       </c>
     </row>
     <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
-        <v>41426</v>
+        <v>41456</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>17</v>
@@ -7078,39 +7078,39 @@
         <v>17</v>
       </c>
       <c r="H112" s="9">
-        <v>9.5500000000000007</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="I112" s="10">
-        <v>-0.05</v>
-      </c>
-      <c r="J112" s="8">
-        <v>10.6</v>
+        <v>1.67</v>
+      </c>
+      <c r="J112" s="10">
+        <v>14.5</v>
       </c>
       <c r="K112" s="9">
-        <v>57.4</v>
-      </c>
-      <c r="L112" s="8">
-        <v>13.7</v>
+        <v>67.11</v>
+      </c>
+      <c r="L112" s="10">
+        <v>13.8</v>
       </c>
       <c r="M112" s="9">
-        <v>9.5500000000000007</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="N112" s="10">
-        <v>-0.05</v>
-      </c>
-      <c r="O112" s="8">
-        <v>10.6</v>
+        <v>1.67</v>
+      </c>
+      <c r="O112" s="10">
+        <v>14.5</v>
       </c>
       <c r="P112" s="9">
-        <v>57.4</v>
-      </c>
-      <c r="Q112" s="8">
-        <v>13.7</v>
+        <v>67.11</v>
+      </c>
+      <c r="Q112" s="10">
+        <v>13.8</v>
       </c>
     </row>
     <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
-        <v>41395</v>
+        <v>41426</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>17</v>
@@ -7131,39 +7131,39 @@
         <v>17</v>
       </c>
       <c r="H113" s="9">
-        <v>9.56</v>
-      </c>
-      <c r="I113" s="10">
-        <v>-6.65</v>
-      </c>
-      <c r="J113" s="8">
-        <v>13.1</v>
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="I113" s="8">
+        <v>-0.05</v>
+      </c>
+      <c r="J113" s="10">
+        <v>10.6</v>
       </c>
       <c r="K113" s="9">
-        <v>47.85</v>
-      </c>
-      <c r="L113" s="8">
-        <v>14.4</v>
+        <v>57.4</v>
+      </c>
+      <c r="L113" s="10">
+        <v>13.7</v>
       </c>
       <c r="M113" s="9">
-        <v>9.56</v>
-      </c>
-      <c r="N113" s="10">
-        <v>-6.65</v>
-      </c>
-      <c r="O113" s="8">
-        <v>13.1</v>
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="N113" s="8">
+        <v>-0.05</v>
+      </c>
+      <c r="O113" s="10">
+        <v>10.6</v>
       </c>
       <c r="P113" s="9">
-        <v>47.85</v>
-      </c>
-      <c r="Q113" s="8">
-        <v>14.4</v>
+        <v>57.4</v>
+      </c>
+      <c r="Q113" s="10">
+        <v>13.7</v>
       </c>
     </row>
     <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
-        <v>41365</v>
+        <v>41395</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>17</v>
@@ -7184,39 +7184,39 @@
         <v>17</v>
       </c>
       <c r="H114" s="9">
-        <v>10.24</v>
+        <v>9.56</v>
       </c>
       <c r="I114" s="8">
-        <v>2.27</v>
-      </c>
-      <c r="J114" s="8">
-        <v>10.4</v>
+        <v>-6.65</v>
+      </c>
+      <c r="J114" s="10">
+        <v>13.1</v>
       </c>
       <c r="K114" s="9">
-        <v>38.29</v>
-      </c>
-      <c r="L114" s="8">
-        <v>14.7</v>
+        <v>47.85</v>
+      </c>
+      <c r="L114" s="10">
+        <v>14.4</v>
       </c>
       <c r="M114" s="9">
-        <v>10.24</v>
+        <v>9.56</v>
       </c>
       <c r="N114" s="8">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="O114" s="8">
-        <v>10.4</v>
+        <v>-6.65</v>
+      </c>
+      <c r="O114" s="10">
+        <v>13.1</v>
       </c>
       <c r="P114" s="9">
-        <v>38.29</v>
-      </c>
-      <c r="Q114" s="8">
-        <v>14.7</v>
+        <v>47.85</v>
+      </c>
+      <c r="Q114" s="10">
+        <v>14.4</v>
       </c>
     </row>
     <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
-        <v>41334</v>
+        <v>41365</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>17</v>
@@ -7237,39 +7237,39 @@
         <v>17</v>
       </c>
       <c r="H115" s="9">
-        <v>10.01</v>
-      </c>
-      <c r="I115" s="8">
-        <v>19.8</v>
-      </c>
-      <c r="J115" s="8">
-        <v>14.4</v>
+        <v>10.24</v>
+      </c>
+      <c r="I115" s="10">
+        <v>2.27</v>
+      </c>
+      <c r="J115" s="10">
+        <v>10.4</v>
       </c>
       <c r="K115" s="9">
-        <v>28.06</v>
-      </c>
-      <c r="L115" s="8">
-        <v>16.3</v>
+        <v>38.29</v>
+      </c>
+      <c r="L115" s="10">
+        <v>14.7</v>
       </c>
       <c r="M115" s="9">
-        <v>10.01</v>
-      </c>
-      <c r="N115" s="8">
-        <v>19.8</v>
-      </c>
-      <c r="O115" s="8">
-        <v>14.4</v>
+        <v>10.24</v>
+      </c>
+      <c r="N115" s="10">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="O115" s="10">
+        <v>10.4</v>
       </c>
       <c r="P115" s="9">
-        <v>28.06</v>
-      </c>
-      <c r="Q115" s="8">
-        <v>16.3</v>
+        <v>38.29</v>
+      </c>
+      <c r="Q115" s="10">
+        <v>14.7</v>
       </c>
     </row>
     <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
-        <v>41306</v>
+        <v>41334</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>17</v>
@@ -7290,39 +7290,39 @@
         <v>17</v>
       </c>
       <c r="H116" s="9">
-        <v>8.35</v>
+        <v>10.01</v>
       </c>
       <c r="I116" s="10">
-        <v>-13.8</v>
-      </c>
-      <c r="J116" s="8">
-        <v>3.08</v>
+        <v>19.8</v>
+      </c>
+      <c r="J116" s="10">
+        <v>14.4</v>
       </c>
       <c r="K116" s="9">
-        <v>18.05</v>
-      </c>
-      <c r="L116" s="8">
-        <v>17.399999999999999</v>
+        <v>28.06</v>
+      </c>
+      <c r="L116" s="10">
+        <v>16.3</v>
       </c>
       <c r="M116" s="9">
-        <v>8.35</v>
+        <v>10.01</v>
       </c>
       <c r="N116" s="10">
-        <v>-13.8</v>
-      </c>
-      <c r="O116" s="8">
-        <v>3.09</v>
+        <v>19.8</v>
+      </c>
+      <c r="O116" s="10">
+        <v>14.4</v>
       </c>
       <c r="P116" s="9">
-        <v>18.05</v>
-      </c>
-      <c r="Q116" s="8">
-        <v>17.399999999999999</v>
+        <v>28.06</v>
+      </c>
+      <c r="Q116" s="10">
+        <v>16.3</v>
       </c>
     </row>
     <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
-        <v>41275</v>
+        <v>41306</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>17</v>
@@ -7343,39 +7343,39 @@
         <v>17</v>
       </c>
       <c r="H117" s="9">
-        <v>9.69</v>
-      </c>
-      <c r="I117" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J117" s="8">
-        <v>33.200000000000003</v>
+        <v>8.35</v>
+      </c>
+      <c r="I117" s="8">
+        <v>-13.8</v>
+      </c>
+      <c r="J117" s="10">
+        <v>3.08</v>
       </c>
       <c r="K117" s="9">
-        <v>9.69</v>
-      </c>
-      <c r="L117" s="8">
-        <v>33.200000000000003</v>
+        <v>18.05</v>
+      </c>
+      <c r="L117" s="10">
+        <v>17.399999999999999</v>
       </c>
       <c r="M117" s="9">
-        <v>9.69</v>
-      </c>
-      <c r="N117" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O117" s="8">
-        <v>33.200000000000003</v>
+        <v>8.35</v>
+      </c>
+      <c r="N117" s="8">
+        <v>-13.8</v>
+      </c>
+      <c r="O117" s="10">
+        <v>3.09</v>
       </c>
       <c r="P117" s="9">
-        <v>9.69</v>
-      </c>
-      <c r="Q117" s="8">
-        <v>33.200000000000003</v>
+        <v>18.05</v>
+      </c>
+      <c r="Q117" s="10">
+        <v>17.399999999999999</v>
       </c>
     </row>
     <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
-        <v>41244</v>
+        <v>41275</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>17</v>
@@ -7396,39 +7396,39 @@
         <v>17</v>
       </c>
       <c r="H118" s="9">
-        <v>8.82</v>
-      </c>
-      <c r="I118" s="10">
-        <v>-2.0699999999999998</v>
-      </c>
-      <c r="J118" s="8">
-        <v>28.4</v>
+        <v>9.69</v>
+      </c>
+      <c r="I118" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J118" s="10">
+        <v>33.200000000000003</v>
       </c>
       <c r="K118" s="9">
-        <v>105.6</v>
-      </c>
-      <c r="L118" s="8">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="M118" s="9" t="s">
-        <v>17</v>
+        <v>9.69</v>
+      </c>
+      <c r="L118" s="10">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="M118" s="9">
+        <v>9.69</v>
       </c>
       <c r="N118" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O118" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P118" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q118" s="9" t="s">
-        <v>17</v>
+      <c r="O118" s="10">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="P118" s="9">
+        <v>9.69</v>
+      </c>
+      <c r="Q118" s="10">
+        <v>33.200000000000003</v>
       </c>
     </row>
     <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
-        <v>41214</v>
+        <v>41244</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>17</v>
@@ -7449,19 +7449,19 @@
         <v>17</v>
       </c>
       <c r="H119" s="9">
-        <v>9.01</v>
-      </c>
-      <c r="I119" s="10">
-        <v>-6.51</v>
-      </c>
-      <c r="J119" s="8">
-        <v>26.7</v>
+        <v>8.82</v>
+      </c>
+      <c r="I119" s="8">
+        <v>-2.0699999999999998</v>
+      </c>
+      <c r="J119" s="10">
+        <v>28.4</v>
       </c>
       <c r="K119" s="9">
-        <v>96.76</v>
-      </c>
-      <c r="L119" s="8">
-        <v>15.6</v>
+        <v>105.6</v>
+      </c>
+      <c r="L119" s="10">
+        <v>16.600000000000001</v>
       </c>
       <c r="M119" s="9" t="s">
         <v>17</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
-        <v>41183</v>
+        <v>41214</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>17</v>
@@ -7502,19 +7502,19 @@
         <v>17</v>
       </c>
       <c r="H120" s="9">
-        <v>9.6300000000000008</v>
-      </c>
-      <c r="I120" s="10">
-        <v>-0.12</v>
-      </c>
-      <c r="J120" s="8">
-        <v>22.8</v>
+        <v>9.01</v>
+      </c>
+      <c r="I120" s="8">
+        <v>-6.51</v>
+      </c>
+      <c r="J120" s="10">
+        <v>26.7</v>
       </c>
       <c r="K120" s="9">
-        <v>87.76</v>
-      </c>
-      <c r="L120" s="8">
-        <v>14.6</v>
+        <v>96.76</v>
+      </c>
+      <c r="L120" s="10">
+        <v>15.6</v>
       </c>
       <c r="M120" s="9" t="s">
         <v>17</v>
@@ -7534,7 +7534,7 @@
     </row>
     <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
-        <v>41153</v>
+        <v>41183</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>17</v>
@@ -7555,19 +7555,19 @@
         <v>17</v>
       </c>
       <c r="H121" s="9">
-        <v>9.64</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="I121" s="8">
-        <v>1.37</v>
-      </c>
-      <c r="J121" s="8">
-        <v>23.6</v>
+        <v>-0.12</v>
+      </c>
+      <c r="J121" s="10">
+        <v>22.8</v>
       </c>
       <c r="K121" s="9">
-        <v>78.13</v>
-      </c>
-      <c r="L121" s="8">
-        <v>13.6</v>
+        <v>87.76</v>
+      </c>
+      <c r="L121" s="10">
+        <v>14.6</v>
       </c>
       <c r="M121" s="9" t="s">
         <v>17</v>
@@ -7587,7 +7587,7 @@
     </row>
     <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
-        <v>41122</v>
+        <v>41153</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>17</v>
@@ -7608,19 +7608,19 @@
         <v>17</v>
       </c>
       <c r="H122" s="9">
-        <v>9.51</v>
-      </c>
-      <c r="I122" s="8">
-        <v>12.1</v>
-      </c>
-      <c r="J122" s="8">
-        <v>29.9</v>
+        <v>9.64</v>
+      </c>
+      <c r="I122" s="10">
+        <v>1.37</v>
+      </c>
+      <c r="J122" s="10">
+        <v>23.6</v>
       </c>
       <c r="K122" s="9">
-        <v>68.48</v>
-      </c>
-      <c r="L122" s="8">
-        <v>12.4</v>
+        <v>78.13</v>
+      </c>
+      <c r="L122" s="10">
+        <v>13.6</v>
       </c>
       <c r="M122" s="9" t="s">
         <v>17</v>
@@ -7640,7 +7640,7 @@
     </row>
     <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
-        <v>41091</v>
+        <v>41122</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>17</v>
@@ -7661,19 +7661,19 @@
         <v>17</v>
       </c>
       <c r="H123" s="9">
-        <v>8.48</v>
+        <v>9.51</v>
       </c>
       <c r="I123" s="10">
-        <v>-1.78</v>
-      </c>
-      <c r="J123" s="8">
-        <v>8.33</v>
+        <v>12.1</v>
+      </c>
+      <c r="J123" s="10">
+        <v>29.9</v>
       </c>
       <c r="K123" s="9">
-        <v>58.97</v>
-      </c>
-      <c r="L123" s="8">
-        <v>9.98</v>
+        <v>68.48</v>
+      </c>
+      <c r="L123" s="10">
+        <v>12.4</v>
       </c>
       <c r="M123" s="9" t="s">
         <v>17</v>
@@ -7693,7 +7693,7 @@
     </row>
     <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
-        <v>41061</v>
+        <v>41091</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>17</v>
@@ -7714,19 +7714,19 @@
         <v>17</v>
       </c>
       <c r="H124" s="9">
-        <v>8.64</v>
+        <v>8.48</v>
       </c>
       <c r="I124" s="8">
-        <v>2.25</v>
-      </c>
-      <c r="J124" s="8">
-        <v>28.3</v>
+        <v>-1.78</v>
+      </c>
+      <c r="J124" s="10">
+        <v>8.33</v>
       </c>
       <c r="K124" s="9">
-        <v>50.48</v>
-      </c>
-      <c r="L124" s="8">
-        <v>10.3</v>
+        <v>58.97</v>
+      </c>
+      <c r="L124" s="10">
+        <v>9.98</v>
       </c>
       <c r="M124" s="9" t="s">
         <v>17</v>
@@ -7746,7 +7746,7 @@
     </row>
     <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
-        <v>41030</v>
+        <v>41061</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>17</v>
@@ -7767,19 +7767,19 @@
         <v>17</v>
       </c>
       <c r="H125" s="9">
-        <v>8.4499999999999993</v>
+        <v>8.64</v>
       </c>
       <c r="I125" s="10">
-        <v>-8.8800000000000008</v>
-      </c>
-      <c r="J125" s="8">
-        <v>5.44</v>
+        <v>2.25</v>
+      </c>
+      <c r="J125" s="10">
+        <v>28.3</v>
       </c>
       <c r="K125" s="9">
-        <v>41.84</v>
-      </c>
-      <c r="L125" s="8">
-        <v>7.16</v>
+        <v>50.48</v>
+      </c>
+      <c r="L125" s="10">
+        <v>10.3</v>
       </c>
       <c r="M125" s="9" t="s">
         <v>17</v>
@@ -7799,7 +7799,7 @@
     </row>
     <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
-        <v>41000</v>
+        <v>41030</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>17</v>
@@ -7820,19 +7820,19 @@
         <v>17</v>
       </c>
       <c r="H126" s="9">
-        <v>9.27</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="I126" s="8">
-        <v>6</v>
-      </c>
-      <c r="J126" s="8">
-        <v>11.6</v>
+        <v>-8.8800000000000008</v>
+      </c>
+      <c r="J126" s="10">
+        <v>5.44</v>
       </c>
       <c r="K126" s="9">
-        <v>33.4</v>
-      </c>
-      <c r="L126" s="8">
-        <v>7.6</v>
+        <v>41.84</v>
+      </c>
+      <c r="L126" s="10">
+        <v>7.16</v>
       </c>
       <c r="M126" s="9" t="s">
         <v>17</v>
@@ -7852,7 +7852,7 @@
     </row>
     <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
-        <v>40969</v>
+        <v>41000</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>17</v>
@@ -7873,19 +7873,19 @@
         <v>17</v>
       </c>
       <c r="H127" s="9">
-        <v>8.75</v>
-      </c>
-      <c r="I127" s="8">
-        <v>7.96</v>
-      </c>
-      <c r="J127" s="8">
-        <v>3.31</v>
+        <v>9.27</v>
+      </c>
+      <c r="I127" s="10">
+        <v>6</v>
+      </c>
+      <c r="J127" s="10">
+        <v>11.6</v>
       </c>
       <c r="K127" s="9">
-        <v>24.12</v>
-      </c>
-      <c r="L127" s="8">
-        <v>6.13</v>
+        <v>33.4</v>
+      </c>
+      <c r="L127" s="10">
+        <v>7.6</v>
       </c>
       <c r="M127" s="9" t="s">
         <v>17</v>
@@ -7905,7 +7905,7 @@
     </row>
     <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
-        <v>40940</v>
+        <v>40969</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>17</v>
@@ -7926,19 +7926,19 @@
         <v>17</v>
       </c>
       <c r="H128" s="9">
-        <v>8.1</v>
-      </c>
-      <c r="I128" s="8">
-        <v>11.4</v>
-      </c>
-      <c r="J128" s="8">
-        <v>25.2</v>
+        <v>8.75</v>
+      </c>
+      <c r="I128" s="10">
+        <v>7.96</v>
+      </c>
+      <c r="J128" s="10">
+        <v>3.31</v>
       </c>
       <c r="K128" s="9">
-        <v>15.38</v>
-      </c>
-      <c r="L128" s="8">
-        <v>7.81</v>
+        <v>24.12</v>
+      </c>
+      <c r="L128" s="10">
+        <v>6.13</v>
       </c>
       <c r="M128" s="9" t="s">
         <v>17</v>
@@ -7958,7 +7958,7 @@
     </row>
     <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
-        <v>40909</v>
+        <v>40940</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>17</v>
@@ -7979,19 +7979,19 @@
         <v>17</v>
       </c>
       <c r="H129" s="9">
-        <v>7.28</v>
-      </c>
-      <c r="I129" s="8">
-        <v>5.98</v>
+        <v>8.1</v>
+      </c>
+      <c r="I129" s="10">
+        <v>11.4</v>
       </c>
       <c r="J129" s="10">
-        <v>-6.61</v>
+        <v>25.2</v>
       </c>
       <c r="K129" s="9">
-        <v>7.28</v>
+        <v>15.38</v>
       </c>
       <c r="L129" s="10">
-        <v>-6.61</v>
+        <v>7.81</v>
       </c>
       <c r="M129" s="9" t="s">
         <v>17</v>
@@ -8011,7 +8011,7 @@
     </row>
     <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
-        <v>40878</v>
+        <v>40909</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>17</v>
@@ -8032,19 +8032,19 @@
         <v>17</v>
       </c>
       <c r="H130" s="9">
-        <v>6.86</v>
+        <v>7.28</v>
       </c>
       <c r="I130" s="10">
-        <v>-3.41</v>
+        <v>5.98</v>
       </c>
       <c r="J130" s="8">
-        <v>2.5</v>
+        <v>-6.61</v>
       </c>
       <c r="K130" s="9">
-        <v>90.56</v>
-      </c>
-      <c r="L130" s="10">
-        <v>-1.26</v>
+        <v>7.28</v>
+      </c>
+      <c r="L130" s="8">
+        <v>-6.61</v>
       </c>
       <c r="M130" s="9" t="s">
         <v>17</v>
@@ -8064,7 +8064,7 @@
     </row>
     <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
-        <v>40848</v>
+        <v>40878</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>17</v>
@@ -8085,19 +8085,19 @@
         <v>17</v>
       </c>
       <c r="H131" s="9">
-        <v>7.11</v>
-      </c>
-      <c r="I131" s="10">
-        <v>-9.39</v>
+        <v>6.86</v>
+      </c>
+      <c r="I131" s="8">
+        <v>-3.41</v>
       </c>
       <c r="J131" s="10">
-        <v>-4.38</v>
+        <v>2.5</v>
       </c>
       <c r="K131" s="9">
-        <v>83.69</v>
-      </c>
-      <c r="L131" s="10">
-        <v>-1.56</v>
+        <v>90.56</v>
+      </c>
+      <c r="L131" s="8">
+        <v>-1.26</v>
       </c>
       <c r="M131" s="9" t="s">
         <v>17</v>
@@ -8117,7 +8117,7 @@
     </row>
     <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
-        <v>40817</v>
+        <v>40848</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>17</v>
@@ -8138,19 +8138,19 @@
         <v>17</v>
       </c>
       <c r="H132" s="9">
-        <v>7.84</v>
+        <v>7.11</v>
       </c>
       <c r="I132" s="8">
-        <v>0.5</v>
+        <v>-9.39</v>
       </c>
       <c r="J132" s="8">
-        <v>9.58</v>
+        <v>-4.38</v>
       </c>
       <c r="K132" s="9">
-        <v>76.59</v>
-      </c>
-      <c r="L132" s="10">
-        <v>-1.29</v>
+        <v>83.69</v>
+      </c>
+      <c r="L132" s="8">
+        <v>-1.56</v>
       </c>
       <c r="M132" s="9" t="s">
         <v>17</v>
@@ -8170,7 +8170,7 @@
     </row>
     <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
-        <v>40787</v>
+        <v>40817</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>17</v>
@@ -8191,19 +8191,19 @@
         <v>17</v>
       </c>
       <c r="H133" s="9">
-        <v>7.8</v>
-      </c>
-      <c r="I133" s="8">
-        <v>6.54</v>
-      </c>
-      <c r="J133" s="8">
-        <v>6</v>
+        <v>7.84</v>
+      </c>
+      <c r="I133" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="J133" s="10">
+        <v>9.58</v>
       </c>
       <c r="K133" s="9">
-        <v>68.739999999999995</v>
-      </c>
-      <c r="L133" s="10">
-        <v>-2.39</v>
+        <v>76.59</v>
+      </c>
+      <c r="L133" s="8">
+        <v>-1.29</v>
       </c>
       <c r="M133" s="9" t="s">
         <v>17</v>
@@ -8223,7 +8223,7 @@
     </row>
     <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
-        <v>40756</v>
+        <v>40787</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>17</v>
@@ -8244,19 +8244,19 @@
         <v>17</v>
       </c>
       <c r="H134" s="9">
-        <v>7.33</v>
+        <v>7.8</v>
       </c>
       <c r="I134" s="10">
-        <v>-6.45</v>
-      </c>
-      <c r="J134" s="8">
-        <v>2.93</v>
+        <v>6.54</v>
+      </c>
+      <c r="J134" s="10">
+        <v>6</v>
       </c>
       <c r="K134" s="9">
-        <v>60.94</v>
-      </c>
-      <c r="L134" s="10">
-        <v>-3.38</v>
+        <v>68.739999999999995</v>
+      </c>
+      <c r="L134" s="8">
+        <v>-2.39</v>
       </c>
       <c r="M134" s="9" t="s">
         <v>17</v>
@@ -8276,7 +8276,7 @@
     </row>
     <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
-        <v>40725</v>
+        <v>40756</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>17</v>
@@ -8297,19 +8297,19 @@
         <v>17</v>
       </c>
       <c r="H135" s="9">
-        <v>7.83</v>
+        <v>7.33</v>
       </c>
       <c r="I135" s="8">
-        <v>16.3</v>
-      </c>
-      <c r="J135" s="8">
-        <v>6.26</v>
+        <v>-6.45</v>
+      </c>
+      <c r="J135" s="10">
+        <v>2.93</v>
       </c>
       <c r="K135" s="9">
-        <v>53.61</v>
-      </c>
-      <c r="L135" s="10">
-        <v>-4.18</v>
+        <v>60.94</v>
+      </c>
+      <c r="L135" s="8">
+        <v>-3.38</v>
       </c>
       <c r="M135" s="9" t="s">
         <v>17</v>
@@ -8329,7 +8329,7 @@
     </row>
     <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
-        <v>40695</v>
+        <v>40725</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>17</v>
@@ -8350,19 +8350,19 @@
         <v>17</v>
       </c>
       <c r="H136" s="9">
-        <v>6.73</v>
+        <v>7.83</v>
       </c>
       <c r="I136" s="10">
-        <v>-16</v>
+        <v>16.3</v>
       </c>
       <c r="J136" s="10">
-        <v>-6.06</v>
+        <v>6.26</v>
       </c>
       <c r="K136" s="9">
-        <v>45.78</v>
-      </c>
-      <c r="L136" s="10">
-        <v>-5.76</v>
+        <v>53.61</v>
+      </c>
+      <c r="L136" s="8">
+        <v>-4.18</v>
       </c>
       <c r="M136" s="9" t="s">
         <v>17</v>
@@ -8382,7 +8382,7 @@
     </row>
     <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
-        <v>40664</v>
+        <v>40695</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>17</v>
@@ -8403,19 +8403,19 @@
         <v>17</v>
       </c>
       <c r="H137" s="9">
-        <v>8.01</v>
-      </c>
-      <c r="I137" s="10">
-        <v>-3.55</v>
-      </c>
-      <c r="J137" s="10">
-        <v>-3.73</v>
+        <v>6.73</v>
+      </c>
+      <c r="I137" s="8">
+        <v>-16</v>
+      </c>
+      <c r="J137" s="8">
+        <v>-6.06</v>
       </c>
       <c r="K137" s="9">
-        <v>39.049999999999997</v>
-      </c>
-      <c r="L137" s="10">
-        <v>-5.71</v>
+        <v>45.78</v>
+      </c>
+      <c r="L137" s="8">
+        <v>-5.76</v>
       </c>
       <c r="M137" s="9" t="s">
         <v>17</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
-        <v>40634</v>
+        <v>40664</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>17</v>
@@ -8456,19 +8456,19 @@
         <v>17</v>
       </c>
       <c r="H138" s="9">
-        <v>8.31</v>
-      </c>
-      <c r="I138" s="10">
-        <v>-1.87</v>
-      </c>
-      <c r="J138" s="10">
-        <v>-7.17</v>
+        <v>8.01</v>
+      </c>
+      <c r="I138" s="8">
+        <v>-3.55</v>
+      </c>
+      <c r="J138" s="8">
+        <v>-3.73</v>
       </c>
       <c r="K138" s="9">
-        <v>31.04</v>
-      </c>
-      <c r="L138" s="10">
-        <v>-6.21</v>
+        <v>39.049999999999997</v>
+      </c>
+      <c r="L138" s="8">
+        <v>-5.71</v>
       </c>
       <c r="M138" s="9" t="s">
         <v>17</v>
@@ -8488,7 +8488,7 @@
     </row>
     <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
-        <v>40603</v>
+        <v>40634</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>17</v>
@@ -8509,19 +8509,19 @@
         <v>17</v>
       </c>
       <c r="H139" s="9">
-        <v>8.4700000000000006</v>
+        <v>8.31</v>
       </c>
       <c r="I139" s="8">
-        <v>30.8</v>
-      </c>
-      <c r="J139" s="10">
-        <v>-6.73</v>
+        <v>-1.87</v>
+      </c>
+      <c r="J139" s="8">
+        <v>-7.17</v>
       </c>
       <c r="K139" s="9">
-        <v>22.73</v>
-      </c>
-      <c r="L139" s="10">
-        <v>-5.85</v>
+        <v>31.04</v>
+      </c>
+      <c r="L139" s="8">
+        <v>-6.21</v>
       </c>
       <c r="M139" s="9" t="s">
         <v>17</v>
@@ -8541,7 +8541,7 @@
     </row>
     <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
-        <v>40575</v>
+        <v>40603</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>17</v>
@@ -8562,19 +8562,19 @@
         <v>17</v>
       </c>
       <c r="H140" s="9">
-        <v>6.47</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="I140" s="10">
-        <v>-16.899999999999999</v>
-      </c>
-      <c r="J140" s="10">
-        <v>-5.9</v>
+        <v>30.8</v>
+      </c>
+      <c r="J140" s="8">
+        <v>-6.73</v>
       </c>
       <c r="K140" s="9">
-        <v>14.26</v>
-      </c>
-      <c r="L140" s="10">
-        <v>-5.32</v>
+        <v>22.73</v>
+      </c>
+      <c r="L140" s="8">
+        <v>-5.85</v>
       </c>
       <c r="M140" s="9" t="s">
         <v>17</v>
@@ -8594,7 +8594,7 @@
     </row>
     <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
-        <v>40544</v>
+        <v>40575</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>17</v>
@@ -8615,19 +8615,19 @@
         <v>17</v>
       </c>
       <c r="H141" s="9">
-        <v>7.79</v>
+        <v>6.47</v>
       </c>
       <c r="I141" s="8">
-        <v>16.3</v>
-      </c>
-      <c r="J141" s="10">
-        <v>-4.84</v>
+        <v>-16.899999999999999</v>
+      </c>
+      <c r="J141" s="8">
+        <v>-5.9</v>
       </c>
       <c r="K141" s="9">
-        <v>7.79</v>
-      </c>
-      <c r="L141" s="10">
-        <v>-4.84</v>
+        <v>14.26</v>
+      </c>
+      <c r="L141" s="8">
+        <v>-5.32</v>
       </c>
       <c r="M141" s="9" t="s">
         <v>17</v>
@@ -8647,7 +8647,7 @@
     </row>
     <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
-        <v>40513</v>
+        <v>40544</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>17</v>
@@ -8668,19 +8668,19 @@
         <v>17</v>
       </c>
       <c r="H142" s="9">
-        <v>6.7</v>
+        <v>7.79</v>
       </c>
       <c r="I142" s="10">
-        <v>-9.9</v>
-      </c>
-      <c r="J142" s="10">
-        <v>-13.9</v>
+        <v>16.3</v>
+      </c>
+      <c r="J142" s="8">
+        <v>-4.84</v>
       </c>
       <c r="K142" s="9">
-        <v>91.72</v>
+        <v>7.79</v>
       </c>
       <c r="L142" s="8">
-        <v>17.399999999999999</v>
+        <v>-4.84</v>
       </c>
       <c r="M142" s="9" t="s">
         <v>17</v>
@@ -8700,7 +8700,7 @@
     </row>
     <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
-        <v>40483</v>
+        <v>40513</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>17</v>
@@ -8721,19 +8721,19 @@
         <v>17</v>
       </c>
       <c r="H143" s="9">
-        <v>7.43</v>
+        <v>6.7</v>
       </c>
       <c r="I143" s="8">
-        <v>3.85</v>
-      </c>
-      <c r="J143" s="10">
-        <v>-2.69</v>
+        <v>-9.9</v>
+      </c>
+      <c r="J143" s="8">
+        <v>-13.9</v>
       </c>
       <c r="K143" s="9">
-        <v>85.02</v>
-      </c>
-      <c r="L143" s="8">
-        <v>20.9</v>
+        <v>91.72</v>
+      </c>
+      <c r="L143" s="10">
+        <v>17.399999999999999</v>
       </c>
       <c r="M143" s="9" t="s">
         <v>17</v>
@@ -8753,7 +8753,7 @@
     </row>
     <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
-        <v>40452</v>
+        <v>40483</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>17</v>
@@ -8774,19 +8774,19 @@
         <v>17</v>
       </c>
       <c r="H144" s="9">
-        <v>7.16</v>
+        <v>7.43</v>
       </c>
       <c r="I144" s="10">
-        <v>-2.78</v>
-      </c>
-      <c r="J144" s="10">
-        <v>-13.2</v>
+        <v>3.85</v>
+      </c>
+      <c r="J144" s="8">
+        <v>-2.69</v>
       </c>
       <c r="K144" s="9">
-        <v>77.59</v>
-      </c>
-      <c r="L144" s="8">
-        <v>23.8</v>
+        <v>85.02</v>
+      </c>
+      <c r="L144" s="10">
+        <v>20.9</v>
       </c>
       <c r="M144" s="9" t="s">
         <v>17</v>
@@ -8806,7 +8806,7 @@
     </row>
     <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
-        <v>40422</v>
+        <v>40452</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>17</v>
@@ -8827,19 +8827,19 @@
         <v>17</v>
       </c>
       <c r="H145" s="9">
-        <v>7.36</v>
+        <v>7.16</v>
       </c>
       <c r="I145" s="8">
-        <v>3.45</v>
-      </c>
-      <c r="J145" s="10">
-        <v>-13.8</v>
+        <v>-2.78</v>
+      </c>
+      <c r="J145" s="8">
+        <v>-13.2</v>
       </c>
       <c r="K145" s="9">
-        <v>70.430000000000007</v>
-      </c>
-      <c r="L145" s="8">
-        <v>29.4</v>
+        <v>77.59</v>
+      </c>
+      <c r="L145" s="10">
+        <v>23.8</v>
       </c>
       <c r="M145" s="9" t="s">
         <v>17</v>
@@ -8859,7 +8859,7 @@
     </row>
     <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
-        <v>40391</v>
+        <v>40422</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>17</v>
@@ -8880,19 +8880,19 @@
         <v>17</v>
       </c>
       <c r="H146" s="9">
-        <v>7.12</v>
+        <v>7.36</v>
       </c>
       <c r="I146" s="10">
-        <v>-3.43</v>
-      </c>
-      <c r="J146" s="10">
-        <v>-12.1</v>
+        <v>3.45</v>
+      </c>
+      <c r="J146" s="8">
+        <v>-13.8</v>
       </c>
       <c r="K146" s="9">
-        <v>63.07</v>
-      </c>
-      <c r="L146" s="8">
-        <v>37.4</v>
+        <v>70.430000000000007</v>
+      </c>
+      <c r="L146" s="10">
+        <v>29.4</v>
       </c>
       <c r="M146" s="9" t="s">
         <v>17</v>
@@ -8912,7 +8912,7 @@
     </row>
     <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
-        <v>40360</v>
+        <v>40391</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>17</v>
@@ -8933,19 +8933,19 @@
         <v>17</v>
       </c>
       <c r="H147" s="9">
-        <v>7.37</v>
+        <v>7.12</v>
       </c>
       <c r="I147" s="8">
-        <v>2.81</v>
-      </c>
-      <c r="J147" s="10">
-        <v>-1.81</v>
+        <v>-3.43</v>
+      </c>
+      <c r="J147" s="8">
+        <v>-12.1</v>
       </c>
       <c r="K147" s="9">
-        <v>55.95</v>
-      </c>
-      <c r="L147" s="8">
-        <v>48</v>
+        <v>63.07</v>
+      </c>
+      <c r="L147" s="10">
+        <v>37.4</v>
       </c>
       <c r="M147" s="9" t="s">
         <v>17</v>
@@ -8965,7 +8965,7 @@
     </row>
     <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
-        <v>40330</v>
+        <v>40360</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>17</v>
@@ -8986,19 +8986,19 @@
         <v>17</v>
       </c>
       <c r="H148" s="9">
-        <v>7.17</v>
+        <v>7.37</v>
       </c>
       <c r="I148" s="10">
-        <v>-13.9</v>
+        <v>2.81</v>
       </c>
       <c r="J148" s="8">
-        <v>14.8</v>
+        <v>-1.81</v>
       </c>
       <c r="K148" s="9">
-        <v>48.58</v>
-      </c>
-      <c r="L148" s="8">
-        <v>60.4</v>
+        <v>55.95</v>
+      </c>
+      <c r="L148" s="10">
+        <v>48</v>
       </c>
       <c r="M148" s="9" t="s">
         <v>17</v>
@@ -9018,7 +9018,7 @@
     </row>
     <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
-        <v>40299</v>
+        <v>40330</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>17</v>
@@ -9039,19 +9039,19 @@
         <v>17</v>
       </c>
       <c r="H149" s="9">
-        <v>8.32</v>
-      </c>
-      <c r="I149" s="10">
-        <v>-7</v>
-      </c>
-      <c r="J149" s="8">
-        <v>25.5</v>
+        <v>7.17</v>
+      </c>
+      <c r="I149" s="8">
+        <v>-13.9</v>
+      </c>
+      <c r="J149" s="10">
+        <v>14.8</v>
       </c>
       <c r="K149" s="9">
-        <v>41.42</v>
-      </c>
-      <c r="L149" s="8">
-        <v>72.3</v>
+        <v>48.58</v>
+      </c>
+      <c r="L149" s="10">
+        <v>60.4</v>
       </c>
       <c r="M149" s="9" t="s">
         <v>17</v>
@@ -9071,7 +9071,7 @@
     </row>
     <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
-        <v>40269</v>
+        <v>40299</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>17</v>
@@ -9092,19 +9092,19 @@
         <v>17</v>
       </c>
       <c r="H150" s="9">
-        <v>8.9499999999999993</v>
-      </c>
-      <c r="I150" s="10">
-        <v>-1.4</v>
-      </c>
-      <c r="J150" s="8">
-        <v>51.4</v>
+        <v>8.32</v>
+      </c>
+      <c r="I150" s="8">
+        <v>-7</v>
+      </c>
+      <c r="J150" s="10">
+        <v>25.5</v>
       </c>
       <c r="K150" s="9">
-        <v>33.090000000000003</v>
-      </c>
-      <c r="L150" s="8">
-        <v>90.1</v>
+        <v>41.42</v>
+      </c>
+      <c r="L150" s="10">
+        <v>72.3</v>
       </c>
       <c r="M150" s="9" t="s">
         <v>17</v>
@@ -9124,7 +9124,7 @@
     </row>
     <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
-        <v>40238</v>
+        <v>40269</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>17</v>
@@ -9145,19 +9145,19 @@
         <v>17</v>
       </c>
       <c r="H151" s="9">
-        <v>9.08</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="I151" s="8">
-        <v>32</v>
-      </c>
-      <c r="J151" s="8">
-        <v>64.7</v>
+        <v>-1.4</v>
+      </c>
+      <c r="J151" s="10">
+        <v>51.4</v>
       </c>
       <c r="K151" s="9">
-        <v>24.14</v>
-      </c>
-      <c r="L151" s="8">
-        <v>110</v>
+        <v>33.090000000000003</v>
+      </c>
+      <c r="L151" s="10">
+        <v>90.1</v>
       </c>
       <c r="M151" s="9" t="s">
         <v>17</v>
@@ -9177,7 +9177,7 @@
     </row>
     <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
-        <v>40210</v>
+        <v>40238</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>17</v>
@@ -9198,19 +9198,19 @@
         <v>17</v>
       </c>
       <c r="H152" s="9">
-        <v>6.88</v>
+        <v>9.08</v>
       </c>
       <c r="I152" s="10">
-        <v>-16</v>
-      </c>
-      <c r="J152" s="8">
-        <v>89</v>
+        <v>32</v>
+      </c>
+      <c r="J152" s="10">
+        <v>64.7</v>
       </c>
       <c r="K152" s="9">
-        <v>15.07</v>
-      </c>
-      <c r="L152" s="8">
-        <v>151.69999999999999</v>
+        <v>24.14</v>
+      </c>
+      <c r="L152" s="10">
+        <v>110</v>
       </c>
       <c r="M152" s="9" t="s">
         <v>17</v>
@@ -9230,7 +9230,7 @@
     </row>
     <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
-        <v>40179</v>
+        <v>40210</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>17</v>
@@ -9251,19 +9251,19 @@
         <v>17</v>
       </c>
       <c r="H153" s="9">
-        <v>8.19</v>
+        <v>6.88</v>
       </c>
       <c r="I153" s="8">
-        <v>5.29</v>
-      </c>
-      <c r="J153" s="8">
-        <v>249.2</v>
+        <v>-16</v>
+      </c>
+      <c r="J153" s="10">
+        <v>89</v>
       </c>
       <c r="K153" s="9">
-        <v>8.19</v>
-      </c>
-      <c r="L153" s="8">
-        <v>249.2</v>
+        <v>15.07</v>
+      </c>
+      <c r="L153" s="10">
+        <v>151.69999999999999</v>
       </c>
       <c r="M153" s="9" t="s">
         <v>17</v>
@@ -9283,7 +9283,7 @@
     </row>
     <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
-        <v>40148</v>
+        <v>40179</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>17</v>
@@ -9304,19 +9304,19 @@
         <v>17</v>
       </c>
       <c r="H154" s="9">
-        <v>7.78</v>
-      </c>
-      <c r="I154" s="8">
-        <v>1.78</v>
-      </c>
-      <c r="J154" s="8">
-        <v>173</v>
+        <v>8.19</v>
+      </c>
+      <c r="I154" s="10">
+        <v>5.29</v>
+      </c>
+      <c r="J154" s="10">
+        <v>249.2</v>
       </c>
       <c r="K154" s="9">
-        <v>78.099999999999994</v>
-      </c>
-      <c r="L154" s="8">
-        <v>23.2</v>
+        <v>8.19</v>
+      </c>
+      <c r="L154" s="10">
+        <v>249.2</v>
       </c>
       <c r="M154" s="9" t="s">
         <v>17</v>
@@ -9336,7 +9336,7 @@
     </row>
     <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
-        <v>40118</v>
+        <v>40148</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>17</v>
@@ -9357,19 +9357,19 @@
         <v>17</v>
       </c>
       <c r="H155" s="9">
-        <v>7.64</v>
+        <v>7.78</v>
       </c>
       <c r="I155" s="10">
-        <v>-7.41</v>
-      </c>
-      <c r="J155" s="8">
-        <v>94.6</v>
+        <v>1.78</v>
+      </c>
+      <c r="J155" s="10">
+        <v>173</v>
       </c>
       <c r="K155" s="9">
-        <v>70.319999999999993</v>
-      </c>
-      <c r="L155" s="8">
-        <v>16.100000000000001</v>
+        <v>78.099999999999994</v>
+      </c>
+      <c r="L155" s="10">
+        <v>23.2</v>
       </c>
       <c r="M155" s="9" t="s">
         <v>17</v>
@@ -9389,7 +9389,7 @@
     </row>
     <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
-        <v>40087</v>
+        <v>40118</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>17</v>
@@ -9410,19 +9410,19 @@
         <v>17</v>
       </c>
       <c r="H156" s="9">
-        <v>8.25</v>
-      </c>
-      <c r="I156" s="10">
-        <v>-3.44</v>
-      </c>
-      <c r="J156" s="8">
-        <v>44.1</v>
+        <v>7.64</v>
+      </c>
+      <c r="I156" s="8">
+        <v>-7.41</v>
+      </c>
+      <c r="J156" s="10">
+        <v>94.6</v>
       </c>
       <c r="K156" s="9">
-        <v>62.68</v>
-      </c>
-      <c r="L156" s="8">
-        <v>10.7</v>
+        <v>70.319999999999993</v>
+      </c>
+      <c r="L156" s="10">
+        <v>16.100000000000001</v>
       </c>
       <c r="M156" s="9" t="s">
         <v>17</v>
@@ -9442,7 +9442,7 @@
     </row>
     <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
-        <v>40057</v>
+        <v>40087</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>17</v>
@@ -9463,19 +9463,19 @@
         <v>17</v>
       </c>
       <c r="H157" s="9">
-        <v>8.5500000000000007</v>
+        <v>8.25</v>
       </c>
       <c r="I157" s="8">
-        <v>5.58</v>
-      </c>
-      <c r="J157" s="8">
-        <v>53.8</v>
+        <v>-3.44</v>
+      </c>
+      <c r="J157" s="10">
+        <v>44.1</v>
       </c>
       <c r="K157" s="9">
-        <v>54.43</v>
-      </c>
-      <c r="L157" s="8">
-        <v>6.93</v>
+        <v>62.68</v>
+      </c>
+      <c r="L157" s="10">
+        <v>10.7</v>
       </c>
       <c r="M157" s="9" t="s">
         <v>17</v>
@@ -9495,7 +9495,7 @@
     </row>
     <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
-        <v>40026</v>
+        <v>40057</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>17</v>
@@ -9516,19 +9516,19 @@
         <v>17</v>
       </c>
       <c r="H158" s="9">
-        <v>8.09</v>
-      </c>
-      <c r="I158" s="8">
-        <v>7.82</v>
-      </c>
-      <c r="J158" s="8">
-        <v>39.200000000000003</v>
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="I158" s="10">
+        <v>5.58</v>
+      </c>
+      <c r="J158" s="10">
+        <v>53.8</v>
       </c>
       <c r="K158" s="9">
-        <v>45.88</v>
-      </c>
-      <c r="L158" s="8">
-        <v>1.19</v>
+        <v>54.43</v>
+      </c>
+      <c r="L158" s="10">
+        <v>6.93</v>
       </c>
       <c r="M158" s="9" t="s">
         <v>17</v>
@@ -9548,7 +9548,7 @@
     </row>
     <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
-        <v>39995</v>
+        <v>40026</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>17</v>
@@ -9569,19 +9569,19 @@
         <v>17</v>
       </c>
       <c r="H159" s="9">
-        <v>7.51</v>
-      </c>
-      <c r="I159" s="8">
-        <v>20.2</v>
-      </c>
-      <c r="J159" s="8">
-        <v>20.2</v>
+        <v>8.09</v>
+      </c>
+      <c r="I159" s="10">
+        <v>7.82</v>
+      </c>
+      <c r="J159" s="10">
+        <v>39.200000000000003</v>
       </c>
       <c r="K159" s="9">
-        <v>37.79</v>
+        <v>45.88</v>
       </c>
       <c r="L159" s="10">
-        <v>-4.4000000000000004</v>
+        <v>1.19</v>
       </c>
       <c r="M159" s="9" t="s">
         <v>17</v>
@@ -9601,7 +9601,7 @@
     </row>
     <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
-        <v>39965</v>
+        <v>39995</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>17</v>
@@ -9622,19 +9622,19 @@
         <v>17</v>
       </c>
       <c r="H160" s="9">
-        <v>6.25</v>
+        <v>7.51</v>
       </c>
       <c r="I160" s="10">
-        <v>-5.84</v>
-      </c>
-      <c r="J160" s="8">
-        <v>2</v>
+        <v>20.2</v>
+      </c>
+      <c r="J160" s="10">
+        <v>20.2</v>
       </c>
       <c r="K160" s="9">
-        <v>30.29</v>
-      </c>
-      <c r="L160" s="10">
-        <v>-9.02</v>
+        <v>37.79</v>
+      </c>
+      <c r="L160" s="8">
+        <v>-4.4000000000000004</v>
       </c>
       <c r="M160" s="9" t="s">
         <v>17</v>
@@ -9654,7 +9654,7 @@
     </row>
     <row r="161" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
-        <v>39934</v>
+        <v>39965</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>17</v>
@@ -9675,19 +9675,19 @@
         <v>17</v>
       </c>
       <c r="H161" s="9">
-        <v>6.63</v>
+        <v>6.25</v>
       </c>
       <c r="I161" s="8">
-        <v>12.3</v>
-      </c>
-      <c r="J161" s="8">
-        <v>3.77</v>
+        <v>-5.84</v>
+      </c>
+      <c r="J161" s="10">
+        <v>2</v>
       </c>
       <c r="K161" s="9">
-        <v>24.04</v>
-      </c>
-      <c r="L161" s="10">
-        <v>-11.5</v>
+        <v>30.29</v>
+      </c>
+      <c r="L161" s="8">
+        <v>-9.02</v>
       </c>
       <c r="M161" s="9" t="s">
         <v>17</v>
@@ -9707,7 +9707,7 @@
     </row>
     <row r="162" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
-        <v>39904</v>
+        <v>39934</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>17</v>
@@ -9728,19 +9728,19 @@
         <v>17</v>
       </c>
       <c r="H162" s="9">
-        <v>5.91</v>
-      </c>
-      <c r="I162" s="8">
-        <v>7.2</v>
-      </c>
-      <c r="J162" s="8">
-        <v>11.4</v>
+        <v>6.63</v>
+      </c>
+      <c r="I162" s="10">
+        <v>12.3</v>
+      </c>
+      <c r="J162" s="10">
+        <v>3.77</v>
       </c>
       <c r="K162" s="9">
-        <v>17.41</v>
-      </c>
-      <c r="L162" s="10">
-        <v>-16.2</v>
+        <v>24.04</v>
+      </c>
+      <c r="L162" s="8">
+        <v>-11.5</v>
       </c>
       <c r="M162" s="9" t="s">
         <v>17</v>
@@ -9760,7 +9760,7 @@
     </row>
     <row r="163" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
-        <v>39873</v>
+        <v>39904</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>17</v>
@@ -9781,19 +9781,19 @@
         <v>17</v>
       </c>
       <c r="H163" s="9">
-        <v>5.51</v>
-      </c>
-      <c r="I163" s="8">
-        <v>51.4</v>
-      </c>
-      <c r="J163" s="8">
-        <v>1.72</v>
+        <v>5.91</v>
+      </c>
+      <c r="I163" s="10">
+        <v>7.2</v>
+      </c>
+      <c r="J163" s="10">
+        <v>11.4</v>
       </c>
       <c r="K163" s="9">
-        <v>11.5</v>
-      </c>
-      <c r="L163" s="10">
-        <v>-25.7</v>
+        <v>17.41</v>
+      </c>
+      <c r="L163" s="8">
+        <v>-16.2</v>
       </c>
       <c r="M163" s="9" t="s">
         <v>17</v>
@@ -9813,7 +9813,7 @@
     </row>
     <row r="164" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
-        <v>39845</v>
+        <v>39873</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>17</v>
@@ -9834,19 +9834,19 @@
         <v>17</v>
       </c>
       <c r="H164" s="9">
-        <v>3.64</v>
-      </c>
-      <c r="I164" s="8">
-        <v>55.2</v>
+        <v>5.51</v>
+      </c>
+      <c r="I164" s="10">
+        <v>51.4</v>
       </c>
       <c r="J164" s="10">
-        <v>-27.1</v>
+        <v>1.72</v>
       </c>
       <c r="K164" s="9">
-        <v>5.98</v>
-      </c>
-      <c r="L164" s="10">
-        <v>-40.4</v>
+        <v>11.5</v>
+      </c>
+      <c r="L164" s="8">
+        <v>-25.7</v>
       </c>
       <c r="M164" s="9" t="s">
         <v>17</v>
@@ -9866,7 +9866,7 @@
     </row>
     <row r="165" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
-        <v>39814</v>
+        <v>39845</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>17</v>
@@ -9887,19 +9887,19 @@
         <v>17</v>
       </c>
       <c r="H165" s="9">
-        <v>2.34</v>
+        <v>3.64</v>
       </c>
       <c r="I165" s="10">
-        <v>-17.7</v>
-      </c>
-      <c r="J165" s="10">
-        <v>-53.6</v>
+        <v>55.2</v>
+      </c>
+      <c r="J165" s="8">
+        <v>-27.1</v>
       </c>
       <c r="K165" s="9">
-        <v>2.34</v>
-      </c>
-      <c r="L165" s="10">
-        <v>-53.6</v>
+        <v>5.98</v>
+      </c>
+      <c r="L165" s="8">
+        <v>-40.4</v>
       </c>
       <c r="M165" s="9" t="s">
         <v>17</v>
@@ -9919,7 +9919,7 @@
     </row>
     <row r="166" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
-        <v>39783</v>
+        <v>39814</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>17</v>
@@ -9940,19 +9940,19 @@
         <v>17</v>
       </c>
       <c r="H166" s="9">
-        <v>2.85</v>
-      </c>
-      <c r="I166" s="10">
-        <v>-27.4</v>
-      </c>
-      <c r="J166" s="10">
-        <v>-41.8</v>
+        <v>2.34</v>
+      </c>
+      <c r="I166" s="8">
+        <v>-17.7</v>
+      </c>
+      <c r="J166" s="8">
+        <v>-53.6</v>
       </c>
       <c r="K166" s="9">
-        <v>63.4</v>
+        <v>2.34</v>
       </c>
       <c r="L166" s="8">
-        <v>52.8</v>
+        <v>-53.6</v>
       </c>
       <c r="M166" s="9" t="s">
         <v>17</v>
@@ -9972,7 +9972,7 @@
     </row>
     <row r="167" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
-        <v>39753</v>
+        <v>39783</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>17</v>
@@ -9993,19 +9993,19 @@
         <v>17</v>
       </c>
       <c r="H167" s="9">
-        <v>3.93</v>
-      </c>
-      <c r="I167" s="10">
-        <v>-31.4</v>
-      </c>
-      <c r="J167" s="10">
-        <v>-17.5</v>
+        <v>2.85</v>
+      </c>
+      <c r="I167" s="8">
+        <v>-27.4</v>
+      </c>
+      <c r="J167" s="8">
+        <v>-41.8</v>
       </c>
       <c r="K167" s="9">
-        <v>60.55</v>
-      </c>
-      <c r="L167" s="8">
-        <v>65.5</v>
+        <v>63.4</v>
+      </c>
+      <c r="L167" s="10">
+        <v>52.8</v>
       </c>
       <c r="M167" s="9" t="s">
         <v>17</v>
@@ -10025,7 +10025,7 @@
     </row>
     <row r="168" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
-        <v>39722</v>
+        <v>39753</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>17</v>
@@ -10046,19 +10046,19 @@
         <v>17</v>
       </c>
       <c r="H168" s="9">
-        <v>5.73</v>
+        <v>3.93</v>
       </c>
       <c r="I168" s="8">
-        <v>3.01</v>
+        <v>-31.4</v>
       </c>
       <c r="J168" s="8">
-        <v>12.1</v>
+        <v>-17.5</v>
       </c>
       <c r="K168" s="9">
-        <v>56.63</v>
-      </c>
-      <c r="L168" s="8">
-        <v>77.900000000000006</v>
+        <v>60.55</v>
+      </c>
+      <c r="L168" s="10">
+        <v>65.5</v>
       </c>
       <c r="M168" s="9" t="s">
         <v>17</v>
@@ -10078,7 +10078,7 @@
     </row>
     <row r="169" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
-        <v>39692</v>
+        <v>39722</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>17</v>
@@ -10099,19 +10099,19 @@
         <v>17</v>
       </c>
       <c r="H169" s="9">
-        <v>5.56</v>
+        <v>5.73</v>
       </c>
       <c r="I169" s="10">
-        <v>-4.3899999999999997</v>
-      </c>
-      <c r="J169" s="8">
-        <v>6.42</v>
+        <v>3.01</v>
+      </c>
+      <c r="J169" s="10">
+        <v>12.1</v>
       </c>
       <c r="K169" s="9">
-        <v>50.9</v>
-      </c>
-      <c r="L169" s="8">
-        <v>90.5</v>
+        <v>56.63</v>
+      </c>
+      <c r="L169" s="10">
+        <v>77.900000000000006</v>
       </c>
       <c r="M169" s="9" t="s">
         <v>17</v>
@@ -10131,7 +10131,7 @@
     </row>
     <row r="170" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
-        <v>39661</v>
+        <v>39692</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>17</v>
@@ -10152,19 +10152,19 @@
         <v>17</v>
       </c>
       <c r="H170" s="9">
-        <v>5.81</v>
-      </c>
-      <c r="I170" s="10">
-        <v>-6.92</v>
-      </c>
-      <c r="J170" s="8">
-        <v>43.7</v>
+        <v>5.56</v>
+      </c>
+      <c r="I170" s="8">
+        <v>-4.3899999999999997</v>
+      </c>
+      <c r="J170" s="10">
+        <v>6.42</v>
       </c>
       <c r="K170" s="9">
-        <v>45.34</v>
-      </c>
-      <c r="L170" s="8">
-        <v>111</v>
+        <v>50.9</v>
+      </c>
+      <c r="L170" s="10">
+        <v>90.5</v>
       </c>
       <c r="M170" s="9" t="s">
         <v>17</v>
@@ -10184,7 +10184,7 @@
     </row>
     <row r="171" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
-        <v>39630</v>
+        <v>39661</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>17</v>
@@ -10205,19 +10205,19 @@
         <v>17</v>
       </c>
       <c r="H171" s="9">
-        <v>6.25</v>
+        <v>5.81</v>
       </c>
       <c r="I171" s="8">
-        <v>1.99</v>
-      </c>
-      <c r="J171" s="8">
-        <v>40.4</v>
+        <v>-6.92</v>
+      </c>
+      <c r="J171" s="10">
+        <v>43.7</v>
       </c>
       <c r="K171" s="9">
-        <v>39.53</v>
-      </c>
-      <c r="L171" s="8">
-        <v>126.6</v>
+        <v>45.34</v>
+      </c>
+      <c r="L171" s="10">
+        <v>111</v>
       </c>
       <c r="M171" s="9" t="s">
         <v>17</v>
@@ -10237,7 +10237,7 @@
     </row>
     <row r="172" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
-        <v>39600</v>
+        <v>39630</v>
       </c>
       <c r="B172" s="7" t="s">
         <v>17</v>
@@ -10258,19 +10258,19 @@
         <v>17</v>
       </c>
       <c r="H172" s="9">
-        <v>6.12</v>
+        <v>6.25</v>
       </c>
       <c r="I172" s="10">
-        <v>-4.2</v>
-      </c>
-      <c r="J172" s="8">
-        <v>85.7</v>
+        <v>1.99</v>
+      </c>
+      <c r="J172" s="10">
+        <v>40.4</v>
       </c>
       <c r="K172" s="9">
-        <v>33.29</v>
-      </c>
-      <c r="L172" s="8">
-        <v>156</v>
+        <v>39.53</v>
+      </c>
+      <c r="L172" s="10">
+        <v>126.6</v>
       </c>
       <c r="M172" s="9" t="s">
         <v>17</v>
@@ -10290,7 +10290,7 @@
     </row>
     <row r="173" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
-        <v>39569</v>
+        <v>39600</v>
       </c>
       <c r="B173" s="7" t="s">
         <v>17</v>
@@ -10311,19 +10311,19 @@
         <v>17</v>
       </c>
       <c r="H173" s="9">
-        <v>6.39</v>
+        <v>6.12</v>
       </c>
       <c r="I173" s="8">
-        <v>20.5</v>
-      </c>
-      <c r="J173" s="8">
-        <v>142.6</v>
+        <v>-4.2</v>
+      </c>
+      <c r="J173" s="10">
+        <v>85.7</v>
       </c>
       <c r="K173" s="9">
-        <v>27.17</v>
-      </c>
-      <c r="L173" s="8">
-        <v>179.9</v>
+        <v>33.29</v>
+      </c>
+      <c r="L173" s="10">
+        <v>156</v>
       </c>
       <c r="M173" s="9" t="s">
         <v>17</v>
@@ -10343,7 +10343,7 @@
     </row>
     <row r="174" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
-        <v>39539</v>
+        <v>39569</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>17</v>
@@ -10364,19 +10364,19 @@
         <v>17</v>
       </c>
       <c r="H174" s="9">
-        <v>5.3</v>
+        <v>6.39</v>
       </c>
       <c r="I174" s="10">
-        <v>-2.1</v>
-      </c>
-      <c r="J174" s="8">
-        <v>139.9</v>
+        <v>20.5</v>
+      </c>
+      <c r="J174" s="10">
+        <v>142.6</v>
       </c>
       <c r="K174" s="9">
-        <v>20.77</v>
-      </c>
-      <c r="L174" s="8">
-        <v>193.8</v>
+        <v>27.17</v>
+      </c>
+      <c r="L174" s="10">
+        <v>179.9</v>
       </c>
       <c r="M174" s="9" t="s">
         <v>17</v>
@@ -10396,7 +10396,7 @@
     </row>
     <row r="175" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
-        <v>39508</v>
+        <v>39539</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>17</v>
@@ -10417,19 +10417,19 @@
         <v>17</v>
       </c>
       <c r="H175" s="9">
-        <v>5.42</v>
+        <v>5.3</v>
       </c>
       <c r="I175" s="8">
-        <v>8.5399999999999991</v>
-      </c>
-      <c r="J175" s="8">
-        <v>211.6</v>
+        <v>-2.1</v>
+      </c>
+      <c r="J175" s="10">
+        <v>139.9</v>
       </c>
       <c r="K175" s="9">
-        <v>15.47</v>
-      </c>
-      <c r="L175" s="8">
-        <v>218.3</v>
+        <v>20.77</v>
+      </c>
+      <c r="L175" s="10">
+        <v>193.8</v>
       </c>
       <c r="M175" s="9" t="s">
         <v>17</v>
@@ -10449,7 +10449,7 @@
     </row>
     <row r="176" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
-        <v>39479</v>
+        <v>39508</v>
       </c>
       <c r="B176" s="7" t="s">
         <v>17</v>
@@ -10470,19 +10470,19 @@
         <v>17</v>
       </c>
       <c r="H176" s="9">
-        <v>4.99</v>
+        <v>5.42</v>
       </c>
       <c r="I176" s="10">
-        <v>-1.33</v>
-      </c>
-      <c r="J176" s="8">
-        <v>198.9</v>
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="J176" s="10">
+        <v>211.6</v>
       </c>
       <c r="K176" s="9">
-        <v>10.050000000000001</v>
-      </c>
-      <c r="L176" s="8">
-        <v>222</v>
+        <v>15.47</v>
+      </c>
+      <c r="L176" s="10">
+        <v>218.3</v>
       </c>
       <c r="M176" s="9" t="s">
         <v>17</v>
@@ -10502,7 +10502,7 @@
     </row>
     <row r="177" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
-        <v>39448</v>
+        <v>39479</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>17</v>
@@ -10523,19 +10523,19 @@
         <v>17</v>
       </c>
       <c r="H177" s="9">
-        <v>5.0599999999999996</v>
+        <v>4.99</v>
       </c>
       <c r="I177" s="8">
-        <v>3.27</v>
-      </c>
-      <c r="J177" s="8">
-        <v>248.7</v>
+        <v>-1.33</v>
+      </c>
+      <c r="J177" s="10">
+        <v>198.9</v>
       </c>
       <c r="K177" s="9">
-        <v>5.0599999999999996</v>
-      </c>
-      <c r="L177" s="8">
-        <v>248.7</v>
+        <v>10.050000000000001</v>
+      </c>
+      <c r="L177" s="10">
+        <v>222</v>
       </c>
       <c r="M177" s="9" t="s">
         <v>17</v>
@@ -10555,7 +10555,7 @@
     </row>
     <row r="178" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
-        <v>39417</v>
+        <v>39448</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>17</v>
@@ -10576,19 +10576,19 @@
         <v>17</v>
       </c>
       <c r="H178" s="9">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="I178" s="8">
-        <v>2.94</v>
-      </c>
-      <c r="J178" s="8">
-        <v>388.3</v>
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="I178" s="10">
+        <v>3.27</v>
+      </c>
+      <c r="J178" s="10">
+        <v>248.7</v>
       </c>
       <c r="K178" s="9">
-        <v>41.48</v>
-      </c>
-      <c r="L178" s="8">
-        <v>444</v>
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="L178" s="10">
+        <v>248.7</v>
       </c>
       <c r="M178" s="9" t="s">
         <v>17</v>
@@ -10608,7 +10608,7 @@
     </row>
     <row r="179" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
-        <v>39387</v>
+        <v>39417</v>
       </c>
       <c r="B179" s="7" t="s">
         <v>17</v>
@@ -10629,19 +10629,19 @@
         <v>17</v>
       </c>
       <c r="H179" s="9">
-        <v>4.76</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I179" s="10">
-        <v>-6.84</v>
-      </c>
-      <c r="J179" s="8">
-        <v>501.8</v>
+        <v>2.94</v>
+      </c>
+      <c r="J179" s="10">
+        <v>388.3</v>
       </c>
       <c r="K179" s="9">
-        <v>36.58</v>
-      </c>
-      <c r="L179" s="8">
-        <v>452.4</v>
+        <v>41.48</v>
+      </c>
+      <c r="L179" s="10">
+        <v>444</v>
       </c>
       <c r="M179" s="9" t="s">
         <v>17</v>
@@ -10661,7 +10661,7 @@
     </row>
     <row r="180" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
-        <v>39356</v>
+        <v>39387</v>
       </c>
       <c r="B180" s="7" t="s">
         <v>17</v>
@@ -10682,19 +10682,19 @@
         <v>17</v>
       </c>
       <c r="H180" s="9">
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="I180" s="10">
-        <v>-2.1800000000000002</v>
-      </c>
-      <c r="J180" s="8">
-        <v>309.8</v>
+        <v>4.76</v>
+      </c>
+      <c r="I180" s="8">
+        <v>-6.84</v>
+      </c>
+      <c r="J180" s="10">
+        <v>501.8</v>
       </c>
       <c r="K180" s="9">
-        <v>31.82</v>
-      </c>
-      <c r="L180" s="8">
-        <v>445.7</v>
+        <v>36.58</v>
+      </c>
+      <c r="L180" s="10">
+        <v>452.4</v>
       </c>
       <c r="M180" s="9" t="s">
         <v>17</v>
@@ -10714,54 +10714,107 @@
     </row>
     <row r="181" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
+        <v>39356</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H181" s="9">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="I181" s="8">
+        <v>-2.1800000000000002</v>
+      </c>
+      <c r="J181" s="10">
+        <v>309.8</v>
+      </c>
+      <c r="K181" s="9">
+        <v>31.82</v>
+      </c>
+      <c r="L181" s="10">
+        <v>445.7</v>
+      </c>
+      <c r="M181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q181" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A182" s="6">
         <v>39326</v>
       </c>
-      <c r="B181" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C181" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D181" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E181" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F181" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G181" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H181" s="9">
+      <c r="B182" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H182" s="9">
         <v>5.22</v>
       </c>
-      <c r="I181" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J181" s="8">
+      <c r="I182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J182" s="10">
         <v>237.6</v>
       </c>
-      <c r="K181" s="9">
+      <c r="K182" s="9">
         <v>26.72</v>
       </c>
-      <c r="L181" s="8">
+      <c r="L182" s="10">
         <v>482.6</v>
       </c>
-      <c r="M181" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N181" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O181" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P181" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q181" s="9" t="s">
+      <c r="M182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q182" s="9" t="s">
         <v>17</v>
       </c>
     </row>
